--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -19,66 +19,180 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="63">
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최선을 다해 케어하겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{PlayerName}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Content</x:t>
+  </x:si>
   <x:si>
     <x:t>인사팀장</x:t>
   </x:si>
   <x:si>
+    <x:t>Speaker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B. 프로젝트요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background</x:t>
+  </x:si>
+  <x:si>
     <x:t>다음 대사 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Background</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
     <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
   </x:si>
   <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
+    <x:t>SpeakerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/NPC/Player</x:t>
   </x:si>
   <x:si>
     <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
@@ -87,112 +201,13 @@
     <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
   </x:si>
   <x:si>
-    <x:t>Opening_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Speaker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최선을 다해 케어하겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{PlayerName}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B. 프로젝트요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
+    <x:t>Prefabs/Character/NPC/Boss</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
   </x:si>
   <x:si>
     <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextID</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -339,7 +354,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -387,6 +402,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -992,103 +1013,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:O35"/>
+  <x:dimension ref="A1:P35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="13.85546875" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="120" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="7" max="16384" width="12.54296875" style="3"/>
+    <x:col min="4" max="4" width="23.28515625" style="3" customWidth="1"/>
+    <x:col min="5" max="5" width="120" style="3" customWidth="1"/>
+    <x:col min="6" max="6" width="30.54296875" style="3" customWidth="1"/>
+    <x:col min="7" max="7" width="26.54296875" style="3" customWidth="1"/>
+    <x:col min="8" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
+      <x:c r="H1" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
+      <x:c r="B2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H2" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G2" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="10" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D3" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+    </x:row>
+    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E4" s="5"/>
-      <x:c r="F4" s="14"/>
-      <x:c r="G4" s="5"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E4" s="5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F4" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G4" s="14"/>
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
@@ -1097,23 +1132,28 @@
       <x:c r="M4" s="5"/>
       <x:c r="N4" s="5"/>
       <x:c r="O4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P4" s="5"/>
+    </x:row>
+    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="14"/>
-      <x:c r="G5" s="5"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G5" s="14"/>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1122,22 +1162,27 @@
       <x:c r="M5" s="5"/>
       <x:c r="N5" s="5"/>
       <x:c r="O5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P5" s="5"/>
+    </x:row>
+    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E6" s="5" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F6" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
@@ -1147,22 +1192,27 @@
       <x:c r="M6" s="5"/>
       <x:c r="N6" s="5"/>
       <x:c r="O6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P6" s="5"/>
+    </x:row>
+    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E7" s="5"/>
-      <x:c r="F7" s="5"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E7" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5"/>
       <x:c r="I7" s="5"/>
@@ -1172,22 +1222,27 @@
       <x:c r="M7" s="5"/>
       <x:c r="N7" s="5"/>
       <x:c r="O7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P7" s="5"/>
+    </x:row>
+    <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="5"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5"/>
       <x:c r="I8" s="5"/>
@@ -1197,22 +1252,27 @@
       <x:c r="M8" s="5"/>
       <x:c r="N8" s="5"/>
       <x:c r="O8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P8" s="5"/>
+    </x:row>
+    <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E9" s="5"/>
-      <x:c r="F9" s="5"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5"/>
       <x:c r="I9" s="5"/>
@@ -1222,22 +1282,27 @@
       <x:c r="M9" s="5"/>
       <x:c r="N9" s="5"/>
       <x:c r="O9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P9" s="5"/>
+    </x:row>
+    <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="6" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B10" s="4" t="s">
+      <x:c r="C10" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E10" s="5" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C10" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E10" s="5"/>
-      <x:c r="F10" s="5"/>
       <x:c r="G10" s="5"/>
       <x:c r="H10" s="5"/>
       <x:c r="I10" s="5"/>
@@ -1247,22 +1312,27 @@
       <x:c r="M10" s="5"/>
       <x:c r="N10" s="5"/>
       <x:c r="O10" s="5"/>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P10" s="5"/>
+    </x:row>
+    <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B11" s="4" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="5"/>
-      <x:c r="F11" s="5"/>
       <x:c r="G11" s="5"/>
       <x:c r="H11" s="5"/>
       <x:c r="I11" s="5"/>
@@ -1272,22 +1342,27 @@
       <x:c r="M11" s="5"/>
       <x:c r="N11" s="5"/>
       <x:c r="O11" s="5"/>
-    </x:row>
-    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P11" s="5"/>
+    </x:row>
+    <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G12" s="5"/>
       <x:c r="H12" s="5"/>
       <x:c r="I12" s="5"/>
@@ -1297,22 +1372,27 @@
       <x:c r="M12" s="5"/>
       <x:c r="N12" s="5"/>
       <x:c r="O12" s="5"/>
-    </x:row>
-    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P12" s="5"/>
+    </x:row>
+    <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E13" s="5"/>
-      <x:c r="F13" s="5"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E13" s="5" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G13" s="5"/>
       <x:c r="H13" s="5"/>
       <x:c r="I13" s="5"/>
@@ -1322,22 +1402,27 @@
       <x:c r="M13" s="5"/>
       <x:c r="N13" s="5"/>
       <x:c r="O13" s="5"/>
-    </x:row>
-    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P13" s="5"/>
+    </x:row>
+    <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E14" s="5"/>
-      <x:c r="F14" s="5"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E14" s="5" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G14" s="5"/>
       <x:c r="H14" s="5"/>
       <x:c r="I14" s="5"/>
@@ -1347,22 +1432,27 @@
       <x:c r="M14" s="5"/>
       <x:c r="N14" s="5"/>
       <x:c r="O14" s="5"/>
-    </x:row>
-    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P14" s="5"/>
+    </x:row>
+    <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C15" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E15" s="5"/>
-      <x:c r="F15" s="5"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F15" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G15" s="5"/>
       <x:c r="H15" s="5"/>
       <x:c r="I15" s="5"/>
@@ -1372,192 +1462,257 @@
       <x:c r="M15" s="5"/>
       <x:c r="N15" s="5"/>
       <x:c r="O15" s="5"/>
-    </x:row>
-    <x:row r="16" spans="1:4" ht="15.75" customHeight="1">
+      <x:c r="P15" s="5"/>
+    </x:row>
+    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E16" s="5" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F16" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A17" s="6" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D16" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A17" s="6" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B17" s="4" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="C17" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:4" ht="15.75" customHeight="1">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F17" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E18" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F18" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C19" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E19" s="5"/>
-    </x:row>
-    <x:row r="20" spans="1:4" ht="15.75" customHeight="1">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F19" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F20" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A21" s="6" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A21" s="6" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="5" t="s">
         <x:v>12</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" spans="1:4" ht="15.75" customHeight="1">
+      <x:c r="D21" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E21" s="5" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F21" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B22" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="5" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:4" ht="15.75" customHeight="1">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E22" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F22" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:4" ht="15.75" customHeight="1">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F23" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D24" s="5" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E24" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F24" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A25" s="7"/>
       <x:c r="B25" s="7"/>
       <x:c r="C25" s="7"/>
-      <x:c r="E25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D25" s="7"/>
+      <x:c r="F25" s="5"/>
+    </x:row>
+    <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="8"/>
       <x:c r="B26" s="8"/>
       <x:c r="C26" s="8"/>
-      <x:c r="E26" s="5"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D26" s="8"/>
+      <x:c r="F26" s="5"/>
+    </x:row>
+    <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="8"/>
       <x:c r="B27" s="8"/>
       <x:c r="C27" s="8"/>
-      <x:c r="E27" s="5"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D27" s="8"/>
+      <x:c r="F27" s="5"/>
+    </x:row>
+    <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A28" s="8"/>
       <x:c r="B28" s="8"/>
       <x:c r="C28" s="8"/>
-      <x:c r="E28" s="5"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D28" s="8"/>
+      <x:c r="F28" s="5"/>
+    </x:row>
+    <x:row r="29" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A29" s="8"/>
       <x:c r="B29" s="8"/>
       <x:c r="C29" s="8"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D29" s="8"/>
+    </x:row>
+    <x:row r="30" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A30" s="8"/>
       <x:c r="B30" s="8"/>
       <x:c r="C30" s="8"/>
-    </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D30" s="8"/>
+    </x:row>
+    <x:row r="31" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A31" s="8"/>
       <x:c r="B31" s="8"/>
       <x:c r="C31" s="8"/>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D31" s="8"/>
+    </x:row>
+    <x:row r="32" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A32" s="9"/>
       <x:c r="B32" s="9"/>
       <x:c r="C32" s="9"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D32" s="9"/>
+    </x:row>
+    <x:row r="33" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A33" s="9"/>
       <x:c r="B33" s="9"/>
       <x:c r="C33" s="9"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D33" s="9"/>
+    </x:row>
+    <x:row r="34" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A34" s="9"/>
       <x:c r="B34" s="9"/>
       <x:c r="C34" s="9"/>
-    </x:row>
-    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D34" s="9"/>
+    </x:row>
+    <x:row r="35" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A35" s="9"/>
       <x:c r="B35" s="9"/>
       <x:c r="C35" s="9"/>
+      <x:c r="D35" s="9"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -19,180 +19,180 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="63">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="63">
+  <x:si>
+    <x:t>Content</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Speaker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인사팀장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX</x:t>
+  </x:si>
   <x:si>
     <x:t>ID</x:t>
   </x:si>
   <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX</x:t>
+    <x:t>Opening_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B. 프로젝트요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeakerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{PlayerName}</x:t>
   </x:si>
   <x:si>
     <x:t>최선을 다해 케어하겠습니다!</x:t>
   </x:si>
   <x:si>
-    <x:t>{PlayerName}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인사팀장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Speaker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
   </x:si>
   <x:si>
     <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
   </x:si>
   <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
     <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
   </x:si>
   <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B. 프로젝트요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeakerPath</x:t>
+    <x:t>Prefabs/Character/NPC/Player</x:t>
   </x:si>
   <x:si>
     <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/NPC/Player</x:t>
   </x:si>
   <x:si>
     <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
@@ -1028,100 +1028,100 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="E1" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="H1" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B3" s="10" t="s">
+      <x:c r="F3" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F3" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="11" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G4" s="14"/>
       <x:c r="H4" s="5"/>
@@ -1136,22 +1136,19 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G5" s="14"/>
       <x:c r="H5" s="5"/>
@@ -1166,22 +1163,19 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="F6" s="3" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>
@@ -1196,22 +1190,19 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D7" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F7" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5"/>
@@ -1226,22 +1217,19 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D8" s="16" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E8" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5"/>
@@ -1256,22 +1244,19 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F9" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5"/>
@@ -1286,22 +1271,19 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G10" s="5"/>
       <x:c r="H10" s="5"/>
@@ -1316,22 +1298,19 @@
     </x:row>
     <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D11" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E11" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F11" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G11" s="5"/>
       <x:c r="H11" s="5"/>
@@ -1346,22 +1325,19 @@
     </x:row>
     <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D12" s="16" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E12" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F12" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G12" s="5"/>
       <x:c r="H12" s="5"/>
@@ -1376,22 +1352,19 @@
     </x:row>
     <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E13" s="5" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="F13" s="3" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="G13" s="5"/>
       <x:c r="H13" s="5"/>
@@ -1406,22 +1379,19 @@
     </x:row>
     <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E14" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F14" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G14" s="5"/>
       <x:c r="H14" s="5"/>
@@ -1436,22 +1406,19 @@
     </x:row>
     <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C15" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D15" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E15" s="15" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="F15" s="3" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="G15" s="5"/>
       <x:c r="H15" s="5"/>
@@ -1464,135 +1431,117 @@
       <x:c r="O15" s="5"/>
       <x:c r="P15" s="5"/>
     </x:row>
-    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E16" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F16" s="3" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="16" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E17" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F17" s="3" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E18" s="5" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F18" s="3" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B19" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C19" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D19" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E19" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F19" s="3" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D20" s="16" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E20" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F20" s="3" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E21" s="5" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F21" s="3" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:6" ht="15.75" customHeight="1">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
         <x:v>60</x:v>
@@ -1600,48 +1549,39 @@
       <x:c r="E22" s="5" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F22" s="3" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:6" ht="15.75" customHeight="1">
+    </x:row>
+    <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D23" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E23" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F23" s="3" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:6" ht="15.75" customHeight="1">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D24" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E24" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F24" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -19,54 +19,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="63">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="89">
+  <x:si>
+    <x:t>...결국 또 D 등급이군. 지난번 경고가 가벼웠던 모양이지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인사팀장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextID</x:t>
+  </x:si>
   <x:si>
     <x:t>Content</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
     <x:t>Speaker</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인사팀장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
+    <x:t>Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver</x:t>
   </x:si>
   <x:si>
     <x:t>Opening_03</x:t>
@@ -75,146 +138,161 @@
     <x:t>H.B. 프로젝트요?</x:t>
   </x:si>
   <x:si>
+    <x:t>Opening_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_15</x:t>
+  </x:si>
+  <x:si>
     <x:t>Opening_19</x:t>
   </x:si>
   <x:si>
     <x:t>Opening_21</x:t>
   </x:si>
   <x:si>
-    <x:t>Opening_05</x:t>
+    <x:t>Opening_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_18</x:t>
   </x:si>
   <x:si>
     <x:t>Opening_14</x:t>
   </x:si>
   <x:si>
+    <x:t>Opening_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_13</x:t>
+  </x:si>
+  <x:si>
     <x:t>Opening_08</x:t>
   </x:si>
   <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
+    <x:t>Opening_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_20</x:t>
   </x:si>
   <x:si>
     <x:t>Opening_16</x:t>
   </x:si>
   <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_13</x:t>
+    <x:t>다음 대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeakerPath</x:t>
   </x:si>
   <x:si>
     <x:t>Opening_09</x:t>
   </x:si>
   <x:si>
-    <x:t>Opening_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
     <x:t>Opening_11</x:t>
   </x:si>
   <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeakerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
+    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/NPC/Player</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보안요원, 이 친구 짐 정리시키고 밖으로 던져버리게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
   </x:si>
   <x:si>
     <x:t>{PlayerName}</x:t>
   </x:si>
   <x:si>
+    <x:t>GameOver_2_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_02</x:t>
+  </x:si>
+  <x:si>
     <x:t>최선을 다해 케어하겠습니다!</x:t>
   </x:si>
   <x:si>
-    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/NPC/Player</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
+    <x:t>지, 지부장님! 한 번만 더 기회를 주십시오!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>규정은 규정이야. 자네한테 줄 기회 따위는 없어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/NPC/Boss</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 요양보조사 하나 교체하는 건 일도 아니지.</x:t>
   </x:si>
   <x:si>
     <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
   </x:si>
   <x:si>
-    <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/NPC/Boss</x:t>
+    <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
   </x:si>
   <x:si>
     <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -259,6 +337,11 @@
       <x:name val="&quot;맑은 고딕&quot;"/>
       <x:sz val="11"/>
       <x:color rgb="ff008000"/>
+    </x:font>
+    <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
     </x:font>
   </x:fonts>
   <x:fills count="8">
@@ -382,9 +465,6 @@
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
@@ -408,6 +488,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1013,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:P35"/>
+  <x:dimension ref="A1:P36"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
@@ -1028,102 +1111,102 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G1" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H1" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="10" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F3" s="12" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H3" s="11" t="s">
-        <x:v>14</x:v>
+      <x:c r="D3" s="9" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G4" s="14"/>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G4" s="13"/>
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
@@ -1136,21 +1219,21 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G5" s="14"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G5" s="13"/>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1163,19 +1246,19 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>
@@ -1190,19 +1273,19 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D7" s="6" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5"/>
@@ -1217,19 +1300,19 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5"/>
@@ -1244,19 +1327,19 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5"/>
@@ -1271,19 +1354,19 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="5"/>
       <x:c r="H10" s="5"/>
@@ -1298,19 +1381,19 @@
     </x:row>
     <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="5"/>
       <x:c r="H11" s="5"/>
@@ -1325,19 +1408,19 @@
     </x:row>
     <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G12" s="5"/>
       <x:c r="H12" s="5"/>
@@ -1352,19 +1435,19 @@
     </x:row>
     <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E13" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G13" s="5"/>
       <x:c r="H13" s="5"/>
@@ -1379,19 +1462,19 @@
     </x:row>
     <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E14" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G14" s="5"/>
       <x:c r="H14" s="5"/>
@@ -1406,19 +1489,19 @@
     </x:row>
     <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="6" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G15" s="5"/>
       <x:c r="H15" s="5"/>
@@ -1433,228 +1516,370 @@
     </x:row>
     <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C16" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D16" s="6" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E16" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E18" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="6" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>17</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>26</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>49</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E21" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B22" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E22" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C23" s="6" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D23" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B24" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D24" s="6" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E24" s="5" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A25" s="7"/>
-      <x:c r="B25" s="7"/>
-      <x:c r="C25" s="7"/>
-      <x:c r="D25" s="7"/>
-      <x:c r="F25" s="5"/>
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A25" s="7" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B25" s="7" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C25" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F25" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G25" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A26" s="8"/>
-      <x:c r="B26" s="8"/>
-      <x:c r="C26" s="8"/>
-      <x:c r="D26" s="8"/>
+      <x:c r="A26" s="7" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B26" s="7" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="F26" s="5"/>
     </x:row>
     <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A27" s="8"/>
-      <x:c r="B27" s="8"/>
-      <x:c r="C27" s="8"/>
-      <x:c r="D27" s="8"/>
+      <x:c r="A27" s="7" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B27" s="7" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C27" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D27" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="F27" s="5"/>
     </x:row>
     <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A28" s="8"/>
-      <x:c r="B28" s="8"/>
-      <x:c r="C28" s="8"/>
-      <x:c r="D28" s="8"/>
+      <x:c r="A28" s="7" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B28" s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D28" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="s">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="F28" s="5"/>
     </x:row>
-    <x:row r="29" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A29" s="8"/>
-      <x:c r="B29" s="8"/>
-      <x:c r="C29" s="8"/>
-      <x:c r="D29" s="8"/>
-    </x:row>
-    <x:row r="30" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A30" s="8"/>
-      <x:c r="B30" s="8"/>
-      <x:c r="C30" s="8"/>
-      <x:c r="D30" s="8"/>
-    </x:row>
-    <x:row r="31" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A31" s="8"/>
-      <x:c r="B31" s="8"/>
-      <x:c r="C31" s="8"/>
-      <x:c r="D31" s="8"/>
-    </x:row>
-    <x:row r="32" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A32" s="9"/>
-      <x:c r="B32" s="9"/>
-      <x:c r="C32" s="9"/>
-      <x:c r="D32" s="9"/>
-    </x:row>
-    <x:row r="33" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A33" s="9"/>
-      <x:c r="B33" s="9"/>
-      <x:c r="C33" s="9"/>
-      <x:c r="D33" s="9"/>
-    </x:row>
-    <x:row r="34" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A34" s="9"/>
-      <x:c r="B34" s="9"/>
-      <x:c r="C34" s="9"/>
-      <x:c r="D34" s="9"/>
-    </x:row>
-    <x:row r="35" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A35" s="9"/>
-      <x:c r="B35" s="9"/>
-      <x:c r="C35" s="9"/>
-      <x:c r="D35" s="9"/>
-    </x:row>
-    <x:row r="36" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A29" s="7" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B29" s="7" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A30" s="7" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B30" s="7" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A31" s="7" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B31" s="7" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E31" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A32" s="7" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C32" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D32" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A33" s="7" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E33" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A34" s="7" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E34" s="3" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A35" s="7" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B35" s="7" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C35" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E35" s="17" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A36" s="7" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B36" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E36" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
     <x:row r="37" ht="15.75" customHeight="1"/>
     <x:row r="38" ht="15.75" customHeight="1"/>
     <x:row r="39" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -19,249 +19,330 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="89">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="117">
+  <x:si>
+    <x:t>Quest_03_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바로 온도 올려드릴게요, 제발 메테오만 쏘지 마세요...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 문 손잡이 또 박살 내셨네요… 제 월급에서 또 까이겠네…</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이봐, 샤워실 물 온도가 너무 차잖아! 허리가 하나도 안 지져져!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월급 200만 원에 블랙기업이라니… 퇴사하고 싶다…</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그건 외부에 사찰단 올 때 보여주는 위조 간판이고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거긴 단순한 시골 노인정이 아니야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네? 쥐, 쥐어짠다뇨…?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저희 실버타운 슬로건이 '사랑과 정성의 실버타운' 아니었습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인사팀장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Content</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Speaker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참고로 자네 지난달 파스값, 실적 못 채우면 자네 월급에서 깐다. 수고하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{PlayerName}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최선을 다해 케어하겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들 멘탈을 억지로라도 끌어올려서 '기억의 파편'을 쥐어짜 내야 하는 '재고 관리실'이라고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3일 차 보고서 잘 봤네. 근데 지출 내역에 '한방 총명탕 팩'이랑 '초강력 한방 파스 500장'은 뭔가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
+  </x:si>
   <x:si>
     <x:t>...결국 또 D 등급이군. 지난번 경고가 가벼웠던 모양이지?</x:t>
   </x:si>
   <x:si>
-    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
+    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
   </x:si>
   <x:si>
     <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
   </x:si>
   <x:si>
-    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인사팀장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Speaker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Home</x:t>
+    <x:t>H.B. 프로젝트요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_19</x:t>
   </x:si>
   <x:si>
     <x:t>GameOver</x:t>
   </x:si>
   <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B. 프로젝트요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_10</x:t>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_18</x:t>
   </x:si>
   <x:si>
     <x:t>Opening_02</x:t>
   </x:si>
   <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
     <x:t>Opening_14</x:t>
   </x:si>
   <x:si>
+    <x:t>Opening_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeakerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_12</x:t>
+  </x:si>
+  <x:si>
     <x:t>Opening_07</x:t>
   </x:si>
   <x:si>
-    <x:t>Room_Office</x:t>
+    <x:t>Opening_20</x:t>
   </x:si>
   <x:si>
     <x:t>Opening_13</x:t>
   </x:si>
   <x:si>
-    <x:t>Opening_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeakerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_11</x:t>
+    <x:t>보안요원, 이 친구 짐 정리시키고 밖으로 던져버리게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/NPC/Player</x:t>
   </x:si>
   <x:si>
     <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Character/NPC/Player</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보안요원, 이 친구 짐 정리시키고 밖으로 던져버리게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{PlayerName}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최선을 다해 케어하겠습니다!</x:t>
+    <x:t>쯧쯧… 자네, 착각하지 말게. 상부에서 매달 내려주는 지원금이 어르신들 찜질방이나 지어주라고 나오는 공짜 돈인 줄 아나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님. 어르신들이 관절염이랑 건망증 때문에 자꾸 복도에서 마법을 쏘셔서요. 파스라도 붙여드려야 조용해집니다.</x:t>
   </x:si>
   <x:si>
     <x:t>지, 지부장님! 한 번만 더 기회를 주십시오!</x:t>
@@ -282,10 +363,13 @@
     <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
   </x:si>
   <x:si>
+    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
+  </x:si>
+  <x:si>
     <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
   </x:si>
   <x:si>
-    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
+    <x:t>5일 차가 되면 지하 4층 추출 장치 전원이 켜질 테니, 어르신들 초능력이나 팍팍 추출할 준비나 하게.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1096,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:P36"/>
+  <x:dimension ref="A1:P50"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
@@ -1111,100 +1195,100 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G1" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H1" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H2" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="10" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="9" t="s">
-        <x:v>24</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="9" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="9" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D3" s="9" t="s">
-        <x:v>60</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E3" s="11" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F3" s="11" t="s">
-        <x:v>47</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G3" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="10" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G4" s="13"/>
       <x:c r="H4" s="5"/>
@@ -1219,19 +1303,19 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G5" s="13"/>
       <x:c r="H5" s="5"/>
@@ -1246,19 +1330,19 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>
@@ -1273,19 +1357,19 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5"/>
@@ -1300,19 +1384,19 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>1</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5"/>
@@ -1327,19 +1411,19 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5"/>
@@ -1354,19 +1438,19 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G10" s="5"/>
       <x:c r="H10" s="5"/>
@@ -1381,19 +1465,19 @@
     </x:row>
     <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G11" s="5"/>
       <x:c r="H11" s="5"/>
@@ -1408,19 +1492,19 @@
     </x:row>
     <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="5"/>
       <x:c r="H12" s="5"/>
@@ -1435,19 +1519,19 @@
     </x:row>
     <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E13" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G13" s="5"/>
       <x:c r="H13" s="5"/>
@@ -1462,19 +1546,19 @@
     </x:row>
     <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E14" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G14" s="5"/>
       <x:c r="H14" s="5"/>
@@ -1489,19 +1573,19 @@
     </x:row>
     <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C15" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G15" s="5"/>
       <x:c r="H15" s="5"/>
@@ -1516,384 +1600,521 @@
     </x:row>
     <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C16" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E16" s="5" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="D16" s="6" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E16" s="5" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E18" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B19" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C19" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D19" s="16" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E21" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B22" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E22" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>56</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C23" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D23" s="16" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>12</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B24" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D24" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E24" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A25" s="7" t="s">
-        <x:v>78</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B25" s="7" t="s">
-        <x:v>79</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E25" s="17" t="s">
-        <x:v>3</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F25" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G25" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="7" t="s">
-        <x:v>79</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B26" s="7" t="s">
-        <x:v>76</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C26" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E26" s="17" t="s">
-        <x:v>6</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F26" s="5"/>
     </x:row>
     <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="7" t="s">
-        <x:v>76</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B27" s="7" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C27" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E27" s="17" t="s">
-        <x:v>5</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F27" s="5"/>
     </x:row>
     <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A28" s="7" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D28" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E28" s="17" t="s">
-        <x:v>11</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F28" s="5"/>
     </x:row>
     <x:row r="29" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A29" s="7" t="s">
-        <x:v>68</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B29" s="7" t="s">
-        <x:v>71</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C29" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D29" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E29" s="17" t="s">
-        <x:v>0</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G29" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A30" s="7" t="s">
-        <x:v>71</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B30" s="7" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C30" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D30" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E30" s="17" t="s">
-        <x:v>81</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F30" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A31" s="7" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="7" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C31" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D31" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E31" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A32" s="7" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="7" t="s">
-        <x:v>77</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C32" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D32" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E32" s="17" t="s">
-        <x:v>82</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A33" s="7" t="s">
-        <x:v>77</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B33" s="7" t="s">
-        <x:v>70</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C33" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D33" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E33" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A34" s="7" t="s">
-        <x:v>70</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="7" t="s">
-        <x:v>69</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C34" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D34" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A35" s="7" t="s">
-        <x:v>69</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B35" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C35" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D35" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E35" s="17" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A36" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E36" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A37" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B37" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E37" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A38" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B38" s="3" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E38" s="3" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A39" s="3" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B39" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E39" s="3" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A40" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B40" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E40" s="17" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A41" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B41" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E41" s="3" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A42" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B42" s="3" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E42" s="3" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A43" s="3" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B43" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E43" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A44" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B44" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E44" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="15.75" customHeight="1"/>
-    <x:row r="38" ht="15.75" customHeight="1"/>
-    <x:row r="39" ht="15.75" customHeight="1"/>
-    <x:row r="40" ht="15.75" customHeight="1"/>
-    <x:row r="41" ht="15.75" customHeight="1"/>
-    <x:row r="42" ht="15.75" customHeight="1"/>
-    <x:row r="43" ht="15.75" customHeight="1"/>
-    <x:row r="44" ht="15.75" customHeight="1"/>
-    <x:row r="45" ht="15.75" customHeight="1"/>
-    <x:row r="46" ht="15.75" customHeight="1"/>
-    <x:row r="47" ht="15.75" customHeight="1"/>
-    <x:row r="48" ht="15.75" customHeight="1"/>
-    <x:row r="49" ht="15.75" customHeight="1"/>
-    <x:row r="50" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A45" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" s="3" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E45" s="17" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A46" s="3" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B46" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E46" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A47" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B47" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E47" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A48" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B48" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E48" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A49" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B49" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E49" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A50" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E50" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
     <x:row r="51" ht="15.75" customHeight="1"/>
     <x:row r="52" ht="15.75" customHeight="1"/>
     <x:row r="53" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -19,357 +19,831 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="117">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="275">
+  <x:si>
+    <x:t>하하! 자네는 그 매뉴얼 다 보고서도 아직 순진한 소리를 하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초능력이 뿌리째 뽑혀 나가는데 사람이 멀쩡할 리가 있나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 보안요원! 이 친구 짐 챙겨서 정문 밖으로 던져버리게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니... 왠지 이 기계 앞에만 오면 머리가 핑 돌고, 옛날에 마왕 잡을 때 쓰던 메테오 마나가 쪽쪽 빨려 나가는 느낌이라 온 건데...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 부자가 되었지만, 고급 레스토랑에서 어떤 맛있는 음식을 사 먹어도 이상하게 입안 가득 씁쓸한 파스 냄새가 감돕니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사가 돋보기를 잘 비춰준 덕에... 네놈의 혈자리 세 곳이 선명하게 보이는구나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘부로 사직서 제출합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인사팀장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캡틴물렁카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...미친?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Content</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Speaker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[프로젝트: 늙은 사자 / 초능력 추출 및 배터리 가공 매뉴얼]...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이봐, 샤워실 물 온도가 너무 차잖아! 허리가 하나도 안 지져져!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 문 손잡이 또 박살 내셨네요… 제 월급에서 또 까이겠군요…</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(매뉴얼까지 이렇게 대놓고 적혀있는데 모른 척할 수는 없지...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
   <x:si>
     <x:t>Quest_03_14</x:t>
   </x:si>
   <x:si>
+    <x:t>Quest_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B. 프로젝트요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeakerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네? 쥐, 쥐어짠다뇨…?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최선을 다해 케어하겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{PlayerName}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무장 요원 전원 투입! 저 반골 보조사 놈을 당장 제압해!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(지부장의 명령대로 어르신들을 바치고 내 보신을 챙길 것인가... 아니면 어르신들과 손을 잡고 이 조직을 엎어버릴 것인가...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사가 매일 달여준 총명탕 덕에 뇌세포가 맑아져서, 잊어버렸던 9클래스 메테오 주문이 다 생각났다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3일 차 보고서 잘 봤네. 근데 지출 내역에 '한방 총명탕 팩'이랑 '초강력 한방 파스 500장'은 뭔가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5일 차가 되면 지하 4층 추출 장치 전원이 켜질 테니, 어르신들 초능력이나 팍팍 추출할 준비나 하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(남은 시간은 단 이틀... 어르신들의 마음을 얻지 못하면, 내가 먼저 이 지하에 묻히게 될지도 모른다.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 어르신들한테 파스 붙여주고 총명탕 끓여준 게, 죄다 초능력 잘 뽑히라고 찜질 마사지해 준 거였다고?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상을 구했던 전설의 영웅들은 이제 기억과 능력을 완전히 잃은 채, 지하 냉동 창고에서 거대한 '초능력 배터리'로 영원히 잠들었습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어라... 지부장 너희들이 우리 보조사를 해고하고 지하 배터리로 만들려고 했다고?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>히, 히익?! 말도 안 돼! 분명 녹내장에 치매에 관절염 걸린 노인네들이었잖아!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 초능력 파편 덕분에 우리 조직은 세계 최고의 초능력 무기 상인이 되었다네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들 멘탈을 억지로라도 끌어올려서 '기억의 파편'을 쥐어짜 내야 하는 '재고 관리실'이라고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어서 오게, 김 보조사. 마침내 Day 7 최종 정산 및 초능력 추출 작업이 100% 완료되었네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...지부장님. 어르신들이 지하 4층 유리관 안에 갇혀 계시는데... 정말 괜찮으신 거 맞습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신의 파스와 총명탕, 그리고 따뜻한 케어가 있는 한 이곳은 세계에서 가장 안전하고 무적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네는 아주 훌륭한 사육사였어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들 민원이나 서사에 일일이 감정 이입하지 않고, 우리가 시키는 대로 '재고 확보'에만 집중해 준 덕분에 아주 깔끔하게 작업이 끝났지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자, 보게나. 자네가 일주일 동안 적당히 돌봐준 영웅들의 현재 상태라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나...? 메테오...? 그게 뭐야... 손끝이 그냥 둔탁한 돌멩이 같아... 이봐, 보조사... 나 집에 보내줘...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1단계: 영웅들의 만족도를 높여 초능력을 전성기 수준으로 복원한다.'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저희 실버타운 슬로건이 '사랑과 정성의 실버타운' 아니었습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 2단계: 지하 추출기로 마나를 쥐어짜 내어 거대 배터리로 가공, 암시장에 팔아치운다.'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 날 진심으로 대해준 사람이라면, 그 사람이 어떤 처지든 이 늙은이가 끝까지 편을 들어주지 않겠나? 허허.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장이 말한 지하 4층 특별 구역이 여길 말한 건가...? 먼지 냄새에... 기계 소리만 웅웅거리는데...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님. 어르신들이 관절염이랑 건망증 때문에 자꾸 복도에서 마법을 쏘셔서요. 파스라도 붙여드려야 조용해집니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쯧쯧… 자네, 착각하지 말게. 상부에서 매달 내려주는 지원금이 어르신들 찜질방이나 지어주라고 나오는 공짜 돈인 줄 아나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...결국 또 D 등급이군. 지난번 경고가 가벼웠던 모양이지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사... 오늘 온천 물이... 왜 이렇게 차가운가...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어이, 지부장 나부랭이! 누구 집 보조사를 제압하겠다는 거냐!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...어르신, 만약에 말이죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에구구... 여기서 혼자 뭐 하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거긴 단순한 시골 노인정이 아니야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일주일 동안 군말 없이 참 잘해줬어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 누군가 어르신들의 비밀을 전부 파헤쳐서 위험에 빠뜨리려고 하면...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참고로 자네 지난달 파스값, 실적 못 채우면 자네 월급에서 깐다. 수고하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(결국 모든 건 내가 어르신들과 얼마나 깊은 유대감을 쌓았느냐에 달려있어.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계 옆에 친절하게 [초능력 추출 중 - 접근 금지] 스티커까지 붙여놨잖아?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음... 글쎄다. 날 속이고 이용하려 한 놈이라면 메테오로 지져버리겠지만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탈인간 실버타운이 아니라 탈인간 배터리 공장이었어?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월급 200만 원에 블랙기업이라니… 퇴사하고 싶다…</x:t>
+  </x:si>
+  <x:si>
     <x:t>바로 온도 올려드릴게요, 제발 메테오만 쏘지 마세요...</x:t>
   </x:si>
   <x:si>
-    <x:t>어르신, 문 손잡이 또 박살 내셨네요… 제 월급에서 또 까이겠네…</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이봐, 샤워실 물 온도가 너무 차잖아! 허리가 하나도 안 지져져!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월급 200만 원에 블랙기업이라니… 퇴사하고 싶다…</x:t>
+    <x:t>그나저나 자네, 모니터 보고 얼굴이 왜 그렇게 흙빛인가?</x:t>
   </x:si>
   <x:si>
     <x:t>그건 외부에 사찰단 올 때 보여주는 위조 간판이고!</x:t>
   </x:si>
   <x:si>
-    <x:t>거긴 단순한 시골 노인정이 아니야!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네? 쥐, 쥐어짠다뇨…?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저희 실버타운 슬로건이 '사랑과 정성의 실버타운' 아니었습니까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인사팀장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Speaker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참고로 자네 지난달 파스값, 실적 못 채우면 자네 월급에서 깐다. 수고하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{PlayerName}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최선을 다해 케어하겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들 멘탈을 억지로라도 끌어올려서 '기억의 파편'을 쥐어짜 내야 하는 '재고 관리실'이라고!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3일 차 보고서 잘 봤네. 근데 지출 내역에 '한방 총명탕 팩'이랑 '초강력 한방 파스 500장'은 뭔가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...결국 또 D 등급이군. 지난번 경고가 가벼웠던 모양이지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B. 프로젝트요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeakerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_13</x:t>
+    <x:t>Prefabs/Character/NPC/Player</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으악! 캡틴물렁카 할아버지! 여긴 어떻게 내려오셨어요?!</x:t>
   </x:si>
   <x:si>
     <x:t>보안요원, 이 친구 짐 정리시키고 밖으로 던져버리게.</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Character/NPC/Player</x:t>
-  </x:si>
-  <x:si>
     <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
   </x:si>
   <x:si>
-    <x:t>쯧쯧… 자네, 착각하지 말게. 상부에서 매달 내려주는 지원금이 어르신들 찜질방이나 지어주라고 나오는 공짜 돈인 줄 아나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 지부장님. 어르신들이 관절염이랑 건망증 때문에 자꾸 복도에서 마법을 쏘셔서요. 파스라도 붙여드려야 조용해집니다.</x:t>
+    <x:t>바깥에서 입이라도 뻥끗하면 다음 추출 대상은 자네가 될 테니 명심하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅은 죽지 않는다. 그저 전력으로 소모될 뿐.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>규정은 규정이야. 자네한테 줄 기회 따위는 없어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 요양보조사 하나 교체하는 건 일도 아니지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
   </x:si>
   <x:si>
     <x:t>지, 지부장님! 한 번만 더 기회를 주십시오!</x:t>
   </x:si>
   <x:si>
-    <x:t>규정은 규정이야. 자네한테 줄 기회 따위는 없어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
+    <x:t>어? 제어판 모니터가 켜져 있네? 어디 보자...</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Character/NPC/Boss</x:t>
   </x:si>
   <x:si>
-    <x:t>말단 요양보조사 하나 교체하는 건 일도 아니지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
+    <x:t>어르신들은 그 사람을 용서하실 수 있겠습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장이라는 녀석이 또 야근 시켰나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
   </x:si>
   <x:si>
     <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
   </x:si>
   <x:si>
-    <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5일 차가 되면 지하 4층 추출 장치 전원이 켜질 테니, 어르신들 초능력이나 팍팍 추출할 준비나 하게.</x:t>
+    <x:t>보조사...? 글쎄... 잘 모르겠는데... 나한테 파스나 붙여주던 모르는 청년인가...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 몸은 늙었을지 몰라도, 그분들이 지켜온 정의와 옛 영광까지 늙은 건 아니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈앞이... 검은 안개밖에 안 보여... 보조사가 준 돋보기... 아무 소용이 없네...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흑막 조직은 완전히 소탕되었고, 비밀 지하 요양원은 영웅들의 진짜 안식처로 탈바꿈했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사! 이게 무슨 짓인가! 감히 지하 4층 추출 장치 전원을 끄고 메인 차단기를 내려?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그분들도 자네와 유대감이 없으니, 자네가 자신들을 구해줄 거라곤 전혀 기대조차 안 하더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허리가 안 아파... 아무 느낌도 안 들어... 내가... 원래 뭘 하던 사람이었지...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 블랙기업의 소모품 보조사에서, 이 위대한 실버타운의 정식 '원장'으로 추대되었습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비록 여전히 허리가 삐끗하고, 주문을 깜빡하고, 사물이 침침하게 보이는 어르신들이지만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저번에 본 매뉴얼에는 능력을 뽑아내면 기억까지 파괴된다고...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떻게 전성기보다 더 잘 싸우는 건데?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘도 '아무튼 탈인간 실버타운'의 하루는 평화롭습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가라, 메테오-!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원장님! 오늘 점심 총명탕 맞지? 빨리 끓여와~!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 7일간의 노고를 인정받아 두둑한 퇴직금을 받고 요양원에서 쫓겨났습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미친 소리! 고작 파스나 붙여주던 말단 보조사 주제에 눈에 뵈는 게 없구나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장님, 5일 차 때 그 친절한 매뉴얼이랑 포스트잇 보고 다 깨달았습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 지난 일주일 동안 어르신들을 그저 '실적용 소모품'으로 대하지 않았나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원장님! 할망구가 내 돋보기 또 숨겼어! 빨리 찾아서 파스랑 같이 가져와!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크하하! 우리 보조사가 일주일 내내 매일 내 허리를 완벽하게 지져줬거든!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비가 내리는 밤이면, 당신의 귓가에 멍한 목소리가 환청처럼 들려옵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파스와 총명탕, 그리고 사랑으로 케어한 '탈인간 실버타운' 어르신들을 무시하지 마라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장 녀석, 방탄유리 뒤로 숨어도 소용없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어, 어르신들...! 오즈 할아버지, 저에요! 매일 총명탕 달여드리던 보조사라고요! 저 기억 안 나세요?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소용없네, 보조사.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상을 구했던 그들, 이제는 우리의 일상을 구하다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무, 무슨?! 관절염 때문에 제대로 걷지도 못하던 늙은이가 어떻게 기계실 벽을 부수고 들어온 거지?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파스 값도 안 주고 월급에서 까겠다느니, '탈인간 배터리 공장'으로 어르신들 팔아넘기려던 블랙기업 따위!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허리 통증 완화 완충 상태다! 전설의 지면 강타 맛을 봐라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>약속했던 거액의 퇴직금 봉투일세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 웃으며 파스 상자를 들고 어르신들에게 달려갑니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_16</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -521,7 +995,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="21">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -574,6 +1051,12 @@
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1180,1019 +1663,2013 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:P50"/>
+  <x:dimension ref="A1:P128"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
-    <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
-    <x:col min="3" max="3" width="13.85546875" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="23.28515625" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="120" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="30.54296875" style="3" customWidth="1"/>
-    <x:col min="7" max="7" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="8" max="16384" width="12.54296875" style="3"/>
+    <x:col min="1" max="1" width="19.453125" style="4" customWidth="1"/>
+    <x:col min="2" max="2" width="19.54296875" style="4" customWidth="1"/>
+    <x:col min="3" max="3" width="13.85546875" style="4" customWidth="1"/>
+    <x:col min="4" max="4" width="23.28515625" style="4" customWidth="1"/>
+    <x:col min="5" max="5" width="120" style="4" customWidth="1"/>
+    <x:col min="6" max="6" width="30.54296875" style="4" customWidth="1"/>
+    <x:col min="7" max="7" width="26.54296875" style="4" customWidth="1"/>
+    <x:col min="8" max="16384" width="12.54296875" style="4"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" ht="13.199999999999999">
+      <x:c r="A2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H2" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="10" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A4" s="5" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G4" s="14"/>
+      <x:c r="H4" s="6"/>
+      <x:c r="I4" s="6"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
+      <x:c r="L4" s="6"/>
+      <x:c r="M4" s="6"/>
+      <x:c r="N4" s="6"/>
+      <x:c r="O4" s="6"/>
+      <x:c r="P4" s="6"/>
+    </x:row>
+    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A5" s="5" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G5" s="14"/>
+      <x:c r="H5" s="6"/>
+      <x:c r="I5" s="6"/>
+      <x:c r="J5" s="6"/>
+      <x:c r="K5" s="6"/>
+      <x:c r="L5" s="6"/>
+      <x:c r="M5" s="6"/>
+      <x:c r="N5" s="6"/>
+      <x:c r="O5" s="6"/>
+      <x:c r="P5" s="6"/>
+    </x:row>
+    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A6" s="7" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G6" s="6"/>
+      <x:c r="H6" s="6"/>
+      <x:c r="I6" s="6"/>
+      <x:c r="J6" s="6"/>
+      <x:c r="K6" s="6"/>
+      <x:c r="L6" s="6"/>
+      <x:c r="M6" s="6"/>
+      <x:c r="N6" s="6"/>
+      <x:c r="O6" s="6"/>
+      <x:c r="P6" s="6"/>
+    </x:row>
+    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A7" s="7" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D7" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G7" s="6"/>
+      <x:c r="H7" s="6"/>
+      <x:c r="I7" s="6"/>
+      <x:c r="J7" s="6"/>
+      <x:c r="K7" s="6"/>
+      <x:c r="L7" s="6"/>
+      <x:c r="M7" s="6"/>
+      <x:c r="N7" s="6"/>
+      <x:c r="O7" s="6"/>
+      <x:c r="P7" s="6"/>
+    </x:row>
+    <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A8" s="7" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G8" s="6"/>
+      <x:c r="H8" s="6"/>
+      <x:c r="I8" s="6"/>
+      <x:c r="J8" s="6"/>
+      <x:c r="K8" s="6"/>
+      <x:c r="L8" s="6"/>
+      <x:c r="M8" s="6"/>
+      <x:c r="N8" s="6"/>
+      <x:c r="O8" s="6"/>
+      <x:c r="P8" s="6"/>
+    </x:row>
+    <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A9" s="7" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G9" s="6"/>
+      <x:c r="H9" s="6"/>
+      <x:c r="I9" s="6"/>
+      <x:c r="J9" s="6"/>
+      <x:c r="K9" s="6"/>
+      <x:c r="L9" s="6"/>
+      <x:c r="M9" s="6"/>
+      <x:c r="N9" s="6"/>
+      <x:c r="O9" s="6"/>
+      <x:c r="P9" s="6"/>
+    </x:row>
+    <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A10" s="7" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G10" s="6"/>
+      <x:c r="H10" s="6"/>
+      <x:c r="I10" s="6"/>
+      <x:c r="J10" s="6"/>
+      <x:c r="K10" s="6"/>
+      <x:c r="L10" s="6"/>
+      <x:c r="M10" s="6"/>
+      <x:c r="N10" s="6"/>
+      <x:c r="O10" s="6"/>
+      <x:c r="P10" s="6"/>
+    </x:row>
+    <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A11" s="7" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G11" s="6"/>
+      <x:c r="H11" s="6"/>
+      <x:c r="I11" s="6"/>
+      <x:c r="J11" s="6"/>
+      <x:c r="K11" s="6"/>
+      <x:c r="L11" s="6"/>
+      <x:c r="M11" s="6"/>
+      <x:c r="N11" s="6"/>
+      <x:c r="O11" s="6"/>
+      <x:c r="P11" s="6"/>
+    </x:row>
+    <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A12" s="7" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B12" s="5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C12" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G12" s="6"/>
+      <x:c r="H12" s="6"/>
+      <x:c r="I12" s="6"/>
+      <x:c r="J12" s="6"/>
+      <x:c r="K12" s="6"/>
+      <x:c r="L12" s="6"/>
+      <x:c r="M12" s="6"/>
+      <x:c r="N12" s="6"/>
+      <x:c r="O12" s="6"/>
+      <x:c r="P12" s="6"/>
+    </x:row>
+    <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A13" s="7" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B13" s="5" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C13" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D13" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G13" s="6"/>
+      <x:c r="H13" s="6"/>
+      <x:c r="I13" s="6"/>
+      <x:c r="J13" s="6"/>
+      <x:c r="K13" s="6"/>
+      <x:c r="L13" s="6"/>
+      <x:c r="M13" s="6"/>
+      <x:c r="N13" s="6"/>
+      <x:c r="O13" s="6"/>
+      <x:c r="P13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A14" s="7" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B14" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C14" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G14" s="6"/>
+      <x:c r="H14" s="6"/>
+      <x:c r="I14" s="6"/>
+      <x:c r="J14" s="6"/>
+      <x:c r="K14" s="6"/>
+      <x:c r="L14" s="6"/>
+      <x:c r="M14" s="6"/>
+      <x:c r="N14" s="6"/>
+      <x:c r="O14" s="6"/>
+      <x:c r="P14" s="6"/>
+    </x:row>
+    <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A15" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B15" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G15" s="6"/>
+      <x:c r="H15" s="6"/>
+      <x:c r="I15" s="6"/>
+      <x:c r="J15" s="6"/>
+      <x:c r="K15" s="6"/>
+      <x:c r="L15" s="6"/>
+      <x:c r="M15" s="6"/>
+      <x:c r="N15" s="6"/>
+      <x:c r="O15" s="6"/>
+      <x:c r="P15" s="6"/>
+    </x:row>
+    <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A16" s="7" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B16" s="5" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A17" s="7" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B17" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C17" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A18" s="7" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B18" s="5" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D18" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E18" s="6" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A19" s="7" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B19" s="5" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C19" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A20" s="7" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B20" s="5" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A21" s="7" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B21" s="5" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D21" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E21" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A22" s="7" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B22" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C22" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D22" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E22" s="6" t="s">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A23" s="7" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B23" s="5" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C23" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A24" s="7" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B24" s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A25" s="8" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D25" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E25" s="18" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G25" s="4" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A26" s="8" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B26" s="8" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C26" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E26" s="18" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F26" s="6"/>
+    </x:row>
+    <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A27" s="8" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B27" s="8" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D27" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F27" s="6"/>
+    </x:row>
+    <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A28" s="8" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B28" s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E28" s="18" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F28" s="6"/>
+    </x:row>
+    <x:row r="29" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A29" s="8" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B29" s="8" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C29" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D29" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G29" s="4" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A30" s="8" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B30" s="8" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C30" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E30" s="18" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F30" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A31" s="8" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B31" s="8" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C31" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E31" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A32" s="8" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B32" s="8" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C32" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D32" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E32" s="18" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A33" s="8" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B33" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C33" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D33" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E33" s="18" t="s">
+        <x:v>207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A34" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B34" s="8" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C34" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D34" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A35" s="8" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B35" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C35" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E35" s="18" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A36" s="8" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B36" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E36" s="18" t="s">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A37" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C37" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D37" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A38" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B38" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C38" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D38" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E38" s="4" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A39" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C39" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D39" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A40" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B40" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C40" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D40" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E40" s="18" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A41" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B41" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C41" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D41" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E41" s="4" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A42" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B42" s="4" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C42" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D42" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E42" s="4" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A43" s="4" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B43" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C43" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D43" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E43" s="4" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A44" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B44" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C44" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D44" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E44" s="4" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A45" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B45" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C45" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D45" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E45" s="18" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A46" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B46" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C46" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D46" s="5" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E46" s="4" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A47" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B47" s="4" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C47" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D47" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E47" s="4" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A48" s="4" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B48" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C48" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D48" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E48" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A49" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B49" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C49" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D49" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E49" s="4" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
+    </x:row>
+    <x:row r="50" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A50" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B50" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C50" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D50" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E50" s="4" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A51" s="4" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B51" s="4" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C51" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D51" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E51" s="18" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A52" s="4" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B52" s="4" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C52" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D52" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E52" s="18" t="s">
+        <x:v>210</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A53" s="4" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B53" s="4" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C53" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D53" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E53" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A54" s="4" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B54" s="4" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D54" s="7"/>
+      <x:c r="E54" s="20" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A55" s="4" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B55" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E55" s="19" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A56" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B56" s="4" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C56" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D56" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E56" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A57" s="4" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B57" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C57" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D57" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E57" s="18" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A58" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B58" s="4" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C58" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D58" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E58" s="4" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A59" s="4" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B59" s="4" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C59" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D59" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E59" s="18" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A60" s="4" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B60" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C60" s="5" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="D60" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E60" s="18" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A61" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B61" s="4" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C61" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D61" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E61" s="18" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A62" s="4" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B62" s="4" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C62" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D62" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E62" s="18" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A63" s="4" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B63" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C63" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D63" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E63" s="18" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A64" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B64" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C64" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D64" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E64" s="4" t="s">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A65" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B65" s="4" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C65" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D65" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E65" s="18" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A66" s="4" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B66" s="4" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C66" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D66" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E66" s="4" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A67" s="4" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B67" s="4" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C67" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D67" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E67" s="4" t="s">
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A68" s="4" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B68" s="4" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C68" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D68" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E68" s="18" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A69" s="4" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B69" s="4" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C69" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D69" s="7" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E69" s="18" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A70" s="4" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B70" s="4" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C70" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D70" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E70" s="18" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H2" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B3" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D3" s="9" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E3" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F3" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H3" s="10" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G4" s="13"/>
-      <x:c r="H4" s="5"/>
-      <x:c r="I4" s="5"/>
-      <x:c r="J4" s="5"/>
-      <x:c r="K4" s="5"/>
-      <x:c r="L4" s="5"/>
-      <x:c r="M4" s="5"/>
-      <x:c r="N4" s="5"/>
-      <x:c r="O4" s="5"/>
-      <x:c r="P4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A5" s="4" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G5" s="13"/>
-      <x:c r="H5" s="5"/>
-      <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5"/>
-      <x:c r="K5" s="5"/>
-      <x:c r="L5" s="5"/>
-      <x:c r="M5" s="5"/>
-      <x:c r="N5" s="5"/>
-      <x:c r="O5" s="5"/>
-      <x:c r="P5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A6" s="6" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E6" s="5" t="s">
+    </x:row>
+    <x:row r="71" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A71" s="4" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B71" s="4" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C71" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D71" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E71" s="18" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A72" s="4" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B72" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C72" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D72" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E72" s="18" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A73" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B73" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C73" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D73" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="E73" s="18" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A74" s="4" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B74" s="4" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E74" s="18" t="s">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A75" s="4" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B75" s="4" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E75" s="18" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A76" s="4" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B76" s="4" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E76" s="4" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A77" s="4" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B77" s="4" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E77" s="18" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A78" s="4" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B78" s="4" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E78" s="4" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A79" s="4" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B79" s="4" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="E79" s="18" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A80" s="4" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B80" s="4" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E80" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A81" s="4" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B81" s="4" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E81" s="18" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A82" s="4" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B82" s="4" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E82" s="18" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A83" s="4" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B83" s="4" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E83" s="18" t="s">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A84" s="4" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B84" s="4" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E84" s="18" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A85" s="4" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B85" s="4" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="E85" s="18" t="s">
+        <x:v>247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A86" s="4" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B86" s="4" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E86" s="18" t="s">
+        <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A87" s="4" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B87" s="4" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E87" s="18" t="s">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A88" s="4" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B88" s="4" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E88" s="4" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A89" s="4" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B89" s="4" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E89" s="4" t="s">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A90" s="4" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B90" s="4" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E90" s="18" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A91" s="4" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B91" s="4" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E91" s="4" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A92" s="4" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B92" s="4" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E92" s="18" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A93" s="4" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B93" s="4" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E93" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A94" s="4" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B94" s="4" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E94" s="4" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A95" s="4" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B95" s="4" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E95" s="18" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A96" s="4" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B96" s="4" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="E96" s="18" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A97" s="4" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B97" s="4" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E97" s="4" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A98" s="4" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B98" s="4" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="G6" s="5"/>
-      <x:c r="H6" s="5"/>
-      <x:c r="I6" s="5"/>
-      <x:c r="J6" s="5"/>
-      <x:c r="K6" s="5"/>
-      <x:c r="L6" s="5"/>
-      <x:c r="M6" s="5"/>
-      <x:c r="N6" s="5"/>
-      <x:c r="O6" s="5"/>
-      <x:c r="P6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A7" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E7" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G7" s="5"/>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="5"/>
-      <x:c r="J7" s="5"/>
-      <x:c r="K7" s="5"/>
-      <x:c r="L7" s="5"/>
-      <x:c r="M7" s="5"/>
-      <x:c r="N7" s="5"/>
-      <x:c r="O7" s="5"/>
-      <x:c r="P7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A8" s="6" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B8" s="4" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C8" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G8" s="5"/>
-      <x:c r="H8" s="5"/>
-      <x:c r="I8" s="5"/>
-      <x:c r="J8" s="5"/>
-      <x:c r="K8" s="5"/>
-      <x:c r="L8" s="5"/>
-      <x:c r="M8" s="5"/>
-      <x:c r="N8" s="5"/>
-      <x:c r="O8" s="5"/>
-      <x:c r="P8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B9" s="4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C9" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E9" s="5" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G9" s="5"/>
-      <x:c r="H9" s="5"/>
-      <x:c r="I9" s="5"/>
-      <x:c r="J9" s="5"/>
-      <x:c r="K9" s="5"/>
-      <x:c r="L9" s="5"/>
-      <x:c r="M9" s="5"/>
-      <x:c r="N9" s="5"/>
-      <x:c r="O9" s="5"/>
-      <x:c r="P9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A10" s="6" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B10" s="4" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C10" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E10" s="5" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G10" s="5"/>
-      <x:c r="H10" s="5"/>
-      <x:c r="I10" s="5"/>
-      <x:c r="J10" s="5"/>
-      <x:c r="K10" s="5"/>
-      <x:c r="L10" s="5"/>
-      <x:c r="M10" s="5"/>
-      <x:c r="N10" s="5"/>
-      <x:c r="O10" s="5"/>
-      <x:c r="P10" s="5"/>
-    </x:row>
-    <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A11" s="6" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B11" s="4" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G11" s="5"/>
-      <x:c r="H11" s="5"/>
-      <x:c r="I11" s="5"/>
-      <x:c r="J11" s="5"/>
-      <x:c r="K11" s="5"/>
-      <x:c r="L11" s="5"/>
-      <x:c r="M11" s="5"/>
-      <x:c r="N11" s="5"/>
-      <x:c r="O11" s="5"/>
-      <x:c r="P11" s="5"/>
-    </x:row>
-    <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B12" s="4" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C12" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G12" s="5"/>
-      <x:c r="H12" s="5"/>
-      <x:c r="I12" s="5"/>
-      <x:c r="J12" s="5"/>
-      <x:c r="K12" s="5"/>
-      <x:c r="L12" s="5"/>
-      <x:c r="M12" s="5"/>
-      <x:c r="N12" s="5"/>
-      <x:c r="O12" s="5"/>
-      <x:c r="P12" s="5"/>
-    </x:row>
-    <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A13" s="6" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B13" s="4" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C13" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E13" s="5" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G13" s="5"/>
-      <x:c r="H13" s="5"/>
-      <x:c r="I13" s="5"/>
-      <x:c r="J13" s="5"/>
-      <x:c r="K13" s="5"/>
-      <x:c r="L13" s="5"/>
-      <x:c r="M13" s="5"/>
-      <x:c r="N13" s="5"/>
-      <x:c r="O13" s="5"/>
-      <x:c r="P13" s="5"/>
-    </x:row>
-    <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A14" s="6" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B14" s="4" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C14" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E14" s="5" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G14" s="5"/>
-      <x:c r="H14" s="5"/>
-      <x:c r="I14" s="5"/>
-      <x:c r="J14" s="5"/>
-      <x:c r="K14" s="5"/>
-      <x:c r="L14" s="5"/>
-      <x:c r="M14" s="5"/>
-      <x:c r="N14" s="5"/>
-      <x:c r="O14" s="5"/>
-      <x:c r="P14" s="5"/>
-    </x:row>
-    <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A15" s="6" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B15" s="4" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="E98" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A99" s="4" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B99" s="4" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="E99" s="4" t="s">
+        <x:v>243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A100" s="4" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B100" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E100" s="4" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A101" s="4" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B101" s="4" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E101" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A102" s="4" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B102" s="4" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="E102" s="4" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A103" s="4" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B103" s="4" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="E103" s="18" t="s">
+        <x:v>251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A104" s="4" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B104" s="4" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="E104" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A105" s="4" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B105" s="4" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="E105" s="18" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A106" s="4" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B106" s="4" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="E106" s="4" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="G15" s="5"/>
-      <x:c r="H15" s="5"/>
-      <x:c r="I15" s="5"/>
-      <x:c r="J15" s="5"/>
-      <x:c r="K15" s="5"/>
-      <x:c r="L15" s="5"/>
-      <x:c r="M15" s="5"/>
-      <x:c r="N15" s="5"/>
-      <x:c r="O15" s="5"/>
-      <x:c r="P15" s="5"/>
-    </x:row>
-    <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A16" s="6" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B16" s="4" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C16" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D16" s="6" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E16" s="5" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A17" s="6" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B17" s="4" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C17" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A18" s="6" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B18" s="4" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C18" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D18" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E18" s="5" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="6" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B19" s="4" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C19" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A20" s="6" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B20" s="4" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C20" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A21" s="6" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B21" s="4" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C21" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D21" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E21" s="5" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A22" s="6" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B22" s="4" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C22" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D22" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E22" s="5" t="s">
+    </x:row>
+    <x:row r="107" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A107" s="4" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="B107" s="4" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="E107" s="18" t="s">
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A108" s="4" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B108" s="4" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="E108" s="18" t="s">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A109" s="4" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B109" s="4" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="E109" s="18" t="s">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A110" s="4" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B110" s="4" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="E110" s="4" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A111" s="4" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B111" s="4" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="E111" s="18" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A112" s="4" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B112" s="4" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="E112" s="18" t="s">
         <x:v>114</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A23" s="6" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B23" s="4" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C23" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A24" s="6" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B24" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D24" s="6" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E24" s="5" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A25" s="7" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B25" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C25" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D25" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F25" s="3" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G25" s="3" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A26" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B26" s="7" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C26" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D26" s="6" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E26" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F26" s="5"/>
-    </x:row>
-    <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A27" s="7" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B27" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C27" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D27" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E27" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F27" s="5"/>
-    </x:row>
-    <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A28" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B28" s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D28" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E28" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F28" s="5"/>
-    </x:row>
-    <x:row r="29" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A29" s="7" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B29" s="7" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C29" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D29" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E29" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G29" s="3" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A30" s="7" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B30" s="7" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C30" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D30" s="6" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E30" s="17" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F30" s="3" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A31" s="7" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B31" s="7" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C31" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D31" s="6" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E31" s="3" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A32" s="7" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B32" s="7" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C32" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D32" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E32" s="17" t="s">
-        <x:v>109</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A33" s="7" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B33" s="7" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C33" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D33" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E33" s="17" t="s">
-        <x:v>112</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A34" s="7" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B34" s="7" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C34" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D34" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E34" s="3" t="s">
-        <x:v>103</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A35" s="7" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B35" s="7" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C35" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D35" s="6" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E35" s="17" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A36" s="7" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B36" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E36" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A37" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B37" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E37" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A38" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B38" s="3" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E38" s="3" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A39" s="3" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B39" s="3" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E39" s="3" t="s">
-        <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A40" s="3" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B40" s="3" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E40" s="17" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A41" s="3" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B41" s="3" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E41" s="3" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A42" s="3" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B42" s="3" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E42" s="3" t="s">
+    <x:row r="113" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A113" s="4" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B113" s="4" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="E113" s="4" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A114" s="4" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B114" s="4" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="E114" s="4" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A115" s="4" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B115" s="4" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E115" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A116" s="4" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B116" s="4" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="E116" s="18" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A117" s="4" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B117" s="4" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="E117" s="4" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A118" s="4" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B118" s="4" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="E118" s="18" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A119" s="4" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B119" s="4" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="E119" s="18" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A120" s="4" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B120" s="4" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="E120" s="18" t="s">
+        <x:v>249</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A121" s="4" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="B121" s="4" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E121" s="18" t="s">
+        <x:v>219</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A122" s="4" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B122" s="4" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="E122" s="4" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A123" s="4" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B123" s="4" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="E123" s="4" t="s">
+        <x:v>224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A124" s="4" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B124" s="4" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="E124" s="4" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A125" s="4" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B125" s="4" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="E125" s="4" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A126" s="4" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B126" s="4" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="E126" s="4" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A127" s="4" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B127" s="4" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="E127" s="4" t="s">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A128" s="4" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B128" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
-    </x:row>
-    <x:row r="43" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A43" s="3" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B43" s="3" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E43" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A44" s="3" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B44" s="3" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E44" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A45" s="3" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B45" s="3" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E45" s="17" t="s">
-        <x:v>116</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A46" s="3" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B46" s="3" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E46" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A47" s="3" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B47" s="3" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E47" s="3" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A48" s="3" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B48" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E48" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A49" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B49" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E49" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A50" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E50" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="15.75" customHeight="1"/>
-    <x:row r="52" ht="15.75" customHeight="1"/>
-    <x:row r="53" ht="15.75" customHeight="1"/>
-    <x:row r="54" ht="15.75" customHeight="1"/>
-    <x:row r="55" ht="15.75" customHeight="1"/>
-    <x:row r="56" ht="15.75" customHeight="1"/>
-    <x:row r="57" ht="15.75" customHeight="1"/>
-    <x:row r="58" ht="15.75" customHeight="1"/>
-    <x:row r="59" ht="15.75" customHeight="1"/>
-    <x:row r="60" ht="15.75" customHeight="1"/>
-    <x:row r="61" ht="15.75" customHeight="1"/>
-    <x:row r="62" ht="15.75" customHeight="1"/>
-    <x:row r="63" ht="15.75" customHeight="1"/>
-    <x:row r="64" ht="15.75" customHeight="1"/>
-    <x:row r="65" ht="15.75" customHeight="1"/>
-    <x:row r="66" ht="15.75" customHeight="1"/>
-    <x:row r="67" ht="15.75" customHeight="1"/>
-    <x:row r="68" ht="15.75" customHeight="1"/>
-    <x:row r="69" ht="15.75" customHeight="1"/>
-    <x:row r="70" ht="15.75" customHeight="1"/>
-    <x:row r="71" ht="15.75" customHeight="1"/>
-    <x:row r="72" ht="15.75" customHeight="1"/>
-    <x:row r="73" ht="15.75" customHeight="1"/>
-    <x:row r="74" ht="15.75" customHeight="1"/>
-    <x:row r="75" ht="15.75" customHeight="1"/>
-    <x:row r="76" ht="15.75" customHeight="1"/>
-    <x:row r="77" ht="15.75" customHeight="1"/>
-    <x:row r="78" ht="15.75" customHeight="1"/>
-    <x:row r="79" ht="15.75" customHeight="1"/>
-    <x:row r="80" ht="15.75" customHeight="1"/>
-    <x:row r="81" ht="15.75" customHeight="1"/>
-    <x:row r="82" ht="15.75" customHeight="1"/>
-    <x:row r="83" ht="15.75" customHeight="1"/>
-    <x:row r="84" ht="15.75" customHeight="1"/>
-    <x:row r="85" ht="15.75" customHeight="1"/>
-    <x:row r="86" ht="15.75" customHeight="1"/>
-    <x:row r="87" ht="15.75" customHeight="1"/>
-    <x:row r="88" ht="15.75" customHeight="1"/>
-    <x:row r="89" ht="15.75" customHeight="1"/>
-    <x:row r="90" ht="15.75" customHeight="1"/>
-    <x:row r="91" ht="15.75" customHeight="1"/>
-    <x:row r="92" ht="15.75" customHeight="1"/>
-    <x:row r="93" ht="15.75" customHeight="1"/>
-    <x:row r="94" ht="15.75" customHeight="1"/>
-    <x:row r="95" ht="15.75" customHeight="1"/>
-    <x:row r="96" ht="15.75" customHeight="1"/>
-    <x:row r="97" ht="15.75" customHeight="1"/>
-    <x:row r="98" ht="15.75" customHeight="1"/>
-    <x:row r="99" ht="15.75" customHeight="1"/>
-    <x:row r="100" ht="15.75" customHeight="1"/>
-    <x:row r="101" ht="15.75" customHeight="1"/>
-    <x:row r="102" ht="15.75" customHeight="1"/>
-    <x:row r="103" ht="15.75" customHeight="1"/>
-    <x:row r="104" ht="15.75" customHeight="1"/>
-    <x:row r="105" ht="15.75" customHeight="1"/>
-    <x:row r="106" ht="15.75" customHeight="1"/>
-    <x:row r="107" ht="15.75" customHeight="1"/>
-    <x:row r="108" ht="15.75" customHeight="1"/>
-    <x:row r="109" ht="15.75" customHeight="1"/>
-    <x:row r="110" ht="15.75" customHeight="1"/>
-    <x:row r="111" ht="15.75" customHeight="1"/>
-    <x:row r="112" ht="15.75" customHeight="1"/>
-    <x:row r="113" ht="15.75" customHeight="1"/>
-    <x:row r="114" ht="15.75" customHeight="1"/>
-    <x:row r="115" ht="15.75" customHeight="1"/>
-    <x:row r="116" ht="15.75" customHeight="1"/>
-    <x:row r="117" ht="15.75" customHeight="1"/>
-    <x:row r="118" ht="15.75" customHeight="1"/>
-    <x:row r="119" ht="15.75" customHeight="1"/>
-    <x:row r="120" ht="15.75" customHeight="1"/>
-    <x:row r="121" ht="15.75" customHeight="1"/>
-    <x:row r="122" ht="15.75" customHeight="1"/>
-    <x:row r="123" ht="15.75" customHeight="1"/>
-    <x:row r="124" ht="15.75" customHeight="1"/>
-    <x:row r="125" ht="15.75" customHeight="1"/>
-    <x:row r="126" ht="15.75" customHeight="1"/>
-    <x:row r="127" ht="15.75" customHeight="1"/>
-    <x:row r="128" ht="15.75" customHeight="1"/>
+      <x:c r="E128" s="4" t="s">
+        <x:v>228</x:v>
+      </x:c>
+    </x:row>
     <x:row r="129" ht="15.75" customHeight="1"/>
     <x:row r="130" ht="15.75" customHeight="1"/>
     <x:row r="131" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -19,7 +19,244 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="280">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="284">
+  <x:si>
+    <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사가 돋보기를 잘 비춰준 덕에... 네놈의 혈자리 세 곳이 선명하게 보이는구나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어라... 지부장 너희들이 우리 보조사를 해고하고 지하 배터리로 만들려고 했다고?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 초능력 파편 덕분에 우리 조직은 세계 최고의 초능력 무기 상인이 되었다네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파스와 총명탕, 그리고 사랑으로 케어한 '탈인간 실버타운' 어르신들을 무시하지 마라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>히, 히익?! 말도 안 돼! 분명 녹내장에 치매에 관절염 걸린 노인네들이었잖아!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무장 요원 전원 투입! 저 반골 보조사 놈을 당장 제압해!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저번에 본 매뉴얼에는 능력을 뽑아내면 기억까지 파괴된다고...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허리 통증 완화 완충 상태다! 전설의 지면 강타 맛을 봐라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사가 매일 달여준 총명탕 덕에 뇌세포가 맑아져서, 잊어버렸던 9클래스 메테오 주문이 다 생각났다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5일 차가 되면 지하 4층 추출 장치 전원이 켜질 테니, 어르신들 초능력이나 팍팍 추출할 준비나 하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어, 어르신들...! 오즈 할아버지, 저에요! 매일 총명탕 달여드리던 보조사라고요! 저 기억 안 나세요?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3일 차 보고서 잘 봤네. 근데 지출 내역에 '한방 총명탕 팩'이랑 '초강력 한방 파스 500장'은 뭔가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파스 값도 안 주고 월급에서 까겠다느니, '탈인간 배터리 공장'으로 어르신들 팔아넘기려던 블랙기업 따위!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무, 무슨?! 관절염 때문에 제대로 걷지도 못하던 늙은이가 어떻게 기계실 벽을 부수고 들어온 거지?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 어르신들한테 파스 붙여주고 총명탕 끓여준 게, 죄다 초능력 잘 뽑히라고 찜질 마사지해 준 거였다고?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(남은 시간은 단 이틀... 어르신들의 마음을 얻지 못하면, 내가 먼저 이 지하에 묻히게 될지도 모른다.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상을 구했던 전설의 영웅들은 이제 기억과 능력을 완전히 잃은 채, 지하 냉동 창고에서 거대한 '초능력 배터리'로 영원히 잠들었습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들 멘탈을 억지로라도 끌어올려서 '기억의 파편'을 쥐어짜 내야 하는 '재고 관리실'이라고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...지부장님. 어르신들이 지하 4층 유리관 안에 갇혀 계시는데... 정말 괜찮으신 거 맞습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어서 오게, 김 보조사. 마침내 Day 7 최종 정산 및 초능력 추출 작업이 100% 완료되었네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신의 파스와 총명탕, 그리고 따뜻한 케어가 있는 한 이곳은 세계에서 가장 안전하고 무적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사! 이게 무슨 짓인가! 감히 지하 4층 추출 장치 전원을 끄고 메인 차단기를 내려?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 블랙기업의 소모품 보조사에서, 이 위대한 실버타운의 정식 '원장'으로 추대되었습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흑막 조직은 완전히 소탕되었고, 비밀 지하 요양원은 영웅들의 진짜 안식처로 탈바꿈했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허리가 안 아파... 아무 느낌도 안 들어... 내가... 원래 뭘 하던 사람이었지...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 2단계: 지하 추출기로 마나를 쥐어짜 내어 거대 배터리로 가공, 암시장에 팔아치운다.'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비록 여전히 허리가 삐끗하고, 주문을 깜빡하고, 사물이 침침하게 보이는 어르신들이지만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 몸은 늙었을지 몰라도, 그분들이 지켜온 정의와 옛 영광까지 늙은 건 아니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그분들도 자네와 유대감이 없으니, 자네가 자신들을 구해줄 거라곤 전혀 기대조차 안 하더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사...? 글쎄... 잘 모르겠는데... 나한테 파스나 붙여주던 모르는 청년인가...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈앞이... 검은 안개밖에 안 보여... 보조사가 준 돋보기... 아무 소용이 없네...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비가 내리는 밤이면, 당신의 귓가에 멍한 목소리가 환청처럼 들려옵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이봐, 샤워실 물 온도가 너무 차잖아! 허리가 하나도 안 지져져!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 문 손잡이 또 박살 내셨네요… 제 월급에서 또 까이겠군요…</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바깥에서 입이라도 뻥끗하면 다음 추출 대상은 자네가 될 테니 명심하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1단계: 영웅들의 만족도를 높여 초능력을 전성기 수준으로 복원한다.'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[프로젝트: 늙은 사자 / 초능력 추출 및 배터리 가공 매뉴얼]...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(매뉴얼까지 이렇게 대놓고 적혀있는데 모른 척할 수는 없지...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 부자가 되었지만, 고급 레스토랑에서 어떤 맛있는 음식을 사 먹어도 이상하게 입안 가득 씁쓸한 파스 냄새가 감돕니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(지부장의 명령대로 어르신들을 바치고 내 보신을 챙길 것인가... 아니면 어르신들과 손을 잡고 이 조직을 엎어버릴 것인가...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니... 왠지 이 기계 앞에만 오면 머리가 핑 돌고, 옛날에 마왕 잡을 때 쓰던 메테오 마나가 쪽쪽 빨려 나가는 느낌이라 온 건데...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들 민원이나 서사에 일일이 감정 이입하지 않고, 우리가 시키는 대로 '재고 확보'에만 집중해 준 덕분에 아주 깔끔하게 작업이 끝났지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님. 어르신들이 관절염이랑 건망증 때문에 자꾸 복도에서 마법을 쏘셔서요. 파스라도 붙여드려야 조용해집니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나...? 메테오...? 그게 뭐야... 손끝이 그냥 둔탁한 돌멩이 같아... 이봐, 보조사... 나 집에 보내줘...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쯧쯧… 자네, 착각하지 말게. 상부에서 매달 내려주는 지원금이 어르신들 찜질방이나 지어주라고 나오는 공짜 돈인 줄 아나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 날 진심으로 대해준 사람이라면, 그 사람이 어떤 처지든 이 늙은이가 끝까지 편을 들어주지 않겠나? 허허.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장이 말한 지하 4층 특별 구역이 여길 말한 건가...? 먼지 냄새에... 기계 소리만 웅웅거리는데...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원장님! 할망구가 내 돋보기 또 숨겼어! 빨리 찾아서 파스랑 같이 가져와!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 지난 일주일 동안 어르신들을 그저 '실적용 소모품'으로 대하지 않았나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자, 보게나. 자네가 일주일 동안 적당히 돌봐준 영웅들의 현재 상태라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음... 글쎄다. 날 속이고 이용하려 한 놈이라면 메테오로 지져버리겠지만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크하하! 우리 보조사가 일주일 내내 매일 내 허리를 완벽하게 지져줬거든!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 누군가 어르신들의 비밀을 전부 파헤쳐서 위험에 빠뜨리려고 하면...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(결국 모든 건 내가 어르신들과 얼마나 깊은 유대감을 쌓았느냐에 달려있어.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계 옆에 친절하게 [초능력 추출 중 - 접근 금지] 스티커까지 붙여놨잖아?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장님, 5일 차 때 그 친절한 매뉴얼이랑 포스트잇 보고 다 깨달았습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 7일간의 노고를 인정받아 두둑한 퇴직금을 받고 요양원에서 쫓겨났습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미친 소리! 고작 파스나 붙여주던 말단 보조사 주제에 눈에 뵈는 게 없구나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참고로 자네 지난달 파스값, 실적 못 채우면 자네 월급에서 깐다. 수고하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
+  </x:si>
   <x:si>
     <x:t>하하! 자네는 그 매뉴얼 다 보고서도 아직 순진한 소리를 하나?</x:t>
   </x:si>
@@ -27,838 +264,613 @@
     <x:t>...결국 또 D 등급이군. 지난번 경고가 가벼웠던 모양이지?</x:t>
   </x:si>
   <x:si>
-    <x:t>저번에 본 매뉴얼에는 능력을 뽑아내면 기억까지 파괴된다고...</x:t>
+    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어이, 지부장 나부랭이! 누구 집 보조사를 제압하겠다는 거냐!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저희 실버타운 슬로건이 '사랑과 정성의 실버타운' 아니었습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사... 오늘 온천 물이... 왜 이렇게 차가운가...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소용없네, 보조사.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그건 외부에 사찰단 올 때 보여주는 위조 간판이고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으악! 캡틴물렁카 할아버지! 여긴 어떻게 내려오셨어요?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상을 구했던 그들, 이제는 우리의 일상을 구하다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그나저나 자네, 모니터 보고 얼굴이 왜 그렇게 흙빛인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바로 온도 올려드릴게요. 제발 메테오만 쏘지 마세요...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보안요원, 이 친구 짐 정리시키고 밖으로 던져버리게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초능력이 뿌리째 뽑혀 나가는데 사람이 멀쩡할 리가 있나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월급 200만 원에 블랙기업이라니… 퇴사하고 싶다…</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘도 '아무튼 탈인간 실버타운'의 하루는 평화롭습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/NPC/Player</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 보안요원! 이 친구 짐 챙겨서 정문 밖으로 던져버리게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 웃으며 파스 상자를 들고 어르신들에게 달려갑니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탈인간 실버타운이 아니라 탈인간 배터리 공장이었어?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가라, 메테오-!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main1</x:t>
   </x:si>
   <x:si>
     <x:t>캡틴물렁카</x:t>
   </x:si>
   <x:si>
-    <x:t>인사팀장</x:t>
-  </x:si>
-  <x:si>
     <x:t>Home</x:t>
   </x:si>
   <x:si>
+    <x:t>캐릭터 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Happy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오십위도우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...미친?!</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>Happy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 주소</x:t>
-  </x:si>
-  <x:si>
     <x:t>Main2</x:t>
   </x:si>
   <x:si>
-    <x:t>대사 ID</x:t>
+    <x:t>Speaker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Content</x:t>
   </x:si>
   <x:si>
     <x:t>NextID</x:t>
   </x:si>
   <x:si>
-    <x:t>Speaker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Main1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...미친?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어이, 지부장 나부랭이! 누구 집 보조사를 제압하겠다는 거냐!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마나...? 메테오...? 그게 뭐야... 손끝이 그냥 둔탁한 돌멩이 같아... 이봐, 보조사... 나 집에 보내줘...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쯧쯧… 자네, 착각하지 말게. 상부에서 매달 내려주는 지원금이 어르신들 찜질방이나 지어주라고 나오는 공짜 돈인 줄 아나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 지부장님. 어르신들이 관절염이랑 건망증 때문에 자꾸 복도에서 마법을 쏘셔서요. 파스라도 붙여드려야 조용해집니다.</x:t>
+    <x:t>호크아이고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네는 아주 훌륭한 사육사였어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>약속했던 거액의 퇴직금 봉투일세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에구구... 여기서 혼자 뭐 하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...어르신, 만약에 말이죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거긴 단순한 시골 노인정이 아니야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeakerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B. 프로젝트요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지, 지부장님! 한 번만 더 기회를 주십시오!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 요양보조사 하나 교체하는 건 일도 아니지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅은 죽지 않는다. 그저 전력으로 소모될 뿐.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/NPC/Boss</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들은 그 사람을 용서하실 수 있겠습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어? 제어판 모니터가 켜져 있네? 어디 보자...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장 녀석, 방탄유리 뒤로 숨어도 소용없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원장님! 오늘 점심 총명탕 맞지? 빨리 끓여와~!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>규정은 규정이야. 자네한테 줄 기회 따위는 없어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최선을 다해 케어하겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{PlayerName}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘부로 사직서 제출합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_04</x:t>
   </x:si>
   <x:si>
     <x:t>GameOver_2_05</x:t>
   </x:si>
   <x:si>
-    <x:t>GameOver_1_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최선을 다해 케어하겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘부로 사직서 제출합니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{PlayerName}</x:t>
-  </x:si>
-  <x:si>
     <x:t>네? 쥐, 쥐어짠다뇨…?</x:t>
   </x:si>
   <x:si>
-    <x:t>GameOver_2_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_03</x:t>
+    <x:t>Ending_Happy_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_20</x:t>
   </x:si>
   <x:si>
     <x:t>Ending_Happy_10</x:t>
   </x:si>
   <x:si>
+    <x:t>Ending_Happy_26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_26</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ending_Happy_01</x:t>
   </x:si>
   <x:si>
     <x:t>Ending_Happy_25</x:t>
   </x:si>
   <x:si>
-    <x:t>GameOver_2_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_27</x:t>
+    <x:t>Ending_Happy_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_02</x:t>
   </x:si>
   <x:si>
     <x:t>Ending_Happy_08</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Happy_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_02</x:t>
-  </x:si>
-  <x:si>
     <x:t>Ending_Happy_22</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Happy_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_14</x:t>
+    <x:t>Ending_Bad_03</x:t>
   </x:si>
   <x:si>
     <x:t>Ending_Bad_12</x:t>
   </x:si>
   <x:si>
+    <x:t>Ending_Happy_24</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ending_Bad_16</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Bad_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_24</x:t>
+    <x:t>Ending_Bad_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_10</x:t>
   </x:si>
   <x:si>
     <x:t>Ending_Bad_18</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Bad_27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_06</x:t>
-  </x:si>
-  <x:si>
     <x:t>Ending_Bad_25</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Bad_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세상을 구했던 전설의 영웅들은 이제 기억과 능력을 완전히 잃은 채, 지하 냉동 창고에서 거대한 '초능력 배터리'로 영원히 잠들었습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사가 매일 달여준 총명탕 덕에 뇌세포가 맑아져서, 잊어버렸던 9클래스 메테오 주문이 다 생각났다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어, 어르신들...! 오즈 할아버지, 저에요! 매일 총명탕 달여드리던 보조사라고요! 저 기억 안 나세요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5일 차가 되면 지하 4층 추출 장치 전원이 켜질 테니, 어르신들 초능력이나 팍팍 추출할 준비나 하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3일 차 보고서 잘 봤네. 근데 지출 내역에 '한방 총명탕 팩'이랑 '초강력 한방 파스 500장'은 뭔가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파스 값도 안 주고 월급에서 까겠다느니, '탈인간 배터리 공장'으로 어르신들 팔아넘기려던 블랙기업 따위!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 어르신들한테 파스 붙여주고 총명탕 끓여준 게, 죄다 초능력 잘 뽑히라고 찜질 마사지해 준 거였다고?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(남은 시간은 단 이틀... 어르신들의 마음을 얻지 못하면, 내가 먼저 이 지하에 묻히게 될지도 모른다.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무, 무슨?! 관절염 때문에 제대로 걷지도 못하던 늙은이가 어떻게 기계실 벽을 부수고 들어온 거지?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사... 오늘 온천 물이... 왜 이렇게 차가운가...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저희 실버타운 슬로건이 '사랑과 정성의 실버타운' 아니었습니까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 초능력 파편 덕분에 우리 조직은 세계 최고의 초능력 무기 상인이 되었다네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사가 돋보기를 잘 비춰준 덕에... 네놈의 혈자리 세 곳이 선명하게 보이는구나!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>히, 히익?! 말도 안 돼! 분명 녹내장에 치매에 관절염 걸린 노인네들이었잖아!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어라... 지부장 너희들이 우리 보조사를 해고하고 지하 배터리로 만들려고 했다고?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파스와 총명탕, 그리고 사랑으로 케어한 '탈인간 실버타운' 어르신들을 무시하지 마라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신의 파스와 총명탕, 그리고 따뜻한 케어가 있는 한 이곳은 세계에서 가장 안전하고 무적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...지부장님. 어르신들이 지하 4층 유리관 안에 갇혀 계시는데... 정말 괜찮으신 거 맞습니까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어서 오게, 김 보조사. 마침내 Day 7 최종 정산 및 초능력 추출 작업이 100% 완료되었네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들 멘탈을 억지로라도 끌어올려서 '기억의 파편'을 쥐어짜 내야 하는 '재고 관리실'이라고!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 2단계: 지하 추출기로 마나를 쥐어짜 내어 거대 배터리로 가공, 암시장에 팔아치운다.'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흑막 조직은 완전히 소탕되었고, 비밀 지하 요양원은 영웅들의 진짜 안식처로 탈바꿈했습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허리가 안 아파... 아무 느낌도 안 들어... 내가... 원래 뭘 하던 사람이었지...?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 몸은 늙었을지 몰라도, 그분들이 지켜온 정의와 옛 영광까지 늙은 건 아니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사...? 글쎄... 잘 모르겠는데... 나한테 파스나 붙여주던 모르는 청년인가...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>눈앞이... 검은 안개밖에 안 보여... 보조사가 준 돋보기... 아무 소용이 없네...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 블랙기업의 소모품 보조사에서, 이 위대한 실버타운의 정식 '원장'으로 추대되었습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비록 여전히 허리가 삐끗하고, 주문을 깜빡하고, 사물이 침침하게 보이는 어르신들이지만...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그분들도 자네와 유대감이 없으니, 자네가 자신들을 구해줄 거라곤 전혀 기대조차 안 하더군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사! 이게 무슨 짓인가! 감히 지하 4층 추출 장치 전원을 끄고 메인 차단기를 내려?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아니... 왠지 이 기계 앞에만 오면 머리가 핑 돌고, 옛날에 마왕 잡을 때 쓰던 메테오 마나가 쪽쪽 빨려 나가는 느낌이라 온 건데...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들 민원이나 서사에 일일이 감정 이입하지 않고, 우리가 시키는 대로 '재고 확보'에만 집중해 준 덕분에 아주 깔끔하게 작업이 끝났지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무장 요원 전원 투입! 저 반골 보조사 놈을 당장 제압해!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허리 통증 완화 완충 상태다! 전설의 지면 강타 맛을 봐라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeakerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B. 프로젝트요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가라, 메테오-!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소용없네, 보조사.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(결국 모든 건 내가 어르신들과 얼마나 깊은 유대감을 쌓았느냐에 달려있어.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음... 글쎄다. 날 속이고 이용하려 한 놈이라면 메테오로 지져버리겠지만...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 지난 일주일 동안 어르신들을 그저 '실적용 소모품'으로 대하지 않았나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크하하! 우리 보조사가 일주일 내내 매일 내 허리를 완벽하게 지져줬거든!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지부장님, 5일 차 때 그 친절한 매뉴얼이랑 포스트잇 보고 다 깨달았습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미친 소리! 고작 파스나 붙여주던 말단 보조사 주제에 눈에 뵈는 게 없구나!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원장님! 할망구가 내 돋보기 또 숨겼어! 빨리 찾아서 파스랑 같이 가져와!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참고로 자네 지난달 파스값, 실적 못 채우면 자네 월급에서 깐다. 수고하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자, 보게나. 자네가 일주일 동안 적당히 돌봐준 영웅들의 현재 상태라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만약에 누군가 어르신들의 비밀을 전부 파헤쳐서 위험에 빠뜨리려고 하면...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계 옆에 친절하게 [초능력 추출 중 - 접근 금지] 스티커까지 붙여놨잖아?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 7일간의 노고를 인정받아 두둑한 퇴직금을 받고 요양원에서 쫓겨났습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지부장이 말한 지하 4층 특별 구역이 여길 말한 건가...? 먼지 냄새에... 기계 소리만 웅웅거리는데...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 날 진심으로 대해준 사람이라면, 그 사람이 어떤 처지든 이 늙은이가 끝까지 편을 들어주지 않겠나? 허허.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신, 문 손잡이 또 박살 내셨네요… 제 월급에서 또 까이겠군요…</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이봐, 샤워실 물 온도가 너무 차잖아! 허리가 하나도 안 지져져!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[프로젝트: 늙은 사자 / 초능력 추출 및 배터리 가공 매뉴얼]...?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비가 내리는 밤이면, 당신의 귓가에 멍한 목소리가 환청처럼 들려옵니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1단계: 영웅들의 만족도를 높여 초능력을 전성기 수준으로 복원한다.'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(매뉴얼까지 이렇게 대놓고 적혀있는데 모른 척할 수는 없지...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바깥에서 입이라도 뻥끗하면 다음 추출 대상은 자네가 될 테니 명심하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(지부장의 명령대로 어르신들을 바치고 내 보신을 챙길 것인가... 아니면 어르신들과 손을 잡고 이 조직을 엎어버릴 것인가...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 부자가 되었지만, 고급 레스토랑에서 어떤 맛있는 음식을 사 먹어도 이상하게 입안 가득 씁쓸한 파스 냄새가 감돕니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘도 '아무튼 탈인간 실버타운'의 하루는 평화롭습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보안요원, 이 친구 짐 정리시키고 밖으로 던져버리게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초능력이 뿌리째 뽑혀 나가는데 사람이 멀쩡할 리가 있나!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>탈인간 실버타운이 아니라 탈인간 배터리 공장이었어?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/NPC/Player</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그나저나 자네, 모니터 보고 얼굴이 왜 그렇게 흙빛인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 웃으며 파스 상자를 들고 어르신들에게 달려갑니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>으악! 캡틴물렁카 할아버지! 여긴 어떻게 내려오셨어요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바로 온도 올려드릴게요. 제발 메테오만 쏘지 마세요...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월급 200만 원에 블랙기업이라니… 퇴사하고 싶다…</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그건 외부에 사찰단 올 때 보여주는 위조 간판이고!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/Hero/hero_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세상을 구했던 그들, 이제는 우리의 일상을 구하다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 보안요원! 이 친구 짐 챙겨서 정문 밖으로 던져버리게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네는 아주 훌륭한 사육사였어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거긴 단순한 시골 노인정이 아니야!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>약속했던 거액의 퇴직금 봉투일세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에구구... 여기서 혼자 뭐 하나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...어르신, 만약에 말이죠.</x:t>
+    <x:t>일주일 동안 군말 없이 참 잘해줬어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장이라는 녀석이 또 야근 시켰나?</x:t>
   </x:si>
   <x:si>
     <x:t>어떻게 전성기보다 더 잘 싸우는 건데?!</x:t>
   </x:si>
   <x:si>
-    <x:t>지부장이라는 녀석이 또 야근 시켰나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일주일 동안 군말 없이 참 잘해줬어.</x:t>
+    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
   </x:si>
   <x:si>
     <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅은 죽지 않는다. 그저 전력으로 소모될 뿐.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지, 지부장님! 한 번만 더 기회를 주십시오!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어? 제어판 모니터가 켜져 있네? 어디 보자...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/NPC/Boss</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들은 그 사람을 용서하실 수 있겠습니까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 요양보조사 하나 교체하는 건 일도 아니지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>규정은 규정이야. 자네한테 줄 기회 따위는 없어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지부장 녀석, 방탄유리 뒤로 숨어도 소용없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원장님! 오늘 점심 총명탕 맞지? 빨리 끓여와~!</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1010,7 +1022,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -1076,6 +1088,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1696,100 +1711,100 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B1" s="3" t="s">
-        <x:v>169</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>95</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F1" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G1" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H1" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>93</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D3" s="11" t="s">
-        <x:v>177</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>14</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>156</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H3" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B4" s="6" t="s">
-        <x:v>193</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D4" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
-        <x:v>183</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G4" s="15"/>
       <x:c r="H4" s="7"/>
@@ -1804,19 +1819,19 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>193</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>176</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E5" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G5" s="15"/>
       <x:c r="H5" s="7"/>
@@ -1831,19 +1846,19 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="8" t="s">
-        <x:v>176</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>155</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D6" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E6" s="7" t="s">
-        <x:v>267</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7"/>
@@ -1858,19 +1873,19 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="8" t="s">
-        <x:v>155</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>165</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D7" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E7" s="7" t="s">
-        <x:v>112</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7"/>
@@ -1885,19 +1900,19 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="8" t="s">
-        <x:v>165</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>182</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D8" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E8" s="16" t="s">
-        <x:v>111</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7"/>
@@ -1912,19 +1927,19 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="8" t="s">
-        <x:v>182</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>196</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E9" s="7" t="s">
-        <x:v>220</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7"/>
@@ -1939,19 +1954,19 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="8" t="s">
-        <x:v>196</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>174</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D10" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E10" s="7" t="s">
-        <x:v>216</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7"/>
@@ -1966,19 +1981,19 @@
     </x:row>
     <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="8" t="s">
-        <x:v>174</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C11" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E11" s="16" t="s">
-        <x:v>121</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7"/>
@@ -1993,19 +2008,19 @@
     </x:row>
     <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A12" s="8" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="D12" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E12" s="16" t="s">
-        <x:v>243</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="7"/>
       <x:c r="H12" s="7"/>
@@ -2020,19 +2035,19 @@
     </x:row>
     <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="8" t="s">
-        <x:v>171</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>180</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D13" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E13" s="7" t="s">
-        <x:v>277</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G13" s="7"/>
       <x:c r="H13" s="7"/>
@@ -2047,19 +2062,19 @@
     </x:row>
     <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="8" t="s">
-        <x:v>180</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>173</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D14" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E14" s="7" t="s">
-        <x:v>102</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="7"/>
       <x:c r="H14" s="7"/>
@@ -2074,19 +2089,19 @@
     </x:row>
     <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="8" t="s">
-        <x:v>173</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>181</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C15" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E15" s="16" t="s">
-        <x:v>274</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G15" s="7"/>
       <x:c r="H15" s="7"/>
@@ -2101,1609 +2116,1861 @@
     </x:row>
     <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A16" s="8" t="s">
-        <x:v>181</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>185</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D16" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E16" s="7" t="s">
-        <x:v>144</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A17" s="8" t="s">
-        <x:v>185</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>153</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C17" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D17" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E17" s="16" t="s">
-        <x:v>253</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A18" s="8" t="s">
-        <x:v>153</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B18" s="6" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="C18" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s">
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D18" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E18" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A19" s="8" t="s">
-        <x:v>190</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B19" s="6" t="s">
-        <x:v>154</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D19" s="18" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E19" s="16" t="s">
-        <x:v>178</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A20" s="8" t="s">
-        <x:v>154</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B20" s="6" t="s">
-        <x:v>172</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C20" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D20" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E20" s="16" t="s">
-        <x:v>238</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A21" s="8" t="s">
-        <x:v>172</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B21" s="6" t="s">
-        <x:v>159</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C21" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D21" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E21" s="7" t="s">
-        <x:v>142</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A22" s="8" t="s">
-        <x:v>159</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B22" s="6" t="s">
-        <x:v>184</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C22" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D22" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E22" s="7" t="s">
-        <x:v>268</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A23" s="8" t="s">
-        <x:v>184</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B23" s="6" t="s">
-        <x:v>168</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E23" s="16" t="s">
-        <x:v>225</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A24" s="8" t="s">
-        <x:v>168</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B24" s="9">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D24" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E24" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A25" s="9" t="s">
-        <x:v>23</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B25" s="9" t="s">
-        <x:v>51</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C25" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D25" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E25" s="19" t="s">
-        <x:v>17</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F25" s="5" t="s">
-        <x:v>183</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G25" s="5" t="s">
-        <x:v>175</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="9" t="s">
-        <x:v>51</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
-        <x:v>34</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C26" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D26" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E26" s="19" t="s">
-        <x:v>126</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F26" s="7"/>
     </x:row>
     <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="9" t="s">
-        <x:v>34</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>27</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C27" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D27" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E27" s="19" t="s">
-        <x:v>123</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F27" s="7"/>
     </x:row>
     <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A28" s="9" t="s">
-        <x:v>27</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B28" s="10">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D28" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E28" s="19" t="s">
-        <x:v>229</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F28" s="7"/>
     </x:row>
     <x:row r="29" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A29" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B29" s="9" t="s">
-        <x:v>57</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C29" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D29" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E29" s="19" t="s">
-        <x:v>1</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G29" s="5" t="s">
-        <x:v>175</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A30" s="9" t="s">
-        <x:v>57</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B30" s="9" t="s">
-        <x:v>24</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C30" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D30" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E30" s="19" t="s">
-        <x:v>270</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="F30" s="5" t="s">
-        <x:v>183</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A31" s="9" t="s">
-        <x:v>24</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B31" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C31" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D31" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E31" s="5" t="s">
-        <x:v>231</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A32" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B32" s="9" t="s">
-        <x:v>22</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C32" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D32" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E32" s="19" t="s">
-        <x:v>276</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A33" s="9" t="s">
-        <x:v>22</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B33" s="9" t="s">
-        <x:v>32</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C33" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D33" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E33" s="19" t="s">
-        <x:v>275</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A34" s="9" t="s">
-        <x:v>32</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B34" s="9" t="s">
-        <x:v>61</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C34" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D34" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E34" s="5" t="s">
-        <x:v>245</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A35" s="9" t="s">
-        <x:v>61</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B35" s="9" t="s">
-        <x:v>38</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C35" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D35" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E35" s="19" t="s">
-        <x:v>120</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A36" s="9" t="s">
-        <x:v>38</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B36" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E36" s="19" t="s">
-        <x:v>129</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="5" t="s">
-        <x:v>166</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B37" s="5" t="s">
-        <x:v>150</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C37" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D37" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E37" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="5" t="s">
-        <x:v>183</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G37" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A38" s="5" t="s">
-        <x:v>150</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B38" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C38" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D38" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E38" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A39" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B39" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C39" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D39" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E39" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A40" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B40" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C40" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D40" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E40" s="19" t="s">
-        <x:v>260</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A41" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B41" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C41" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D41" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E41" s="5" t="s">
-        <x:v>128</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A42" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B42" s="5" t="s">
-        <x:v>163</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C42" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D42" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E42" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A43" s="5" t="s">
-        <x:v>163</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B43" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C43" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D43" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E43" s="5" t="s">
-        <x:v>115</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A44" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B44" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C44" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D44" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E44" s="5" t="s">
-        <x:v>255</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A45" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B45" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C45" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D45" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E45" s="19" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A46" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B46" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C46" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D46" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E46" s="5" t="s">
-        <x:v>222</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A47" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B47" s="5" t="s">
-        <x:v>157</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C47" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D47" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E47" s="5" t="s">
-        <x:v>254</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A48" s="5" t="s">
-        <x:v>157</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B48" s="5" t="s">
-        <x:v>179</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C48" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D48" s="8" t="s">
-        <x:v>256</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E48" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A49" s="5" t="s">
-        <x:v>179</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B49" s="5" t="s">
-        <x:v>158</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C49" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D49" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E49" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A50" s="5" t="s">
-        <x:v>158</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B50" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C50" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D50" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E50" s="5" t="s">
-        <x:v>252</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A51" s="5" t="s">
-        <x:v>186</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B51" s="5" t="s">
-        <x:v>201</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C51" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D51" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E51" s="19" t="s">
-        <x:v>228</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F51" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G51" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A52" s="5" t="s">
-        <x:v>201</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B52" s="5" t="s">
-        <x:v>195</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C52" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D52" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E52" s="19" t="s">
-        <x:v>271</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A53" s="5" t="s">
-        <x:v>195</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B53" s="5" t="s">
-        <x:v>194</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C53" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D53" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E53" s="19" t="s">
-        <x:v>234</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A54" s="5" t="s">
-        <x:v>194</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B54" s="5" t="s">
-        <x:v>192</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D54" s="8"/>
       <x:c r="E54" s="21" t="s">
-        <x:v>236</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A55" s="5" t="s">
-        <x:v>192</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B55" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E55" s="20" t="s">
-        <x:v>130</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A56" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B56" s="5" t="s">
-        <x:v>209</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C56" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D56" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E56" s="19" t="s">
-        <x:v>16</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A57" s="5" t="s">
-        <x:v>209</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B57" s="5" t="s">
-        <x:v>187</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C57" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D57" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E57" s="19" t="s">
-        <x:v>226</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A58" s="5" t="s">
-        <x:v>187</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B58" s="5" t="s">
-        <x:v>198</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D58" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E58" s="5" t="s">
-        <x:v>247</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A59" s="5" t="s">
-        <x:v>198</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B59" s="5" t="s">
-        <x:v>207</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C59" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D59" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E59" s="19" t="s">
-        <x:v>108</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A60" s="5" t="s">
-        <x:v>207</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B60" s="5" t="s">
-        <x:v>212</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C60" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D60" s="8" t="s">
-        <x:v>256</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E60" s="19" t="s">
-        <x:v>262</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A61" s="5" t="s">
-        <x:v>212</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B61" s="5" t="s">
-        <x:v>197</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C61" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D61" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E61" s="19" t="s">
-        <x:v>251</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A62" s="5" t="s">
-        <x:v>197</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B62" s="5" t="s">
-        <x:v>191</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C62" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D62" s="8" t="s">
-        <x:v>256</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E62" s="19" t="s">
-        <x:v>141</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A63" s="5" t="s">
-        <x:v>191</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B63" s="5" t="s">
-        <x:v>188</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C63" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D63" s="8" t="s">
-        <x:v>256</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E63" s="19" t="s">
-        <x:v>249</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A64" s="5" t="s">
-        <x:v>188</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B64" s="5" t="s">
-        <x:v>199</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C64" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D64" s="8" t="s">
-        <x:v>256</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E64" s="5" t="s">
-        <x:v>265</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A65" s="5" t="s">
-        <x:v>199</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B65" s="5" t="s">
-        <x:v>200</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C65" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D65" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E65" s="19" t="s">
-        <x:v>263</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A66" s="5" t="s">
-        <x:v>200</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B66" s="5" t="s">
-        <x:v>202</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C66" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D66" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E66" s="5" t="s">
-        <x:v>224</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A67" s="5" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B67" s="5" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C67" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D67" s="8" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="E67" s="5" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="B67" s="5" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="C67" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D67" s="8" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="E67" s="5" t="s">
-        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A68" s="5" t="s">
-        <x:v>204</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B68" s="5" t="s">
-        <x:v>210</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C68" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D68" s="8" t="s">
-        <x:v>256</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E68" s="19" t="s">
-        <x:v>214</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A69" s="5" t="s">
-        <x:v>210</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B69" s="5" t="s">
-        <x:v>208</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C69" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D69" s="8" t="s">
-        <x:v>256</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E69" s="19" t="s">
-        <x:v>230</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A70" s="5" t="s">
-        <x:v>208</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B70" s="5" t="s">
-        <x:v>189</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C70" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D70" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E70" s="19" t="s">
-        <x:v>237</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A71" s="5" t="s">
-        <x:v>189</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B71" s="5" t="s">
-        <x:v>206</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C71" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D71" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E71" s="19" t="s">
-        <x:v>241</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A72" s="5" t="s">
-        <x:v>206</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B72" s="5" t="s">
-        <x:v>205</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C72" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D72" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E72" s="19" t="s">
-        <x:v>213</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A73" s="5" t="s">
-        <x:v>205</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B73" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C73" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D73" s="8" t="s">
-        <x:v>248</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E73" s="19" t="s">
-        <x:v>109</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A74" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B74" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C74" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D74" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E74" s="19" t="s">
-        <x:v>127</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F74" s="5" t="s">
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G74" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A75" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B75" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C75" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D75" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E75" s="19" t="s">
-        <x:v>266</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A76" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B76" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C76" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D76" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E76" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A77" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B77" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="C77" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D77" s="8" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E77" s="19" t="s">
-        <x:v>125</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A78" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B78" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C78" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D78" s="8" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E78" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A79" s="5" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B79" s="5" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C79" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D79" s="6" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="E79" s="19" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="B79" s="5" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="E79" s="19" t="s">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A80" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B80" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="C80" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D80" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E80" s="5" t="s">
-        <x:v>246</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A81" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B81" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="C81" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D81" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E81" s="19" t="s">
-        <x:v>223</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A82" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B82" s="5" t="s">
-        <x:v>78</x:v>
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="C82" s="8" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D82" s="8" t="s">
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E82" s="19" t="s">
-        <x:v>132</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A83" s="5" t="s">
-        <x:v>78</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B83" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="C83" s="8" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D83" s="8" t="s">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E83" s="19" t="s">
-        <x:v>19</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A84" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B84" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="C84" s="8" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D84" s="8" t="s">
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E84" s="19" t="s">
-        <x:v>135</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A85" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B85" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="C85" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D85" s="8" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E85" s="19" t="s">
-        <x:v>104</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A86" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B86" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C86" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D86" s="8" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E86" s="19" t="s">
-        <x:v>134</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A87" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B87" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C87" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D87" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E87" s="19" t="s">
-        <x:v>211</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A88" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B88" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C88" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D88" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E88" s="5" t="s">
-        <x:v>215</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A89" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B89" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="C89" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D89" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E89" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A90" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B90" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C90" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D90" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E90" s="19" t="s">
-        <x:v>261</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A91" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B91" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C91" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D91" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E91" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A92" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B92" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C92" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D92" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E92" s="19" t="s">
-        <x:v>259</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A93" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B93" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="C93" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D93" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E93" s="5" t="s">
-        <x:v>258</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A94" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B94" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C94" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D94" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E94" s="5" t="s">
-        <x:v>239</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:5" ht="15.75" customHeight="1">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A95" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B95" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E95" s="19" t="s">
-        <x:v>269</x:v>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F95" s="5" t="s">
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A96" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B96" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E96" s="19" t="s">
-        <x:v>227</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A97" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B97" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E97" s="5" t="s">
-        <x:v>101</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A98" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B98" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E98" s="5" t="s">
-        <x:v>242</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A99" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B99" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E99" s="5" t="s">
-        <x:v>235</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A100" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B100" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E100" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A101" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B101" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="C101" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D101" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F101" s="5" t="s">
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G101" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A102" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B102" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="C102" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D102" s="8" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E102" s="5" t="s">
-        <x:v>218</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A103" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B103" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="C103" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D103" s="8" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E103" s="19" t="s">
-        <x:v>107</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A104" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B104" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C104" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D104" s="8" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E104" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A105" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B105" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="C105" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D105" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E105" s="19" t="s">
-        <x:v>219</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A106" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B106" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C106" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D106" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E106" s="5" t="s">
-        <x:v>145</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A107" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B107" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C107" s="5" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D107" s="8" t="s">
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E107" s="19" t="s">
-        <x:v>18</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A108" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B108" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C108" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D108" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E108" s="19" t="s">
-        <x:v>110</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A109" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B109" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C109" s="5" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D109" s="8" t="s">
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E109" s="19" t="s">
-        <x:v>217</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A110" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B110" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="C110" s="5" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D110" s="8" t="s">
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E110" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A111" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B111" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C111" s="6" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D111" s="8" t="s">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E111" s="19" t="s">
-        <x:v>119</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A112" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B112" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="C112" s="6" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D112" s="8" t="s">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E112" s="19" t="s">
-        <x:v>103</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A113" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B113" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C113" s="6" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D113" s="8" t="s">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E113" s="5" t="s">
-        <x:v>203</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A114" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B114" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C114" s="5" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D114" s="8" t="s">
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E114" s="5" t="s">
-        <x:v>278</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A115" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B115" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C115" s="5" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D115" s="8" t="s">
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E115" s="5" t="s">
-        <x:v>117</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A116" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B116" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="C116" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D116" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E116" s="19" t="s">
-        <x:v>118</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A117" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B117" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="C117" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D117" s="6" t="s">
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E117" s="5" t="s">
-        <x:v>264</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A118" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B118" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="C118" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D118" s="8" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E118" s="19" t="s">
-        <x:v>133</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A119" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B119" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C119" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D119" s="8" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E119" s="19" t="s">
-        <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:5" ht="15.75" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A120" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B120" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E120" s="19" t="s">
-        <x:v>257</x:v>
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F120" s="5" t="s">
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A121" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B121" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E121" s="19" t="s">
-        <x:v>131</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A122" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B122" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E122" s="5" t="s">
-        <x:v>136</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A123" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B123" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E123" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A124" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B124" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E124" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A125" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B125" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E125" s="5" t="s">
-        <x:v>221</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A126" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B126" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E126" s="5" t="s">
-        <x:v>279</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A127" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B127" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E127" s="5" t="s">
-        <x:v>250</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A128" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B128" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E128" s="5" t="s">
-        <x:v>244</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -21,853 +21,853 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="284">
   <x:si>
+    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘부로 사직서 제출합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최선을 다해 케어하겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{PlayerName}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네? 쥐, 쥐어짠다뇨…?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소용없네, 보조사.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가라, 메테오-!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B. 프로젝트요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeakerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호크아이고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...미친?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Speaker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Content</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캡틴물렁카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오십위도우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Happy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사가 매일 달여준 총명탕 덕에 뇌세포가 맑아져서, 잊어버렸던 9클래스 메테오 주문이 다 생각났다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3일 차 보고서 잘 봤네. 근데 지출 내역에 '한방 총명탕 팩'이랑 '초강력 한방 파스 500장'은 뭔가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어, 어르신들...! 오즈 할아버지, 저에요! 매일 총명탕 달여드리던 보조사라고요! 저 기억 안 나세요?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 어르신들한테 파스 붙여주고 총명탕 끓여준 게, 죄다 초능력 잘 뽑히라고 찜질 마사지해 준 거였다고?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무, 무슨?! 관절염 때문에 제대로 걷지도 못하던 늙은이가 어떻게 기계실 벽을 부수고 들어온 거지?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(남은 시간은 단 이틀... 어르신들의 마음을 얻지 못하면, 내가 먼저 이 지하에 묻히게 될지도 모른다.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파스 값도 안 주고 월급에서 까겠다느니, '탈인간 배터리 공장'으로 어르신들 팔아넘기려던 블랙기업 따위!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5일 차가 되면 지하 4층 추출 장치 전원이 켜질 테니, 어르신들 초능력이나 팍팍 추출할 준비나 하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...어르신, 만약에 말이죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>약속했던 거액의 퇴직금 봉투일세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네는 아주 훌륭한 사육사였어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거긴 단순한 시골 노인정이 아니야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에구구... 여기서 혼자 뭐 하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쯧쯧… 자네, 착각하지 말게. 상부에서 매달 내려주는 지원금이 어르신들 찜질방이나 지어주라고 나오는 공짜 돈인 줄 아나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나...? 메테오...? 그게 뭐야... 손끝이 그냥 둔탁한 돌멩이 같아... 이봐, 보조사... 나 집에 보내줘...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님. 어르신들이 관절염이랑 건망증 때문에 자꾸 복도에서 마법을 쏘셔서요. 파스라도 붙여드려야 조용해집니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상을 구했던 전설의 영웅들은 이제 기억과 능력을 완전히 잃은 채, 지하 냉동 창고에서 거대한 '초능력 배터리'로 영원히 잠들었습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 부자가 되었지만, 고급 레스토랑에서 어떤 맛있는 음식을 사 먹어도 이상하게 입안 가득 씁쓸한 파스 냄새가 감돕니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어서 오게, 보조사. 마침내 Day 7 최종 정산 및 초능력 추출 작업이 100% 완료되었네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...지부장님. 어르신들이 지하 4층 유리관 안에 갇혀 계시는데... 정말 괜찮으신 거 맞습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신의 파스와 총명탕, 그리고 따뜻한 케어가 있는 한 이곳은 세계에서 가장 안전하고 무적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들 멘탈을 억지로라도 끌어올려서 '기억의 파편'을 쥐어짜 내야 하는 '재고 관리실'이라고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어라... 지부장 너희들이 우리 보조사를 해고하고 지하 배터리로 만들려고 했다고?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파스와 총명탕, 그리고 사랑으로 케어한 '탈인간 실버타운' 어르신들을 무시하지 마라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>히, 히익?! 말도 안 돼! 분명 녹내장에 치매에 관절염 걸린 노인네들이었잖아!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 초능력 파편 덕분에 우리 조직은 세계 최고의 초능력 무기 상인이 되었다네.</x:t>
+  </x:si>
+  <x:si>
     <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
   </x:si>
   <x:si>
     <x:t>보조사가 돋보기를 잘 비춰준 덕에... 네놈의 혈자리 세 곳이 선명하게 보이는구나!</x:t>
   </x:si>
   <x:si>
-    <x:t>어라... 지부장 너희들이 우리 보조사를 해고하고 지하 배터리로 만들려고 했다고?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 초능력 파편 덕분에 우리 조직은 세계 최고의 초능력 무기 상인이 되었다네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파스와 총명탕, 그리고 사랑으로 케어한 '탈인간 실버타운' 어르신들을 무시하지 마라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>히, 히익?! 말도 안 돼! 분명 녹내장에 치매에 관절염 걸린 노인네들이었잖아!</x:t>
+    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니... 왠지 이 기계 앞에만 오면 머리가 핑 돌고, 옛날에 마왕 잡을 때 쓰던 메테오 마나가 쪽쪽 빨려 나가는 느낌이라 온 건데...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들 민원이나 서사에 일일이 감정 이입하지 않고, 우리가 시키는 대로 '재고 확보'에만 집중해 준 덕분에 아주 깔끔하게 작업이 끝났지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비가 내리는 밤이면, 당신의 귓가에 멍한 목소리가 환청처럼 들려옵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1단계: 영웅들의 만족도를 높여 초능력을 전성기 수준으로 복원한다.'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바깥에서 입이라도 뻥끗하면 다음 추출 대상은 자네가 될 테니 명심하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이봐, 샤워실 물 온도가 너무 차잖아! 허리가 하나도 안 지져져!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[프로젝트: 늙은 사자 / 초능력 추출 및 배터리 가공 매뉴얼]...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(매뉴얼까지 이렇게 대놓고 적혀있는데 모른 척할 수는 없지...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 문 손잡이 또 박살 내셨네요… 제 월급에서 또 까이겠군요…</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그분들도 자네와 유대감이 없으니, 자네가 자신들을 구해줄 거라곤 전혀 기대조차 안 하더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사...? 글쎄... 잘 모르겠는데... 나한테 파스나 붙여주던 모르는 청년인가...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허리가 안 아파... 아무 느낌도 안 들어... 내가... 원래 뭘 하던 사람이었지...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흑막 조직은 완전히 소탕되었고, 비밀 지하 요양원은 영웅들의 진짜 안식처로 탈바꿈했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비록 여전히 허리가 삐끗하고, 주문을 깜빡하고, 사물이 침침하게 보이는 어르신들이지만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈앞이... 검은 안개밖에 안 보여... 보조사가 준 돋보기... 아무 소용이 없네...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사! 이게 무슨 짓인가! 감히 지하 4층 추출 장치 전원을 끄고 메인 차단기를 내려?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 몸은 늙었을지 몰라도, 그분들이 지켜온 정의와 옛 영광까지 늙은 건 아니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 블랙기업의 소모품 보조사에서, 이 위대한 실버타운의 정식 '원장'으로 추대되었습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 2단계: 지하 추출기로 마나를 쥐어짜 내어 거대 배터리로 가공, 암시장에 팔아치운다.'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원장님! 할망구가 내 돋보기 또 숨겼어! 빨리 찾아서 파스랑 같이 가져와!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 지난 일주일 동안 어르신들을 그저 '실적용 소모품'으로 대하지 않았나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참고로 자네 지난달 파스값, 실적 못 채우면 자네 월급에서 깐다. 수고하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자, 보게나. 자네가 일주일 동안 적당히 돌봐준 영웅들의 현재 상태라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음... 글쎄다. 날 속이고 이용하려 한 놈이라면 메테오로 지져버리겠지만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크하하! 우리 보조사가 일주일 내내 매일 내 허리를 완벽하게 지져줬거든!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(결국 모든 건 내가 어르신들과 얼마나 깊은 유대감을 쌓았느냐에 달려있어.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장님, 5일 차 때 그 친절한 매뉴얼이랑 포스트잇 보고 다 깨달았습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계 옆에 친절하게 [초능력 추출 중 - 접근 금지] 스티커까지 붙여놨잖아?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 7일간의 노고를 인정받아 두둑한 퇴직금을 받고 요양원에서 쫓겨났습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 누군가 어르신들의 비밀을 전부 파헤쳐서 위험에 빠뜨리려고 하면...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미친 소리! 고작 파스나 붙여주던 말단 보조사 주제에 눈에 뵈는 게 없구나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장이 말한 지하 4층 특별 구역이 여길 말한 건가...? 먼지 냄새에... 기계 소리만 웅웅거리는데...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 날 진심으로 대해준 사람이라면, 그 사람이 어떤 처지든 이 늙은이가 끝까지 편을 들어주지 않겠나? 허허.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사... 오늘 온천 물이... 왜 이렇게 차가운가...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저번에 본 매뉴얼에는 능력을 뽑아내면 기억까지 파괴된다고...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저희 실버타운 슬로건이 '사랑과 정성의 실버타운' 아니었습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하하! 자네는 그 매뉴얼 다 보고서도 아직 순진한 소리를 하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어이, 지부장 나부랭이! 누구 집 보조사를 제압하겠다는 거냐!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...결국 또 D 등급이군. 지난번 경고가 가벼웠던 모양이지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무장 요원 전원 투입! 저 반골 보조사 놈을 당장 제압해!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허리 통증 완화 완충 상태다! 전설의 지면 강타 맛을 봐라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
   </x:si>
   <x:si>
     <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
   </x:si>
   <x:si>
-    <x:t>무장 요원 전원 투입! 저 반골 보조사 놈을 당장 제압해!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저번에 본 매뉴얼에는 능력을 뽑아내면 기억까지 파괴된다고...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허리 통증 완화 완충 상태다! 전설의 지면 강타 맛을 봐라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사가 매일 달여준 총명탕 덕에 뇌세포가 맑아져서, 잊어버렸던 9클래스 메테오 주문이 다 생각났다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5일 차가 되면 지하 4층 추출 장치 전원이 켜질 테니, 어르신들 초능력이나 팍팍 추출할 준비나 하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어, 어르신들...! 오즈 할아버지, 저에요! 매일 총명탕 달여드리던 보조사라고요! 저 기억 안 나세요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3일 차 보고서 잘 봤네. 근데 지출 내역에 '한방 총명탕 팩'이랑 '초강력 한방 파스 500장'은 뭔가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파스 값도 안 주고 월급에서 까겠다느니, '탈인간 배터리 공장'으로 어르신들 팔아넘기려던 블랙기업 따위!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무, 무슨?! 관절염 때문에 제대로 걷지도 못하던 늙은이가 어떻게 기계실 벽을 부수고 들어온 거지?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 어르신들한테 파스 붙여주고 총명탕 끓여준 게, 죄다 초능력 잘 뽑히라고 찜질 마사지해 준 거였다고?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(남은 시간은 단 이틀... 어르신들의 마음을 얻지 못하면, 내가 먼저 이 지하에 묻히게 될지도 모른다.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세상을 구했던 전설의 영웅들은 이제 기억과 능력을 완전히 잃은 채, 지하 냉동 창고에서 거대한 '초능력 배터리'로 영원히 잠들었습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들 멘탈을 억지로라도 끌어올려서 '기억의 파편'을 쥐어짜 내야 하는 '재고 관리실'이라고!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...지부장님. 어르신들이 지하 4층 유리관 안에 갇혀 계시는데... 정말 괜찮으신 거 맞습니까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어서 오게, 김 보조사. 마침내 Day 7 최종 정산 및 초능력 추출 작업이 100% 완료되었네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신의 파스와 총명탕, 그리고 따뜻한 케어가 있는 한 이곳은 세계에서 가장 안전하고 무적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사! 이게 무슨 짓인가! 감히 지하 4층 추출 장치 전원을 끄고 메인 차단기를 내려?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 블랙기업의 소모품 보조사에서, 이 위대한 실버타운의 정식 '원장'으로 추대되었습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흑막 조직은 완전히 소탕되었고, 비밀 지하 요양원은 영웅들의 진짜 안식처로 탈바꿈했습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허리가 안 아파... 아무 느낌도 안 들어... 내가... 원래 뭘 하던 사람이었지...?</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 2단계: 지하 추출기로 마나를 쥐어짜 내어 거대 배터리로 가공, 암시장에 팔아치운다.'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비록 여전히 허리가 삐끗하고, 주문을 깜빡하고, 사물이 침침하게 보이는 어르신들이지만...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 몸은 늙었을지 몰라도, 그분들이 지켜온 정의와 옛 영광까지 늙은 건 아니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그분들도 자네와 유대감이 없으니, 자네가 자신들을 구해줄 거라곤 전혀 기대조차 안 하더군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사...? 글쎄... 잘 모르겠는데... 나한테 파스나 붙여주던 모르는 청년인가...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>눈앞이... 검은 안개밖에 안 보여... 보조사가 준 돋보기... 아무 소용이 없네...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비가 내리는 밤이면, 당신의 귓가에 멍한 목소리가 환청처럼 들려옵니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이봐, 샤워실 물 온도가 너무 차잖아! 허리가 하나도 안 지져져!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신, 문 손잡이 또 박살 내셨네요… 제 월급에서 또 까이겠군요…</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바깥에서 입이라도 뻥끗하면 다음 추출 대상은 자네가 될 테니 명심하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1단계: 영웅들의 만족도를 높여 초능력을 전성기 수준으로 복원한다.'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[프로젝트: 늙은 사자 / 초능력 추출 및 배터리 가공 매뉴얼]...?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(매뉴얼까지 이렇게 대놓고 적혀있는데 모른 척할 수는 없지...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 부자가 되었지만, 고급 레스토랑에서 어떤 맛있는 음식을 사 먹어도 이상하게 입안 가득 씁쓸한 파스 냄새가 감돕니다.</x:t>
+    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
   </x:si>
   <x:si>
     <x:t>(지부장의 명령대로 어르신들을 바치고 내 보신을 챙길 것인가... 아니면 어르신들과 손을 잡고 이 조직을 엎어버릴 것인가...)</x:t>
   </x:si>
   <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아니... 왠지 이 기계 앞에만 오면 머리가 핑 돌고, 옛날에 마왕 잡을 때 쓰던 메테오 마나가 쪽쪽 빨려 나가는 느낌이라 온 건데...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들 민원이나 서사에 일일이 감정 이입하지 않고, 우리가 시키는 대로 '재고 확보'에만 집중해 준 덕분에 아주 깔끔하게 작업이 끝났지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 지부장님. 어르신들이 관절염이랑 건망증 때문에 자꾸 복도에서 마법을 쏘셔서요. 파스라도 붙여드려야 조용해집니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마나...? 메테오...? 그게 뭐야... 손끝이 그냥 둔탁한 돌멩이 같아... 이봐, 보조사... 나 집에 보내줘...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쯧쯧… 자네, 착각하지 말게. 상부에서 매달 내려주는 지원금이 어르신들 찜질방이나 지어주라고 나오는 공짜 돈인 줄 아나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 날 진심으로 대해준 사람이라면, 그 사람이 어떤 처지든 이 늙은이가 끝까지 편을 들어주지 않겠나? 허허.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지부장이 말한 지하 4층 특별 구역이 여길 말한 건가...? 먼지 냄새에... 기계 소리만 웅웅거리는데...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원장님! 할망구가 내 돋보기 또 숨겼어! 빨리 찾아서 파스랑 같이 가져와!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 지난 일주일 동안 어르신들을 그저 '실적용 소모품'으로 대하지 않았나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자, 보게나. 자네가 일주일 동안 적당히 돌봐준 영웅들의 현재 상태라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음... 글쎄다. 날 속이고 이용하려 한 놈이라면 메테오로 지져버리겠지만...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크하하! 우리 보조사가 일주일 내내 매일 내 허리를 완벽하게 지져줬거든!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만약에 누군가 어르신들의 비밀을 전부 파헤쳐서 위험에 빠뜨리려고 하면...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(결국 모든 건 내가 어르신들과 얼마나 깊은 유대감을 쌓았느냐에 달려있어.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계 옆에 친절하게 [초능력 추출 중 - 접근 금지] 스티커까지 붙여놨잖아?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지부장님, 5일 차 때 그 친절한 매뉴얼이랑 포스트잇 보고 다 깨달았습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 7일간의 노고를 인정받아 두둑한 퇴직금을 받고 요양원에서 쫓겨났습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미친 소리! 고작 파스나 붙여주던 말단 보조사 주제에 눈에 뵈는 게 없구나!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참고로 자네 지난달 파스값, 실적 못 채우면 자네 월급에서 깐다. 수고하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하하! 자네는 그 매뉴얼 다 보고서도 아직 순진한 소리를 하나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...결국 또 D 등급이군. 지난번 경고가 가벼웠던 모양이지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어이, 지부장 나부랭이! 누구 집 보조사를 제압하겠다는 거냐!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저희 실버타운 슬로건이 '사랑과 정성의 실버타운' 아니었습니까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사... 오늘 온천 물이... 왜 이렇게 차가운가...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소용없네, 보조사.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_15</x:t>
+    <x:t>Prefabs/Character/Hero/hero_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/NPC/Player</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바로 온도 올려드릴게요. 제발 메테오만 쏘지 마세요...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초능력이 뿌리째 뽑혀 나가는데 사람이 멀쩡할 리가 있나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그나저나 자네, 모니터 보고 얼굴이 왜 그렇게 흙빛인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월급 200만 원에 블랙기업이라니… 퇴사하고 싶다…</x:t>
   </x:si>
   <x:si>
     <x:t>그건 외부에 사찰단 올 때 보여주는 위조 간판이고!</x:t>
   </x:si>
   <x:si>
+    <x:t>당신은 웃으며 파스 상자를 들고 어르신들에게 달려갑니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상을 구했던 그들, 이제는 우리의 일상을 구하다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탈인간 실버타운이 아니라 탈인간 배터리 공장이었어?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_02</x:t>
+  </x:si>
+  <x:si>
     <x:t>으악! 캡틴물렁카 할아버지! 여긴 어떻게 내려오셨어요?!</x:t>
   </x:si>
   <x:si>
-    <x:t>세상을 구했던 그들, 이제는 우리의 일상을 구하다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그나저나 자네, 모니터 보고 얼굴이 왜 그렇게 흙빛인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바로 온도 올려드릴게요. 제발 메테오만 쏘지 마세요...</x:t>
-  </x:si>
-  <x:si>
     <x:t>보안요원, 이 친구 짐 정리시키고 밖으로 던져버리게.</x:t>
   </x:si>
   <x:si>
+    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 보안요원! 이 친구 짐 챙겨서 정문 밖으로 던져버리게.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Prefabs/Character/Hero/hero_01</x:t>
   </x:si>
   <x:si>
-    <x:t>초능력이 뿌리째 뽑혀 나가는데 사람이 멀쩡할 리가 있나!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월급 200만 원에 블랙기업이라니… 퇴사하고 싶다…</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/Hero/hero_02</x:t>
-  </x:si>
-  <x:si>
     <x:t>오늘도 '아무튼 탈인간 실버타운'의 하루는 평화롭습니다!</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Character/NPC/Player</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 보안요원! 이 친구 짐 챙겨서 정문 밖으로 던져버리게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 웃으며 파스 상자를 들고 어르신들에게 달려갑니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/Hero/hero_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>탈인간 실버타운이 아니라 탈인간 배터리 공장이었어?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가라, 메테오-!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Main1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캡틴물렁카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Happy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오십위도우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...미친?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Main2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Speaker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호크아이고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네는 아주 훌륭한 사육사였어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>약속했던 거액의 퇴직금 봉투일세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에구구... 여기서 혼자 뭐 하나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...어르신, 만약에 말이죠.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거긴 단순한 시골 노인정이 아니야!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지부장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeakerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B. 프로젝트요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver</x:t>
-  </x:si>
-  <x:si>
     <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
   </x:si>
   <x:si>
+    <x:t>영웅은 죽지 않는다. 그저 전력으로 소모될 뿐.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
+  </x:si>
+  <x:si>
     <x:t>지, 지부장님! 한 번만 더 기회를 주십시오!</x:t>
   </x:si>
   <x:si>
     <x:t>말단 요양보조사 하나 교체하는 건 일도 아니지.</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅은 죽지 않는다. 그저 전력으로 소모될 뿐.</x:t>
+    <x:t>어르신들은 그 사람을 용서하실 수 있겠습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장 녀석, 방탄유리 뒤로 숨어도 소용없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원장님! 오늘 점심 총명탕 맞지? 빨리 끓여와~!</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Character/NPC/Boss</x:t>
   </x:si>
   <x:si>
-    <x:t>어르신들은 그 사람을 용서하실 수 있겠습니까?</x:t>
-  </x:si>
-  <x:si>
     <x:t>어? 제어판 모니터가 켜져 있네? 어디 보자...</x:t>
   </x:si>
   <x:si>
-    <x:t>지부장 녀석, 방탄유리 뒤로 숨어도 소용없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원장님! 오늘 점심 총명탕 맞지? 빨리 끓여와~!</x:t>
-  </x:si>
-  <x:si>
     <x:t>규정은 규정이야. 자네한테 줄 기회 따위는 없어.</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Bad_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최선을 다해 케어하겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{PlayerName}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘부로 사직서 제출합니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네? 쥐, 쥐어짠다뇨…?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_25</x:t>
+    <x:t>어떻게 전성기보다 더 잘 싸우는 건데?!</x:t>
   </x:si>
   <x:si>
     <x:t>일주일 동안 군말 없이 참 잘해줬어.</x:t>
   </x:si>
   <x:si>
+    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
+  </x:si>
+  <x:si>
     <x:t>지부장이라는 녀석이 또 야근 시켰나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어떻게 전성기보다 더 잘 싸우는 건데?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
   </x:si>
   <x:si>
     <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
@@ -1711,28 +1711,28 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B1" s="3" t="s">
-        <x:v>179</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>171</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>166</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F1" s="4" t="s">
-        <x:v>172</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G1" s="5" t="s">
-        <x:v>173</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H1" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
@@ -1740,71 +1740,71 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>157</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D3" s="11" t="s">
-        <x:v>189</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>133</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>173</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H3" s="12" t="s">
-        <x:v>167</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="6" t="s">
-        <x:v>136</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B4" s="6" t="s">
-        <x:v>111</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D4" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>39</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G4" s="15"/>
       <x:c r="H4" s="7"/>
@@ -1819,19 +1819,19 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>111</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>183</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E5" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G5" s="15"/>
       <x:c r="H5" s="7"/>
@@ -1846,16 +1846,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="8" t="s">
-        <x:v>183</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>177</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D6" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E6" s="7" t="s">
         <x:v>283</x:v>
@@ -1873,19 +1873,19 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="8" t="s">
-        <x:v>177</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>184</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E7" s="7" t="s">
-        <x:v>77</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7"/>
@@ -1900,19 +1900,19 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="8" t="s">
-        <x:v>184</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D8" s="17" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E8" s="16" t="s">
-        <x:v>78</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7"/>
@@ -1927,19 +1927,19 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="8" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E9" s="7" t="s">
-        <x:v>70</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7"/>
@@ -1954,19 +1954,19 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="8" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>195</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D10" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E10" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7"/>
@@ -1981,19 +1981,19 @@
     </x:row>
     <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="8" t="s">
-        <x:v>195</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>186</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C11" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E11" s="16" t="s">
-        <x:v>5</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7"/>
@@ -2008,19 +2008,19 @@
     </x:row>
     <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A12" s="8" t="s">
-        <x:v>186</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>178</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D12" s="17" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E12" s="16" t="s">
-        <x:v>52</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G12" s="7"/>
       <x:c r="H12" s="7"/>
@@ -2035,19 +2035,19 @@
     </x:row>
     <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="8" t="s">
-        <x:v>178</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>193</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D13" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E13" s="7" t="s">
-        <x:v>205</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="G13" s="7"/>
       <x:c r="H13" s="7"/>
@@ -2062,19 +2062,19 @@
     </x:row>
     <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="8" t="s">
-        <x:v>193</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>192</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D14" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E14" s="7" t="s">
-        <x:v>20</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G14" s="7"/>
       <x:c r="H14" s="7"/>
@@ -2089,19 +2089,19 @@
     </x:row>
     <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="8" t="s">
-        <x:v>192</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>190</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C15" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E15" s="16" t="s">
-        <x:v>197</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="G15" s="7"/>
       <x:c r="H15" s="7"/>
@@ -2116,1861 +2116,1861 @@
     </x:row>
     <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A16" s="8" t="s">
-        <x:v>190</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E16" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A17" s="8" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>145</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C17" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D17" s="17" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E17" s="16" t="s">
-        <x:v>129</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A18" s="8" t="s">
-        <x:v>145</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B18" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C18" s="22" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D18" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E18" s="7" t="s">
-        <x:v>51</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A19" s="8" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B19" s="6" t="s">
-        <x:v>135</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="18" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E19" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A20" s="8" t="s">
-        <x:v>135</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B20" s="6" t="s">
-        <x:v>188</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C20" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D20" s="17" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E20" s="16" t="s">
-        <x:v>47</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A21" s="8" t="s">
-        <x:v>188</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B21" s="6" t="s">
-        <x:v>134</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C21" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D21" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E21" s="7" t="s">
-        <x:v>53</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A22" s="8" t="s">
-        <x:v>134</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B22" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C22" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D22" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E22" s="7" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A23" s="8" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B23" s="6" t="s">
-        <x:v>175</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E23" s="16" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A24" s="8" t="s">
-        <x:v>175</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B24" s="9">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E24" s="7" t="s">
-        <x:v>221</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A25" s="9" t="s">
-        <x:v>220</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B25" s="9" t="s">
-        <x:v>265</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C25" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D25" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E25" s="19" t="s">
-        <x:v>81</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="F25" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G25" s="5" t="s">
-        <x:v>196</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="9" t="s">
-        <x:v>265</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
-        <x:v>224</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C26" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E26" s="19" t="s">
-        <x:v>27</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F26" s="7"/>
     </x:row>
     <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="9" t="s">
-        <x:v>224</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>230</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C27" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D27" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E27" s="19" t="s">
-        <x:v>24</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F27" s="7"/>
     </x:row>
     <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A28" s="9" t="s">
-        <x:v>230</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="10">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D28" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E28" s="19" t="s">
-        <x:v>61</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="F28" s="7"/>
     </x:row>
     <x:row r="29" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A29" s="9" t="s">
-        <x:v>228</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B29" s="9" t="s">
-        <x:v>237</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C29" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D29" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E29" s="19" t="s">
-        <x:v>80</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="G29" s="5" t="s">
-        <x:v>196</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A30" s="9" t="s">
-        <x:v>237</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B30" s="9" t="s">
-        <x:v>222</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C30" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D30" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E30" s="19" t="s">
-        <x:v>198</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="F30" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A31" s="9" t="s">
-        <x:v>222</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B31" s="9" t="s">
-        <x:v>223</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C31" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D31" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E31" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A32" s="9" t="s">
-        <x:v>223</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B32" s="9" t="s">
-        <x:v>231</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C32" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D32" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E32" s="19" t="s">
-        <x:v>207</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A33" s="9" t="s">
-        <x:v>231</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="9" t="s">
-        <x:v>226</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C33" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D33" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E33" s="19" t="s">
-        <x:v>199</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A34" s="9" t="s">
-        <x:v>226</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B34" s="9" t="s">
-        <x:v>244</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D34" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E34" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A35" s="9" t="s">
-        <x:v>244</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B35" s="9" t="s">
-        <x:v>245</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D35" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E35" s="19" t="s">
-        <x:v>0</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A36" s="9" t="s">
-        <x:v>245</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B36" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E36" s="19" t="s">
-        <x:v>22</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="5" t="s">
-        <x:v>181</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B37" s="5" t="s">
-        <x:v>132</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C37" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D37" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E37" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F37" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G37" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A38" s="5" t="s">
-        <x:v>132</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B38" s="5" t="s">
-        <x:v>176</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C38" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D38" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E38" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A39" s="5" t="s">
-        <x:v>176</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B39" s="5" t="s">
-        <x:v>144</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C39" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D39" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E39" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A40" s="5" t="s">
-        <x:v>144</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B40" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C40" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D40" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E40" s="19" t="s">
-        <x:v>165</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A41" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B41" s="5" t="s">
-        <x:v>185</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C41" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D41" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E41" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A42" s="5" t="s">
-        <x:v>185</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B42" s="5" t="s">
-        <x:v>187</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C42" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D42" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E42" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A43" s="5" t="s">
-        <x:v>187</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B43" s="5" t="s">
-        <x:v>174</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C43" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D43" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E43" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A44" s="5" t="s">
-        <x:v>174</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B44" s="5" t="s">
-        <x:v>182</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C44" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D44" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E44" s="5" t="s">
-        <x:v>114</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A45" s="5" t="s">
-        <x:v>182</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B45" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C45" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D45" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E45" s="19" t="s">
-        <x:v>12</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A46" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B46" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C46" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D46" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E46" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A47" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B47" s="5" t="s">
-        <x:v>180</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C47" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D47" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E47" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A48" s="5" t="s">
-        <x:v>180</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B48" s="5" t="s">
-        <x:v>191</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C48" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D48" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E48" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A49" s="5" t="s">
-        <x:v>191</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B49" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C49" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D49" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E49" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A50" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B50" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C50" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D50" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E50" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A51" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B51" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C51" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D51" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E51" s="19" t="s">
-        <x:v>60</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F51" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G51" s="5" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A52" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B52" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C52" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D52" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E52" s="19" t="s">
-        <x:v>203</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A53" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B53" s="5" t="s">
-        <x:v>95</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C53" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D53" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E53" s="19" t="s">
-        <x:v>46</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A54" s="5" t="s">
-        <x:v>95</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B54" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D54" s="8"/>
       <x:c r="E54" s="21" t="s">
-        <x:v>45</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A55" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B55" s="5" t="s">
-        <x:v>131</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E55" s="20" t="s">
-        <x:v>33</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A56" s="5" t="s">
-        <x:v>131</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B56" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C56" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D56" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E56" s="19" t="s">
-        <x:v>154</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A57" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B57" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C57" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D57" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E57" s="19" t="s">
-        <x:v>71</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A58" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B58" s="5" t="s">
-        <x:v>112</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D58" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E58" s="5" t="s">
-        <x:v>130</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A59" s="5" t="s">
-        <x:v>112</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B59" s="5" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C59" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D59" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E59" s="19" t="s">
-        <x:v>17</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A60" s="5" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B60" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C60" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D60" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E60" s="19" t="s">
-        <x:v>163</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A61" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B61" s="5" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C61" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D61" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E61" s="19" t="s">
-        <x:v>115</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A62" s="5" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B62" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C62" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D62" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E62" s="19" t="s">
-        <x:v>54</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A63" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B63" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C63" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D63" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E63" s="19" t="s">
-        <x:v>117</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A64" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B64" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C64" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D64" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E64" s="5" t="s">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A65" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B65" s="5" t="s">
-        <x:v>141</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C65" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D65" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E65" s="19" t="s">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A66" s="5" t="s">
-        <x:v>141</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B66" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C66" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D66" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E66" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A67" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B67" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C67" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D67" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E67" s="5" t="s">
-        <x:v>202</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A68" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B68" s="5" t="s">
-        <x:v>108</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C68" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D68" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E68" s="19" t="s">
-        <x:v>65</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A69" s="5" t="s">
-        <x:v>108</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B69" s="5" t="s">
-        <x:v>103</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C69" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D69" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E69" s="19" t="s">
-        <x:v>59</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A70" s="5" t="s">
-        <x:v>103</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B70" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C70" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D70" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E70" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A71" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B71" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C71" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D71" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E71" s="19" t="s">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A72" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B72" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C72" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D72" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E72" s="19" t="s">
-        <x:v>69</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A73" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B73" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C73" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D73" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E73" s="19" t="s">
-        <x:v>18</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A74" s="5" t="s">
-        <x:v>261</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B74" s="5" t="s">
-        <x:v>215</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C74" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D74" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E74" s="19" t="s">
-        <x:v>25</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F74" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G74" s="5" t="s">
-        <x:v>168</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A75" s="5" t="s">
-        <x:v>215</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B75" s="5" t="s">
-        <x:v>268</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C75" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D75" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E75" s="19" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A76" s="5" t="s">
-        <x:v>268</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B76" s="5" t="s">
-        <x:v>217</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C76" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D76" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E76" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A77" s="5" t="s">
-        <x:v>217</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B77" s="5" t="s">
-        <x:v>274</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C77" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D77" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E77" s="19" t="s">
-        <x:v>23</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A78" s="5" t="s">
-        <x:v>274</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B78" s="5" t="s">
-        <x:v>216</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C78" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D78" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E78" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A79" s="5" t="s">
-        <x:v>216</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B79" s="5" t="s">
-        <x:v>210</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C79" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D79" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E79" s="19" t="s">
-        <x:v>79</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A80" s="5" t="s">
-        <x:v>210</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B80" s="5" t="s">
-        <x:v>272</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C80" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D80" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E80" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A81" s="5" t="s">
-        <x:v>272</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B81" s="5" t="s">
-        <x:v>264</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C81" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D81" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E81" s="19" t="s">
-        <x:v>64</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A82" s="5" t="s">
-        <x:v>264</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B82" s="5" t="s">
-        <x:v>276</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C82" s="8" t="s">
-        <x:v>152</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D82" s="8" t="s">
-        <x:v>123</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="E82" s="19" t="s">
-        <x:v>32</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A83" s="5" t="s">
-        <x:v>276</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B83" s="5" t="s">
-        <x:v>208</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C83" s="8" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D83" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E83" s="19" t="s">
-        <x:v>57</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A84" s="5" t="s">
-        <x:v>208</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B84" s="5" t="s">
-        <x:v>269</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C84" s="8" t="s">
-        <x:v>160</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D84" s="8" t="s">
-        <x:v>128</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E84" s="19" t="s">
-        <x:v>38</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A85" s="5" t="s">
-        <x:v>269</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B85" s="5" t="s">
-        <x:v>214</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C85" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D85" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E85" s="19" t="s">
-        <x:v>13</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A86" s="5" t="s">
-        <x:v>214</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B86" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C86" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D86" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E86" s="19" t="s">
-        <x:v>37</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A87" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B87" s="5" t="s">
-        <x:v>218</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C87" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D87" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E87" s="19" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A88" s="5" t="s">
-        <x:v>218</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B88" s="5" t="s">
-        <x:v>271</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C88" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D88" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E88" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A89" s="5" t="s">
-        <x:v>271</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B89" s="5" t="s">
-        <x:v>211</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C89" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D89" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E89" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A90" s="5" t="s">
-        <x:v>211</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B90" s="5" t="s">
-        <x:v>277</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C90" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D90" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E90" s="19" t="s">
-        <x:v>162</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A91" s="5" t="s">
-        <x:v>277</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B91" s="5" t="s">
-        <x:v>209</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C91" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D91" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E91" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A92" s="5" t="s">
-        <x:v>209</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B92" s="5" t="s">
-        <x:v>248</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C92" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D92" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E92" s="19" t="s">
-        <x:v>161</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A93" s="5" t="s">
-        <x:v>248</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B93" s="5" t="s">
-        <x:v>212</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C93" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D93" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E93" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A94" s="5" t="s">
-        <x:v>212</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B94" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C94" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D94" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E94" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A95" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B95" s="5" t="s">
-        <x:v>219</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E95" s="19" t="s">
-        <x:v>200</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F95" s="5" t="s">
-        <x:v>168</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A96" s="5" t="s">
-        <x:v>219</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B96" s="5" t="s">
-        <x:v>259</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E96" s="19" t="s">
-        <x:v>74</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A97" s="5" t="s">
-        <x:v>259</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B97" s="5" t="s">
-        <x:v>278</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E97" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A98" s="5" t="s">
-        <x:v>278</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B98" s="5" t="s">
-        <x:v>252</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E98" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A99" s="5" t="s">
-        <x:v>252</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B99" s="5" t="s">
-        <x:v>275</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E99" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A100" s="5" t="s">
-        <x:v>275</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B100" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E100" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A101" s="5" t="s">
-        <x:v>253</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B101" s="5" t="s">
-        <x:v>247</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C101" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D101" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F101" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G101" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A102" s="5" t="s">
-        <x:v>247</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B102" s="5" t="s">
-        <x:v>262</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C102" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D102" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E102" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A103" s="5" t="s">
-        <x:v>262</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B103" s="5" t="s">
-        <x:v>258</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C103" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D103" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E103" s="19" t="s">
-        <x:v>15</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A104" s="5" t="s">
-        <x:v>258</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B104" s="5" t="s">
-        <x:v>249</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C104" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D104" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E104" s="5" t="s">
-        <x:v>229</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A105" s="5" t="s">
-        <x:v>249</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B105" s="5" t="s">
-        <x:v>236</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C105" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D105" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E105" s="19" t="s">
-        <x:v>75</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A106" s="5" t="s">
-        <x:v>236</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B106" s="5" t="s">
-        <x:v>256</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C106" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D106" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E106" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A107" s="5" t="s">
-        <x:v>256</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B107" s="5" t="s">
-        <x:v>266</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C107" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D107" s="8" t="s">
-        <x:v>123</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="E107" s="19" t="s">
-        <x:v>82</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A108" s="5" t="s">
-        <x:v>266</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B108" s="5" t="s">
-        <x:v>251</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C108" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D108" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E108" s="19" t="s">
-        <x:v>16</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A109" s="5" t="s">
-        <x:v>251</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B109" s="5" t="s">
-        <x:v>239</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C109" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D109" s="8" t="s">
-        <x:v>123</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="E109" s="19" t="s">
-        <x:v>66</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A110" s="5" t="s">
-        <x:v>239</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B110" s="5" t="s">
-        <x:v>260</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C110" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D110" s="8" t="s">
-        <x:v>123</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="E110" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A111" s="5" t="s">
-        <x:v>260</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B111" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C111" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D111" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E111" s="19" t="s">
-        <x:v>2</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A112" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B112" s="5" t="s">
-        <x:v>273</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C112" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D112" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E112" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A113" s="5" t="s">
-        <x:v>273</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B113" s="5" t="s">
-        <x:v>257</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C113" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D113" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E113" s="5" t="s">
-        <x:v>140</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A114" s="5" t="s">
-        <x:v>257</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B114" s="5" t="s">
-        <x:v>250</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C114" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D114" s="8" t="s">
-        <x:v>128</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E114" s="5" t="s">
-        <x:v>204</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A115" s="5" t="s">
-        <x:v>250</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B115" s="5" t="s">
-        <x:v>235</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C115" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D115" s="8" t="s">
-        <x:v>128</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E115" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A116" s="5" t="s">
-        <x:v>235</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B116" s="5" t="s">
-        <x:v>263</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C116" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D116" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E116" s="19" t="s">
-        <x:v>6</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A117" s="5" t="s">
-        <x:v>263</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B117" s="5" t="s">
-        <x:v>241</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C117" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D117" s="6" t="s">
-        <x:v>201</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E117" s="5" t="s">
-        <x:v>281</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A118" s="5" t="s">
-        <x:v>241</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B118" s="5" t="s">
-        <x:v>246</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C118" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D118" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E118" s="19" t="s">
-        <x:v>35</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A119" s="5" t="s">
-        <x:v>246</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B119" s="5" t="s">
-        <x:v>238</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C119" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D119" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E119" s="19" t="s">
-        <x:v>4</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A120" s="5" t="s">
-        <x:v>238</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B120" s="5" t="s">
-        <x:v>255</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E120" s="19" t="s">
-        <x:v>116</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F120" s="5" t="s">
-        <x:v>133</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A121" s="5" t="s">
-        <x:v>255</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B121" s="5" t="s">
-        <x:v>267</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E121" s="19" t="s">
-        <x:v>31</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A122" s="5" t="s">
-        <x:v>267</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B122" s="5" t="s">
-        <x:v>243</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E122" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A123" s="5" t="s">
-        <x:v>243</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B123" s="5" t="s">
-        <x:v>270</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E123" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A124" s="5" t="s">
-        <x:v>270</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B124" s="5" t="s">
-        <x:v>254</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E124" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A125" s="5" t="s">
-        <x:v>254</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B125" s="5" t="s">
-        <x:v>240</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E125" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A126" s="5" t="s">
-        <x:v>240</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B126" s="5" t="s">
-        <x:v>242</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E126" s="5" t="s">
-        <x:v>206</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A127" s="5" t="s">
-        <x:v>242</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B127" s="5" t="s">
-        <x:v>227</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E127" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A128" s="5" t="s">
-        <x:v>227</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B128" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E128" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -19,282 +19,2040 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="284">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="720">
+  <x:si>
+    <x:t>보조사 양반, 나한테 이런 걸 줘서 뭐 하자는 건가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상의 빠름에 치여 어둠 속에 갇혀있던 이 늙은이에게 '아직 자네도 세상과 연결될 수 있다'고 말해주는 가장 따뜻한 손길이었네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 물렁한 뱃살 덕분에 자네랑 이렇게 소파에 파묻혀서 편하게 야식도 먹는 건데.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거울 보며 핏줄 세우고... 그때는 그렇게 나 자신을 달달 볶아야만 세상의 방패가 될 수 있는 줄 알았거든.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우리가 상대한 건 악당만이 아니었어. 세상이 여성 영웅에게 매겨놓은 기괴한 '유통기한'이었지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어서 오게, 보조사 양반. 문 잠그고 들어오게나. 보다시피 지금은 지팡이 점검 시간이라 말이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거울 보기도 싫던 차에, 이런 멍청하고 기분 좋은 유물을 가져다주다니. 보조사 양반, 제법이구만!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 진짜 마법으로 채널을 바꾸고 지팡이를 띄워도, 그저 '치매 영감의 착각'으로 치부해버리지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이고, 저 느끼함...! 차원 안마 의자보다 저 영감 주둥이가 내 뇌세포를 더 마비시키는구만!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매일 나 같은 꼬깐통 할아버지를 위해 안경을 맞춰다 주는 자네의 고단한 얼굴 같은 것들 말이야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이봐, 보조사 양반. 이젠 현상금이나 돈을 벌기보다, 자아실현 단계에서의 자경활동이라고 해두지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 은퇴한 지 40년이 됐지만... 이 손가락 끝의 감각과 '매의 눈'은 아직 녹슬지 않았거든!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>난 여전히 쓸모있고 완벽하다'는 걸 증명하느라 내 몸을 학대한 흔적이었지. 참 웃기는 시대 아닌가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처음엔 이 기계와 시스템들이 나를 늙고 쓸모없는 노인으로 낙인찍는 것 같아서 참 서럽고 억울했네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쯧... 왕년엔 한 손으로 들고 하늘을 날아다니던 묠니르인데, 이젠 두 손으로 들기도 힘드네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 깨달았어. 세상이 아무리 차가운 기계와 빠른 화면으로 노인들을 외면하고 소외시켜도...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>글쎄다. 남성 영웅이 늙어 배가 나오고 수염이 살짝 자라면 '멋들어진 연륜의 베테랑'이라 부르더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니, 이번엔 포즈를 잡으려던 게 아니라... 그냥 거울 속 내 모습을 가만히 들여다보고 있었네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보아라! 나의 마법 지팡이가 보여주는 '동물 차원(동물농장)'과 '트롯 차원'이다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 늙고 병든 동료들, 그리고 매일 나를 케어해주는 자네 같은 사람들과 '같은 눈높이'에서 걷고 싶기 때문이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>듣고 있자니 뇌세포가 파괴될 정도로 재미가 없었다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>차라리 이렇게 배 좀 나오고 뻔뻔하게 남들 골려 먹는 게 노년의 진정한 가성비 아닌가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이놈의 관절염에 통풍까지 겹치니 천둥은커녕 찌릿찌릿 전기 파스나 붙여야 할 신세라니...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이봐, 보조사... 한때 내 가슴근육 위에서 헬기가 착륙 연습을 했다는 걸 믿을 수 있나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어이, 보조사. 퇴근 직전에 들렀나? 앉게나. 방금 막 끓여낸 따뜻한 보리 차가 있거든.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어이! 고목 어르신, 물렁카 영감! 다들 이 트로피 잔에 담긴 보리 차 맛 좀 보시게!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 의사 선생님이 통풍 때문에 알코올은 절대 금지라고 하셨습니다. 보리 차나 드세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적당히 물렁해지면 물렁해진 대로, 뻔뻔하게 웃어넘기면서 사는 거지. 안 그래? 핫핫핫!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...뭐, 거울 보며 뱃살 잡고 있는 것보단 덜 지루하겠어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 그렇게 빡빡하게 안 살아도 세상은 잘만 돌아가는구나.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전성기 땐 하루에 닭가슴살만 1kg씩 씹어 삼키며 살았어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 준 그 썰렁한 유머집 덕분에 힘을 빼는 법을 배웠어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왕년엔 이 잔으로 신들의 음료를 바다처럼 들이켰다고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잘못된 책을 사다준 걸까...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또르르가 트로피 잔을 한 손으로 번쩍 들며 껄껄 웃고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나도 이제 싹 다 말라비틀어진 고목나무인데, 흙장난이나 하라고?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대단하십니다, 어르신. 이젠 완전히 디지털에 적응하셨네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 평생 부린 마법 중 가장 따뜻하고 진짜 같은 순간이라네. 고맙네, 보조사.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고맙네, 보조사. 비록 이 여왕이 3분짜리 인증번호엔 좀 느릴지 몰라도...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오호... 내 마법 지팡이의 마력 파동을 흡수해서 환영을 보여주는 거울이로군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안경 덕분에 요양원 구석구석의 '위협'들이 아주 잘 보여서 기분이 좋구만!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정 할 일 없으시면 거울 보고 우울해하지 마시고 이 책이나 좀 읽으세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캡틴 물렁카가 휴게실에서 다른 사람들을 붙잡고 느끼한 아재개그를 던지고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 관절도 굳으셨는데 거울 앞에서 왜 자꾸 무리한 포즈를 잡으십니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물론 그게 나쁜 건 아니지만 조금 더 놀면서 살면 얼마나 좋았을까 생각해.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이거 켜두시면 렌즈 테두리가 환해서 화면 글씨가 훨씬 잘 보이실 겁니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전성기 땐 말이지... 저 망치가 세상에서 가장 무거운 무기인 줄 알았어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>할머니, 종이 접수 안 돼요. 저기 패드에 QR코드 찍고 접수하세요'라더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>약물로 버티는 건 전성기 때로 족해요. 지금은 그냥 따뜻하게 찜질이나 하세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 손을 보게. 화분에 물을 주기는커녕 화분을 깨부수지나 않으면 다행이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_01_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선물로 한 손에 들어오는 얇은 '유머 모음집'을 건넨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_01_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영감은 투덜거리면서도 밤새 손가락 끝에서 아주 미세하게 짜낸 영양분을 화분에 쏟아붓느라 지쳐 잠든다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네도 참 기가 막힌 유머 감각을 가졌군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하! 전설의 리더인 나한테 이딴 썰렁 아재개그 책을 내밀다니...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무라는 건 말이야... 늙고 비틀어질수록 껍질이 단단해지는 법이거든.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>늙은 몸뚱이 어디선가 반드시 재생될 새로운 나뭇가지가 돋아난다는 거야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어떤 거 말씀이십니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 지팡이는 언제든 자네가 위험할 때 벼락을 내릴 준비가 되어있으니, 안심하고 이 요양원을 이끌어가게나. 핫핫핫!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맞소, 프로스트 할머니!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_02_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사 양반, 저 영감한테 체지방 제거 주사든 뭐든 당장 주사 놓아서 입 좀 막아봐!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근데 지금은 보게. 강철 같던 방패는 어디 가고 푹신한 쿠션만 하나 차고 있잖아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 가져다준 이 작은 TV 소리를 들으며, 동료들과 헛소리를 주고받는 지금이...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어라...? 흠, 흠! 내 눈이 나빠진 게 아니라, 빛의 굴절 현상 때문에 잠시 시야가 왜곡되었던 것뿐이다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상의 모든 표적이 과녁의 붉은 원으로만 보였어. 시력이 떨어지고 노안이 찾아왔을 땐, 마치 내 세상 전체가 어둠 속으로 꺼져가는 것 같더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에구구구... 허리야, 무릎이야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오십위도우가 한쪽 어깨를 틀어쥐고 거울 속 자신의 눈가를 뚫어지게 노려보고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무릎과 어깨가 오십견으로 굳어버리고 나서야 비로소 깨달았어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왔는가, 보조사 양반. 앉게나. 방금 막 안경 렌즈를 깨끗하게 닦아둔 참이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고목 영감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캡틴 물렁카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다른 어르신들하고 노가리라도 까시고요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근데 늙고 나니까 알겠더라고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 난 아주 완벽한 '느끼함'과 '뱃살'을 얻었다네! 핫핫핫!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앉아, 앉아. 칼로리 걱정 따위는 던져버리고 편하게 누우라고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으음... 거 비판이 너무 야박하구만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근데 여성 요원이 늙으면 어땠는지 아나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 어깨 또 아프시려고 그러십니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...방금까지 또 거울 앞에서 랜딩 포즈 연습을 하던 참이었네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 이봐, 보조사... 들어왔으면 밑에 방석이라도 좀 깔아주게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핫핫! 이제야 알아보는군! 그래, 진짜라니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또르르</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허, 이 낡은 깡통이 아직도 남아있었단 말인가...!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네, 네. 은퇴하신 지 40년이나 되셨는데 아직도 활시위를 당기시는 이유가 뭡니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엇, 잠시만...! 방금 불꽃이 튄 거 같은...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젊었을 땐 그랬지. 저 지팡이 하나로 차원을 찢고, 하늘을 날며, 전 세계의 칭송을 받았네. 하지만 말일세...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 어깨와 얼굴에 맞아댄 그 수많은 주사들… 사실 통증을 잊기 위한 게 아니었어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돋보기 거울로 주름을 볼 땐 몰랐는데... 이 전신 거울로 보니까 아주 가관이더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무거운 망치는 들지도 못해서 발등 찍히는 영감이, 맥주 잔 트로피는 어쩜 저렇게 잘도 들어 올리는지...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근데 자네가 갖다 준 이 돋보기안경을 쓰고 세상을 다시 보니까... 과녁보다 더 중요한 것들이 보이더라고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>와… 볼 때마다 신기하네요. 이 정도 마법이 있으시면 어디든 날아가서 거창하게 사실 수도 있을 텐데요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 그래도 제가 준 링 라이트 설치하고 나서는 앱으로 민원 서류 발급하시는 거 성공하셨잖습니까.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쯧, 마력이 노화되어서 그런가... 지상에서 5cm 이상 고도가 안 오르는군. 보조사 양반, 들어왔나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에그그, 시끄러워 죽겠네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평생을 타인의 입맛에 맞춰 완벽하고, 날씬하고, 유연한 '영웅'으로 살아가려 애썼지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>할매 프로스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그러다 어깨 완전히 나갑니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것이야말로 노년의 완벽한 전환점 아니겠나? 핫핫핫!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허허, 원래 위대한 파수꾼의 자경활동이란 가장 작은 평화를 지키는 것부터 시작하는 법이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 진짜 마법 지팡이를 짚고도 보행용 지팡이처럼 터덜터덜 걸어 다니는 이유가 뭔지 아나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제야 비로소 남의 평가에 목매던 인형이 아니라... '진짜 나'로 살아가는 기분이 들어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 위험에 처했을 때 달려가는 속도는 그 누구보다 빠를 테니 늘 안심하게나. 허허...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어라...? 음, 글씨가 한결 또렷하군! ...하지만 화가 나는 건 마찬가지다, 보조사.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배 나온 물렁카 영감의 뻔뻔한 미소, 통풍 때문에 쩔쩔매는 또르르의 잔망스러움, 그리고...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다만 남들이 나를 '미친 마법사'로 생각하게 두는 게 훨씬 편해서 가만히 있는 것뿐이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스칼렛트위치가 보행용 지팡이를 꼭 쥔 채, 방 한가운데서 까치발을 들고 부들부들 떨고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왔는가, 보조사. 방금 자네가 가르쳐 준 대로 인터넷으로 따뜻한 티백 세트를 주문해 봤다네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜딩 포즈를 취할 때 눈가에 주름 한 줄만 잡혀도 '현장감 떨어진 퇴물' 소리를 들었지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_01_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 링 라이트는 단순히 글씨를 밝혀주는 전등이 아니야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보았나, 보조사? 망치를 내려놓으니 비로소 잔을 들 손이 생겼잖아!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 맥주를 안 마시는 게 아니라, 통풍 때문에 참아주는 거라고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무슨 일 있으셨습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응? 택배? 내 무기 부품이라도 왔나? ...어라, 이건?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보았나, 보조사? 아주 효과가 확실하구만!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다이아몬드'라네! 핫핫핫! 어때, 뇌가 파르르 떨리지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빡빡하게 살 빼고 젊은 척해 봤자 피곤하기만 하지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진짜 힘을 보여주면 요양원이 아니라 국방부에 끌려갈 테니까!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사, 제법 근사한 주술 도구를 바쳤어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이고! 거울 보는 것도 모자라서 이젠 안경까지 끼고 온 동네 사람들을 노려보시네!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 방이 어두워서 화면이 더 안 보이시는 겁니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>듣게, 영감들! 요즘 세상 악당들은 도시를 파괴하지 않아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브라운관 TV 가져왔습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 이상 누군가에게 예쁘게 보이기 위해 랜딩 포즈를 취하거나, '몇 cc만 더 맞으면...' 하는 미련으로 나를 마비시키지 않을 거라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적응했다기보단... 마음이 좀 편해졌다고 하는 게 맞겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쩍쩍 갈라진 피부에, 주사 바늘 자국, 굳어버린 어깨까지...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고맙네, 보조사. 나에게 내 진짜 모습을 직시할 수 있는 이 전신 거울을 쥐여줘서.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_01_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 과녁이 세 개가 아니라 벽에 파리가 앉아있던 겁니다. 활 쏘는 건 좋은데 그러다 보조사 맞추시겠습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상은 본인이 믿고 싶은 것만 믿거든.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 천둥 영감의 유쾌함과 방패는 언제든 자네 곁에 있을 테니, 무슨 일 있으면 언제든 날 부르게나. 핫핫핫!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나이가 들고 소중한 이들이 하나둘 떠나고 나니, 거창한 마법 따위 아무 소용 없더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제42회 아스간간드 맥주 빨리 마시기 대회 우승 트로피네요. 5000cc를 3초 만에 들이키셨다고 써있던데요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저걸 들고 있는 동안엔 단 한 번도 쓰러져서도, 약한 모습을 보여서도 안 된다는 중압감이 내 어깨를 짓눌렀지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요즘 인플루언서들이 방송할 때 쓰는 링 라이트입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선물로 밝게 빛나는 카메라용 '라이트 링'을 건넨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...독약을 다루던 치명적인 요원이, 이제는 50도짜리 찜질팩 온기에 살 것 같다고 느끼다니. 참 유쾌한 퇴물이군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전성기 땐 몇 cc만 더 맞으면 될 줄 알았어. 주름을 펴는 시술이든, 굳어가는 관절을 마비시키는 통증 주사든...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 오십위도우가 아직까지 랜딩 연습을 하는 걸 알고 선물한 전신 거울 앞이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어서 오게, 보조사.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 동네 병원에 갔더니 안내원이라는 어린 녀석이 뭐라 하는 줄 아나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흠! 그, 그건 이 조명 빛 덕분에 내 눈이 잠시 되살아났기 때문이지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조명이 없었으면 또 3분 타이머에 쫓겨 휴대폰을 얼려버렸을 거다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 가져다준 이 전신 거울, 사람 참 묘하게 만들어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비록 묠니르는 너무 무거워졌지만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_02_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠시만요, 방금 지팡이가 바닥에서 떠 있었던 것 같은데요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 지팡이 짚고 힘들게 걸어 다니시는 것 같더니...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1시 방향 캡틴 물렁카, 팝콘을 세 개 연속으로 입에 집어넣음. 당뇨 수치 위험.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호크아이고가 소파 뒤에 숨어 캡틴 물렁카와 또르르를 매서운 눈빛으로 관찰하고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 고향 창고에서 요양원으로 택배가 하나 도착했습니다. 무거워서 혼났네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 건네준 이 멍청한 맥주 잔 트로피 덕분에 깨달았어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 눈이 침침한 건가, 아니면 저놈들이 분신술을 쓰는 건가...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쯧... 저 중앙의 붉은 과녁이 왜 세 개로 보이는 게지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 이제 나도 짐을 좀 내려놓아도 되는구나' 하고 말이야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>또르르가 구석에 놓인 거대한 망치를 들어올리다 손을 놓치고 만다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그저 모든 카페와 병원, 관공서에 '무인 키오스크'와 '앱 주문'만 깔아두면 되지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면은 어두워서 글씨도 안 보이고, 돋보기를 찾아 쓰면 이미 3분이 지나가 버리는데!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니, 이놈의 기계는 왜 매번 '3분 안에 입력하지 않으면 처음부터 다시'라는 게냐!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_02_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_01_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero5_01_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11시 방향 또르르, 보리 차 잔에 수증기가 줄어듦. 식어가고 있음….</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세 번이나 오류가 났지만... 허허.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저 무지한 인간들을 보게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에휴, 트위치 할멈. 리모컨 건전지 다 됐다고 또 지팡이 핑계 대네. 지팡이는 그냥 바닥이나 잘 짚고 다니쇼!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_01_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신... 방금 그거 진짜 마법이었습니까? 그 지팡이 진짜였어요?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침대에 뱃살을 드러내고 누워 팝콘을 씹던 캡틴 물렁카.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스칼렛트위치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Meal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근데 지금은 이 조그만 잎사귀에 돋아난 진딧물 한 마리한테 능욕당하고 있단 말이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호크아이고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...미친?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Speaker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Content</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캡틴물렁카</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오십위도우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Happy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Home</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몇 cc만 더 찔러 넣으면 그 유연하던 20대 시절로 돌아가서 완벽한 랜딩을 선보일 수 있을 줄 알았지. 참 미련한 착각이었어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어깨가 좀 안 돌아가면 어때? 내 몸이 유연함을 잃은 대신... 내 연륜과 삶을 바라보는 눈빛은 그 어느 때보다 날카로워졌는데.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상을 구하는 거창한 천둥은 끝났을지 몰라도, 내 굳어버린 손엔 아직 동료들과 잔을 맞대고 웃을 수 있는 온기가 남아있다는 걸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 블랙기업의 소모품 보조사에서, 이 위대한 실버타운의 정식 '원장'으로 추대되었습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero6_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 흘러간 식스팩 그리워해 봤자 뱃살 안 빠집니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어이, 보조사. 퇴근길에 팝콘 냄새 쏠려서 들어왔지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침대에서 배를 두드리며 팝콘을 씹던 캡틴 물렁카와 옆에서 차를 마시는 오십위도우가 대화를 하고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...진짜 마법 지팡이라고요? 아무튼 허공만 바라보지 마시고, 세상 어떻게 돌아가는지 뉴스라도 좀 보세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흠! 흠! 무슨 소리! 겉보기엔 노인네들 짚고 다니는 보행 지팡이 같겠지만, 이건진짜 마법 지팡이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 QR이 뭔지 몰라 멍하게 서 있으니 '어휴, 다음 분 오세요' 하고 날 없는 사람 취급하더란 말이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5일 차가 되면 지하 4층 추출 장치 전원이 켜질 테니, 어르신들 초능력이나 팍팍 추출할 준비나 하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무, 무슨?! 관절염 때문에 제대로 걷지도 못하던 늙은이가 어떻게 기계실 벽을 부수고 들어온 거지?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(남은 시간은 단 이틀... 어르신들의 마음을 얻지 못하면, 내가 먼저 이 지하에 묻히게 될지도 모른다.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 어르신들한테 파스 붙여주고 총명탕 끓여준 게, 죄다 초능력 잘 뽑히라고 찜질 마사지해 준 거였다고?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3일 차 보고서 잘 봤네. 근데 지출 내역에 '한방 총명탕 팩'이랑 '초강력 한방 파스 500장'은 뭔가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사가 매일 달여준 총명탕 덕에 뇌세포가 맑아져서, 잊어버렸던 9클래스 메테오 주문이 다 생각났다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어, 어르신들...! 오즈 할아버지, 저에요! 매일 총명탕 달여드리던 보조사라고요! 저 기억 안 나세요?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파스 값도 안 주고 월급에서 까겠다느니, '탈인간 배터리 공장'으로 어르신들 팔아넘기려던 블랙기업 따위!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 자경활동이라더니 그냥 어르신들 참견하시는 거 아닙니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 요양원에 들어올 땐 다 끝난 줄 알았어. 줄기는 말라죽고, 뿌리는 썩어서 버려질 일만 남은 밑동인 줄 알았지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 표정 굳히는 시술이나 통증 마비 주사로 해결될 몸이 아닙니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 전성기 땐 말이야, 사하라 사막에 단숨에 자작나무 숲을 피웠어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상을 구했던 전설의 영웅들은 이제 기억과 능력을 완전히 잃은 채, 지하 냉동 창고에서 거대한 '초능력 배터리'로 영원히 잠들었습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쯧, 마법사 영감. 당신 지팡이는 10분 전부터 본인 엉덩이 밑에 깔려있었소. 내 '매의 눈'과 자경활동을 모욕하지 마라.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 할매 프로스트는 과거에 수천 명의 목숨을 구했어... 그런데 이젠 고작 화면 하나 못 누른다고 '짐스러운 노인네' 취급이라니!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마음만 먹으면 요양원 지붕까지 날아갈 수 있지만... 정부 사찰단한테 걸리면 귀찮아지니 보행 지팡이인 척 위장하고 있을 뿐이지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 부자가 되었지만, 고급 레스토랑에서 어떤 맛있는 음식을 사 먹어도 이상하게 입안 가득 씁쓸한 파스 냄새가 감돕니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(지부장의 명령대로 어르신들을 바치고 내 보신을 챙길 것인가... 아니면 어르신들과 손을 잡고 이 조직을 엎어버릴 것인가...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜딩 한 번 하면 신문 1면을 도배했지! 다시 그 시절로 돌아가고 싶지 않나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어이, 요원! 자네도 전성기 땐 타이트한 수트 입고 빌딩 사이를 날아다녔잖아?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쯧쯧 소리?! 내 전성기였으면 그놈들 발밑을 얼음으로 미끄러뜨렸을 게야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 우리 같은 늙은이들은 알아서 아무것도 못 하고 사회에서 말라 죽거든!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호크아이고가 활시위를 팽팽하게 당긴 채 눈을 가늘게 뜨고 벽을 노려보고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 초능력 파편 덕분에 우리 조직은 세계 최고의 초능력 무기 상인이 되었다네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>히, 히익?! 말도 안 돼! 분명 녹내장에 치매에 관절염 걸린 노인네들이었잖아!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파스와 총명탕, 그리고 사랑으로 케어한 '탈인간 실버타운' 어르신들을 무시하지 마라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어라... 지부장 너희들이 우리 보조사를 해고하고 지하 배터리로 만들려고 했다고?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사가 돋보기를 잘 비춰준 덕에... 네놈의 혈자리 세 곳이 선명하게 보이는구나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>굳어버린 만큼... 내 아이들과 동료들을 막아줄 방패가 더 튼튼해졌다는 뜻 아니겠나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어서 오게, 보조사. 마침내 Day 7 최종 정산 및 초능력 추출 작업이 100% 완료되었네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신의 파스와 총명탕, 그리고 따뜻한 케어가 있는 한 이곳은 세계에서 가장 안전하고 무적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...지부장님. 어르신들이 지하 4층 유리관 안에 갇혀 계시는데... 정말 괜찮으신 거 맞습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들 멘탈을 억지로라도 끌어올려서 '기억의 파편'을 쥐어짜 내야 하는 '재고 관리실'이라고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말은 그렇게 했지만 고목 영감은 화분을 거실로 들고 나와 돋보기를 끼고 뚫어지게 들여다보고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고목 영감은 방 한구석에 멍하니 앉아 자신의 쩍쩍 갈라지고 딱딱하게 변해버린 손을 바라보고 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero2_02_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무거운 묠니르는 구석에 모셔두셨네요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선물로 작고 보잘것없는 '작은 화분 하나'를 건넨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1단계: 영웅들의 만족도를 높여 초능력을 전성기 수준으로 복원한다.'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(매뉴얼까지 이렇게 대놓고 적혀있는데 모른 척할 수는 없지...)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 문 손잡이 또 박살 내셨네요… 제 월급에서 또 까이겠군요…</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비가 내리는 밤이면, 당신의 귓가에 멍한 목소리가 환청처럼 들려옵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[프로젝트: 늙은 사자 / 초능력 추출 및 배터리 가공 매뉴얼]...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이봐, 샤워실 물 온도가 너무 차잖아! 허리가 하나도 안 지져져!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바깥에서 입이라도 뻥끗하면 다음 추출 대상은 자네가 될 테니 명심하고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 날 진심으로 대해준 사람이라면, 그 사람이 어떤 처지든 이 늙은이가 끝까지 편을 들어주지 않겠나? 허허.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장이 말한 지하 4층 특별 구역이 여길 말한 건가...? 먼지 냄새에... 기계 소리만 웅웅거리는데...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(결국 모든 건 내가 어르신들과 얼마나 깊은 유대감을 쌓았느냐에 달려있어.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네가 지난 일주일 동안 어르신들을 그저 '실적용 소모품'으로 대하지 않았나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음... 글쎄다. 날 속이고 이용하려 한 놈이라면 메테오로 지져버리겠지만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미친 소리! 고작 파스나 붙여주던 말단 보조사 주제에 눈에 뵈는 게 없구나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 7일간의 노고를 인정받아 두둑한 퇴직금을 받고 요양원에서 쫓겨났습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참고로 자네 지난달 파스값, 실적 못 채우면 자네 월급에서 깐다. 수고하게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계 옆에 친절하게 [초능력 추출 중 - 접근 금지] 스티커까지 붙여놨잖아?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크하하! 우리 보조사가 일주일 내내 매일 내 허리를 완벽하게 지져줬거든!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자, 보게나. 자네가 일주일 동안 적당히 돌봐준 영웅들의 현재 상태라네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>만약에 누군가 어르신들의 비밀을 전부 파헤쳐서 위험에 빠뜨리려고 하면...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원장님! 할망구가 내 돋보기 또 숨겼어! 빨리 찾아서 파스랑 같이 가져와!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장님, 5일 차 때 그 친절한 매뉴얼이랑 포스트잇 보고 다 깨달았습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비록 눈은 침침해졌지만... 내 안경 너머의 눈빛과 자네들을 지켜줄 화살은 단 한 번도 빗나간 적이 없으니, 무슨 일 있으면 언제든 내 뒤로 숨게나. 허허허!</x:t>
+  </x:si>
   <x:si>
     <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
   </x:si>
   <x:si>
+    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들 민원이나 서사에 일일이 감정 이입하지 않고, 우리가 시키는 대로 '재고 확보'에만 집중해 준 덕분에 아주 깔끔하게 작업이 끝났지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아니... 왠지 이 기계 앞에만 오면 머리가 핑 돌고, 옛날에 마왕 잡을 때 쓰던 메테오 마나가 쪽쪽 빨려 나가는 느낌이라 온 건데...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최선을 다해 케어하겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{PlayerName}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네? 쥐, 쥐어짠다뇨…?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_06</x:t>
+  </x:si>
+  <x:si>
     <x:t>오늘부로 사직서 제출합니다!</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Bad_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최선을 다해 케어하겠습니다!</x:t>
+    <x:t>Ending_Happy_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_21</x:t>
   </x:si>
   <x:si>
     <x:t>GameOver_2_04</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Happy_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{PlayerName}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_15</x:t>
-  </x:si>
-  <x:si>
     <x:t>GameOver_2_01</x:t>
   </x:si>
   <x:si>
-    <x:t>네? 쥐, 쥐어짠다뇨…?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_06</x:t>
+    <x:t>Ending_Happy_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_25</x:t>
   </x:si>
   <x:si>
     <x:t>Ending_Happy_26</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Happy_21</x:t>
+    <x:t>Ending_Bad_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_1_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver_2_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_09</x:t>
   </x:si>
   <x:si>
     <x:t>Ending_Happy_04</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Bad_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_1_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_10</x:t>
-  </x:si>
-  <x:si>
     <x:t>Ending_Happy_27</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Happy_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>Ending_Happy_18</x:t>
   </x:si>
   <x:si>
-    <x:t>GameOver_2_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver_2_07</x:t>
+    <x:t>Ending_Bad_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Happy_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending_Bad_05</x:t>
   </x:si>
   <x:si>
     <x:t>Ending_Bad_25</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Bad_03</x:t>
-  </x:si>
-  <x:si>
     <x:t>Ending_Happy_13</x:t>
   </x:si>
   <x:si>
     <x:t>Ending_Bad_16</x:t>
   </x:si>
   <x:si>
-    <x:t>Ending_Bad_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Happy_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending_Bad_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_17</x:t>
+    <x:t>Quest_05_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소용없네, 보조사.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가라, 메테오-!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameOver</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeakerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B. 프로젝트요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Opening_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_01_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나도 얼마 전에 햄버거 하나 먹으려다가 화면에서 '옵션 선택'을 못 찾아서 뒤에 서 있던 젊은 친구한테 쯧쯧 소리를 들었지 뭐야.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우리가 악당과 싸울 땐 목숨을 바쳤지만, 세상은 은퇴한 우리에게 '스마트폰도 못 쓰는 디지털 문맹 노인'이라는 표식표만 달아주더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내가 굳어버린 건 내 잘못이나 부끄러움이 아니라, 이 몸으로 세상의 온갖 풍파를 다 받아내며 끝까지 살아남았다는 '훈장'이라는 걸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거 무슨 소리! 묠니르는 무거워서 아군 발등을 찍을 위험이 있지만, 이 황금 잔은 들어 올리기만 해도 모두의 사기가 솟구치지 않나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근데 관절이 삐걱거리고 저 망치를 두 손으로도 못 들게 되었을 때... 씁쓸함과 동시에 이상하게 마음이 홀가분해지더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>활 시위가 미세하게 떨린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거긴 단순한 시골 노인정이 아니야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네는 아주 훌륭한 사육사였어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>약속했던 거액의 퇴직금 봉투일세.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에구구... 여기서 혼자 뭐 하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...어르신, 만약에 말이죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과거엔 도시 하나를 숲으로 만들던 영웅이었지만, 지금은 관절이 굳어 걷는 것조차 힘들다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 2단계: 지하 추출기로 마나를 쥐어짜 내어 거대 배터리로 가공, 암시장에 팔아치운다.'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 말이야, 보조사 양반... 내 늙은 껍데기를 가만 보고 있자니 문득 깨달은 게 있어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나...? 메테오...? 그게 뭐야... 손끝이 그냥 둔탁한 돌멩이 같아... 이봐, 보조사... 나 집에 보내줘...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쯧쯧… 자네, 착각하지 말게. 상부에서 매달 내려주는 지원금이 어르신들 찜질방이나 지어주라고 나오는 공짜 돈인 줄 아나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 지부장님. 어르신들이 관절염이랑 건망증 때문에 자꾸 복도에서 마법을 쏘셔서요. 파스라도 붙여드려야 조용해집니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈앞이... 검은 안개밖에 안 보여... 보조사가 준 돋보기... 아무 소용이 없네...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사! 이게 무슨 짓인가! 감히 지하 4층 추출 장치 전원을 끄고 메인 차단기를 내려?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신들의 몸은 늙었을지 몰라도, 그분들이 지켜온 정의와 옛 영광까지 늙은 건 아니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비록 여전히 허리가 삐끗하고, 주문을 깜빡하고, 사물이 침침하게 보이는 어르신들이지만...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허리가 안 아파... 아무 느낌도 안 들어... 내가... 원래 뭘 하던 사람이었지...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그분들도 자네와 유대감이 없으니, 자네가 자신들을 구해줄 거라곤 전혀 기대조차 안 하더군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사...? 글쎄... 잘 모르겠는데... 나한테 파스나 붙여주던 모르는 청년인가...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흑막 조직은 완전히 소탕되었고, 비밀 지하 요양원은 영웅들의 진짜 안식처로 탈바꿈했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저번에 본 매뉴얼에는 능력을 뽑아내면 기억까지 파괴된다고...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>...결국 또 D 등급이군. 지난번 경고가 가벼웠던 모양이지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저희 실버타운 슬로건이 '사랑과 정성의 실버타운' 아니었습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조사... 오늘 온천 물이... 왜 이렇게 차가운가...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무장 요원 전원 투입! 저 반골 보조사 놈을 당장 제압해!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허리 통증 완화 완충 상태다! 전설의 지면 강타 맛을 봐라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하하! 자네는 그 매뉴얼 다 보고서도 아직 순진한 소리를 하나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어이, 지부장 나부랭이! 누구 집 보조사를 제압하겠다는 거냐!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상을 구했던 그들, 이제는 우리의 일상을 구하다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바로 온도 올려드릴게요. 제발 메테오만 쏘지 마세요...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘도 '아무튼 탈인간 실버타운'의 하루는 평화롭습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탈인간 실버타운이 아니라 탈인간 배터리 공장이었어?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그나저나 자네, 모니터 보고 얼굴이 왜 그렇게 흙빛인가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월급 200만 원에 블랙기업이라니… 퇴사하고 싶다…</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그건 외부에 사찰단 올 때 보여주는 위조 간판이고!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초능력이 뿌리째 뽑혀 나가는데 사람이 멀쩡할 리가 있나!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신은 웃으며 파스 상자를 들고 어르신들에게 달려갑니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/Hero/hero_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으악! 캡틴물렁카 할아버지! 여긴 어떻게 내려오셨어요?!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보안요원, 이 친구 짐 정리시키고 밖으로 던져버리게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 보안요원! 이 친구 짐 챙겨서 정문 밖으로 던져버리게.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Character/NPC/Player</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_05_20</x:t>
@@ -309,520 +2067,43 @@
     <x:t>Quest_05_23</x:t>
   </x:si>
   <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소용없네, 보조사.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가라, 메테오-!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B. 프로젝트요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameOver</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeakerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지부장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호크아이고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...미친?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Main1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Main2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Speaker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캡틴물렁카</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오십위도우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Happy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사가 매일 달여준 총명탕 덕에 뇌세포가 맑아져서, 잊어버렸던 9클래스 메테오 주문이 다 생각났다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3일 차 보고서 잘 봤네. 근데 지출 내역에 '한방 총명탕 팩'이랑 '초강력 한방 파스 500장'은 뭔가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어, 어르신들...! 오즈 할아버지, 저에요! 매일 총명탕 달여드리던 보조사라고요! 저 기억 안 나세요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내가 어르신들한테 파스 붙여주고 총명탕 끓여준 게, 죄다 초능력 잘 뽑히라고 찜질 마사지해 준 거였다고?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무, 무슨?! 관절염 때문에 제대로 걷지도 못하던 늙은이가 어떻게 기계실 벽을 부수고 들어온 거지?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(남은 시간은 단 이틀... 어르신들의 마음을 얻지 못하면, 내가 먼저 이 지하에 묻히게 될지도 모른다.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파스 값도 안 주고 월급에서 까겠다느니, '탈인간 배터리 공장'으로 어르신들 팔아넘기려던 블랙기업 따위!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5일 차가 되면 지하 4층 추출 장치 전원이 켜질 테니, 어르신들 초능력이나 팍팍 추출할 준비나 하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...어르신, 만약에 말이죠.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>약속했던 거액의 퇴직금 봉투일세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네는 아주 훌륭한 사육사였어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거긴 단순한 시골 노인정이 아니야!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에구구... 여기서 혼자 뭐 하나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쯧쯧… 자네, 착각하지 말게. 상부에서 매달 내려주는 지원금이 어르신들 찜질방이나 지어주라고 나오는 공짜 돈인 줄 아나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마나...? 메테오...? 그게 뭐야... 손끝이 그냥 둔탁한 돌멩이 같아... 이봐, 보조사... 나 집에 보내줘...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 지부장님. 어르신들이 관절염이랑 건망증 때문에 자꾸 복도에서 마법을 쏘셔서요. 파스라도 붙여드려야 조용해집니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세상을 구했던 전설의 영웅들은 이제 기억과 능력을 완전히 잃은 채, 지하 냉동 창고에서 거대한 '초능력 배터리'로 영원히 잠들었습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 부자가 되었지만, 고급 레스토랑에서 어떤 맛있는 음식을 사 먹어도 이상하게 입안 가득 씁쓸한 파스 냄새가 감돕니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어서 오게, 보조사. 마침내 Day 7 최종 정산 및 초능력 추출 작업이 100% 완료되었네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...지부장님. 어르신들이 지하 4층 유리관 안에 갇혀 계시는데... 정말 괜찮으신 거 맞습니까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 지부장님! 그게 이번에 어르신들 관절염 민원이 겹치는 바람에 온천 짓느라 지원금이 좀...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 요양보조사 직에서 해고되었습니다. 다음 보조사는 과연 어르신들의 허리를 지켜낼 수 있을까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핑계는 됐고. 자네도 우리 조직 방침 알지? ‘D 등급 이하 2회 기록 시 즉시 계약 해지’야.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신의 파스와 총명탕, 그리고 따뜻한 케어가 있는 한 이곳은 세계에서 가장 안전하고 무적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들 멘탈을 억지로라도 끌어올려서 '기억의 파편'을 쥐어짜 내야 하는 '재고 관리실'이라고!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어라... 지부장 너희들이 우리 보조사를 해고하고 지하 배터리로 만들려고 했다고?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파스와 총명탕, 그리고 사랑으로 케어한 '탈인간 실버타운' 어르신들을 무시하지 마라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>히, 히익?! 말도 안 돼! 분명 녹내장에 치매에 관절염 걸린 노인네들이었잖아!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 초능력 파편 덕분에 우리 조직은 세계 최고의 초능력 무기 상인이 되었다네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아니, 어르신들 파스도 붙여드려야 하고! 총명탕도 끓여야 하는데! 놓으세요! 놔!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사가 돋보기를 잘 비춰준 덕에... 네놈의 혈자리 세 곳이 선명하게 보이는구나!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아니... 왠지 이 기계 앞에만 오면 머리가 핑 돌고, 옛날에 마왕 잡을 때 쓰던 메테오 마나가 쪽쪽 빨려 나가는 느낌이라 온 건데...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들 민원이나 서사에 일일이 감정 이입하지 않고, 우리가 시키는 대로 '재고 확보'에만 집중해 준 덕분에 아주 깔끔하게 작업이 끝났지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비가 내리는 밤이면, 당신의 귓가에 멍한 목소리가 환청처럼 들려옵니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1단계: 영웅들의 만족도를 높여 초능력을 전성기 수준으로 복원한다.'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바깥에서 입이라도 뻥끗하면 다음 추출 대상은 자네가 될 테니 명심하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이봐, 샤워실 물 온도가 너무 차잖아! 허리가 하나도 안 지져져!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[프로젝트: 늙은 사자 / 초능력 추출 및 배터리 가공 매뉴얼]...?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(매뉴얼까지 이렇게 대놓고 적혀있는데 모른 척할 수는 없지...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 주엔 정말 캡틴물렁카 할아버지 만족도도 올리고 파편도 많이...!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신, 문 손잡이 또 박살 내셨네요… 제 월급에서 또 까이겠군요…</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그분들도 자네와 유대감이 없으니, 자네가 자신들을 구해줄 거라곤 전혀 기대조차 안 하더군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사...? 글쎄... 잘 모르겠는데... 나한테 파스나 붙여주던 모르는 청년인가...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허리가 안 아파... 아무 느낌도 안 들어... 내가... 원래 뭘 하던 사람이었지...?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흑막 조직은 완전히 소탕되었고, 비밀 지하 요양원은 영웅들의 진짜 안식처로 탈바꿈했습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비록 여전히 허리가 삐끗하고, 주문을 깜빡하고, 사물이 침침하게 보이는 어르신들이지만...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>눈앞이... 검은 안개밖에 안 보여... 보조사가 준 돋보기... 아무 소용이 없네...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사! 이게 무슨 짓인가! 감히 지하 4층 추출 장치 전원을 끄고 메인 차단기를 내려?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 몸은 늙었을지 몰라도, 그분들이 지켜온 정의와 옛 영광까지 늙은 건 아니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 블랙기업의 소모품 보조사에서, 이 위대한 실버타운의 정식 '원장'으로 추대되었습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 2단계: 지하 추출기로 마나를 쥐어짜 내어 거대 배터리로 가공, 암시장에 팔아치운다.'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원장님! 할망구가 내 돋보기 또 숨겼어! 빨리 찾아서 파스랑 같이 가져와!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 지난 일주일 동안 어르신들을 그저 '실적용 소모품'으로 대하지 않았나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참고로 자네 지난달 파스값, 실적 못 채우면 자네 월급에서 깐다. 수고하게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자, 보게나. 자네가 일주일 동안 적당히 돌봐준 영웅들의 현재 상태라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음... 글쎄다. 날 속이고 이용하려 한 놈이라면 메테오로 지져버리겠지만...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크하하! 우리 보조사가 일주일 내내 매일 내 허리를 완벽하게 지져줬거든!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(결국 모든 건 내가 어르신들과 얼마나 깊은 유대감을 쌓았느냐에 달려있어.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지부장님, 5일 차 때 그 친절한 매뉴얼이랑 포스트잇 보고 다 깨달았습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계 옆에 친절하게 [초능력 추출 중 - 접근 금지] 스티커까지 붙여놨잖아?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 7일간의 노고를 인정받아 두둑한 퇴직금을 받고 요양원에서 쫓겨났습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>만약에 누군가 어르신들의 비밀을 전부 파헤쳐서 위험에 빠뜨리려고 하면...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미친 소리! 고작 파스나 붙여주던 말단 보조사 주제에 눈에 뵈는 게 없구나!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번 한 번은 넘어가지. 대신 다음 정산 때도 이따위 성적표를 들고 오면, 그땐 짐 쌀 생각 하게. 알겠나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지부장이 말한 지하 4층 특별 구역이 여길 말한 건가...? 먼지 냄새에... 기계 소리만 웅웅거리는데...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 날 진심으로 대해준 사람이라면, 그 사람이 어떤 처지든 이 늙은이가 끝까지 편을 들어주지 않겠나? 허허.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조사... 오늘 온천 물이... 왜 이렇게 차가운가...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저번에 본 매뉴얼에는 능력을 뽑아내면 기억까지 파괴된다고...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저희 실버타운 슬로건이 '사랑과 정성의 실버타운' 아니었습니까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하하! 자네는 그 매뉴얼 다 보고서도 아직 순진한 소리를 하나?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어이, 지부장 나부랭이! 누구 집 보조사를 제압하겠다는 거냐!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 정산 보고서 봤네. 등급이 'D'라니, 지금 제정신인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>...결국 또 D 등급이군. 지난번 경고가 가벼웠던 모양이지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무장 요원 전원 투입! 저 반골 보조사 놈을 당장 제압해!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허리 통증 완화 완충 상태다! 전설의 지면 강타 맛을 봐라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(지부장의 명령대로 어르신들을 바치고 내 보신을 챙길 것인가... 아니면 어르신들과 손을 잡고 이 조직을 엎어버릴 것인가...)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/Hero/hero_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/NPC/Player</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바로 온도 올려드릴게요. 제발 메테오만 쏘지 마세요...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>초능력이 뿌리째 뽑혀 나가는데 사람이 멀쩡할 리가 있나!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그나저나 자네, 모니터 보고 얼굴이 왜 그렇게 흙빛인가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월급 200만 원에 블랙기업이라니… 퇴사하고 싶다…</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그건 외부에 사찰단 올 때 보여주는 위조 간판이고!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신은 웃으며 파스 상자를 들고 어르신들에게 달려갑니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세상을 구했던 그들, 이제는 우리의 일상을 구하다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>탈인간 실버타운이 아니라 탈인간 배터리 공장이었어?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/Hero/hero_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>으악! 캡틴물렁카 할아버지! 여긴 어떻게 내려오셨어요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보안요원, 이 친구 짐 정리시키고 밖으로 던져버리게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 보안요원! 이 친구 짐 챙겨서 정문 밖으로 던져버리게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Character/Hero/hero_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘도 '아무튼 탈인간 실버타운'의 하루는 평화롭습니다!</x:t>
+    <x:t>Hero6_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_01_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_01_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero3_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신이 또 이상한 말씀을 하신다...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생각보다 마음에 들어하시는 것 같아 다행이다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어이, 할아범! 아몬드가 죽으면 뭔지 아나?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자네도 너무 빡빡하게 살지 말게. 인생 뭐 있나?</x:t>
   </x:si>
   <x:si>
     <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
@@ -831,53 +2112,80 @@
     <x:t>영웅은 죽지 않는다. 그저 전력으로 소모될 뿐.</x:t>
   </x:si>
   <x:si>
+    <x:t>지, 지부장님! 한 번만 더 기회를 주십시오!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말단 요양보조사 하나 교체하는 건 일도 아니지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지부장 녀석, 방탄유리 뒤로 숨어도 소용없다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원장님! 오늘 점심 총명탕 맞지? 빨리 끓여와~!</x:t>
+  </x:si>
+  <x:si>
     <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
   </x:si>
   <x:si>
-    <x:t>지, 지부장님! 한 번만 더 기회를 주십시오!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 요양보조사 하나 교체하는 건 일도 아니지.</x:t>
-  </x:si>
-  <x:si>
     <x:t>어르신들은 그 사람을 용서하실 수 있겠습니까?</x:t>
   </x:si>
   <x:si>
-    <x:t>지부장 녀석, 방탄유리 뒤로 숨어도 소용없다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원장님! 오늘 점심 총명탕 맞지? 빨리 끓여와~!</x:t>
-  </x:si>
-  <x:si>
     <x:t>Prefabs/Character/NPC/Boss</x:t>
   </x:si>
   <x:si>
+    <x:t>규정은 규정이야. 자네한테 줄 기회 따위는 없어.</x:t>
+  </x:si>
+  <x:si>
     <x:t>어? 제어판 모니터가 켜져 있네? 어디 보자...</x:t>
   </x:si>
   <x:si>
-    <x:t>규정은 규정이야. 자네한테 줄 기회 따위는 없어.</x:t>
+    <x:t>으그그... 쯧, 각도가 전혀 안 나오는군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뱃살 좀 나오고 남들이 물렁카라고 놀리면 어때?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신, 오늘도 과녁 연습 많이 하셨습니까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 마법 지팡이 훔쳐간 범인이나 좀 찾아보쇼!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피부 좀 굳고 관절 좀 굳으면 어때?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일주일 동안 군말 없이 참 잘해줬어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
   </x:si>
   <x:si>
     <x:t>어떻게 전성기보다 더 잘 싸우는 건데?!</x:t>
   </x:si>
   <x:si>
-    <x:t>일주일 동안 군말 없이 참 잘해줬어.</x:t>
-  </x:si>
-  <x:si>
     <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
   </x:si>
   <x:si>
     <x:t>지부장이라는 녀석이 또 야근 시켰나?</x:t>
   </x:si>
   <x:si>
-    <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
+    <x:t>은퇴한 지 40년이나 지난 늙은이의 자경활동을 비웃지 않고 응원해 줘서 고맙네.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전성기 땐 말이야... 1km 밖에서 날아가는 파리의 날개도 맞췄지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>으이그, 내 신세야. 이봐 보조사, 당장 '농약'... 아니, 저 자극성 해충 방제 스프레이 좀 가져와!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero7_02_09</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="10">
+  <x:fonts count="11">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -928,8 +2236,14 @@
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
+    <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+      <x:b val="1"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -969,6 +2283,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd2f2db"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffcdf2e4"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="fff4e5b2"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="fff0f0f0"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffffe7d8"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffdfe6f7"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -1022,7 +2366,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -1091,6 +2435,45 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1696,7 +3079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:P128"/>
+  <x:dimension ref="A1:P337"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="5" customWidth="1"/>
@@ -1711,100 +3094,100 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>152</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B1" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>145</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>161</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F1" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>150</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>372</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>140</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>156</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>154</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D3" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>155</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>108</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>146</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H3" s="12" t="s">
-        <x:v>139</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="6" t="s">
-        <x:v>103</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B4" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D4" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>0</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="G4" s="15"/>
       <x:c r="H4" s="7"/>
@@ -1819,19 +3202,19 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>116</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E5" s="7" t="s">
-        <x:v>215</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="G5" s="15"/>
       <x:c r="H5" s="7"/>
@@ -1846,19 +3229,19 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="8" t="s">
-        <x:v>116</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>127</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="C6" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D6" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E6" s="7" t="s">
-        <x:v>283</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7"/>
@@ -1873,19 +3256,19 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="8" t="s">
-        <x:v>127</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>120</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D7" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E7" s="7" t="s">
-        <x:v>246</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7"/>
@@ -1900,19 +3283,19 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="8" t="s">
-        <x:v>120</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D8" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E8" s="16" t="s">
-        <x:v>238</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7"/>
@@ -1927,19 +3310,19 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="8" t="s">
-        <x:v>84</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E9" s="7" t="s">
-        <x:v>222</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7"/>
@@ -1954,19 +3337,19 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="8" t="s">
-        <x:v>82</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>134</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D10" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E10" s="7" t="s">
-        <x:v>230</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7"/>
@@ -1981,19 +3364,19 @@
     </x:row>
     <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="8" t="s">
-        <x:v>134</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>121</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="C11" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E11" s="16" t="s">
-        <x:v>190</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7"/>
@@ -2008,19 +3391,19 @@
     </x:row>
     <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A12" s="8" t="s">
-        <x:v>121</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>129</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D12" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E12" s="16" t="s">
-        <x:v>249</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="G12" s="7"/>
       <x:c r="H12" s="7"/>
@@ -2035,19 +3418,19 @@
     </x:row>
     <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="8" t="s">
-        <x:v>129</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>137</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D13" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E13" s="7" t="s">
-        <x:v>270</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G13" s="7"/>
       <x:c r="H13" s="7"/>
@@ -2062,19 +3445,19 @@
     </x:row>
     <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="8" t="s">
-        <x:v>137</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>132</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E14" s="7" t="s">
-        <x:v>179</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="G14" s="7"/>
       <x:c r="H14" s="7"/>
@@ -2089,19 +3472,19 @@
     </x:row>
     <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="8" t="s">
-        <x:v>132</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>138</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="C15" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E15" s="16" t="s">
-        <x:v>268</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="G15" s="7"/>
       <x:c r="H15" s="7"/>
@@ -2116,2072 +3499,5485 @@
     </x:row>
     <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A16" s="8" t="s">
-        <x:v>138</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>83</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="C16" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D16" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E16" s="7" t="s">
-        <x:v>247</x:v>
+        <x:v>651</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A17" s="8" t="s">
-        <x:v>83</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="C17" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D17" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E17" s="16" t="s">
-        <x:v>264</x:v>
+        <x:v>663</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A18" s="8" t="s">
-        <x:v>112</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B18" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="C18" s="22" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D18" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E18" s="7" t="s">
-        <x:v>248</x:v>
+        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A19" s="8" t="s">
-        <x:v>79</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B19" s="6" t="s">
-        <x:v>102</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D19" s="18" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E19" s="16" t="s">
-        <x:v>131</x:v>
+        <x:v>616</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A20" s="8" t="s">
-        <x:v>102</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B20" s="6" t="s">
-        <x:v>130</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="C20" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D20" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E20" s="16" t="s">
-        <x:v>203</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A21" s="8" t="s">
-        <x:v>130</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="B21" s="6" t="s">
-        <x:v>111</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="C21" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D21" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E21" s="7" t="s">
-        <x:v>195</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A22" s="8" t="s">
-        <x:v>111</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B22" s="6" t="s">
-        <x:v>81</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="C22" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D22" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E22" s="7" t="s">
-        <x:v>281</x:v>
+        <x:v>714</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A23" s="8" t="s">
-        <x:v>81</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B23" s="6" t="s">
-        <x:v>125</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E23" s="16" t="s">
-        <x:v>225</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A24" s="8" t="s">
-        <x:v>125</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B24" s="9">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D24" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E24" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>513</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A25" s="9" t="s">
-        <x:v>20</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B25" s="9" t="s">
-        <x:v>35</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C25" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D25" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E25" s="19" t="s">
-        <x:v>242</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="F25" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="G25" s="5" t="s">
-        <x:v>133</x:v>
+        <x:v>611</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="9" t="s">
-        <x:v>35</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
-        <x:v>24</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="C26" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D26" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E26" s="19" t="s">
-        <x:v>183</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F26" s="7"/>
     </x:row>
     <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="9" t="s">
-        <x:v>24</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>17</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="C27" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D27" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E27" s="19" t="s">
-        <x:v>185</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="F27" s="7"/>
     </x:row>
     <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A28" s="9" t="s">
-        <x:v>17</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B28" s="10">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D28" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E28" s="19" t="s">
-        <x:v>233</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="F28" s="7"/>
     </x:row>
     <x:row r="29" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A29" s="9" t="s">
-        <x:v>14</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B29" s="9" t="s">
-        <x:v>58</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="C29" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D29" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E29" s="19" t="s">
-        <x:v>243</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="G29" s="5" t="s">
-        <x:v>133</x:v>
+        <x:v>611</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A30" s="9" t="s">
-        <x:v>58</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B30" s="9" t="s">
-        <x:v>21</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="C30" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D30" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E30" s="19" t="s">
-        <x:v>271</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="F30" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>581</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A31" s="9" t="s">
-        <x:v>21</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B31" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="C31" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D31" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E31" s="5" t="s">
-        <x:v>205</x:v>
+        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A32" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B32" s="9" t="s">
-        <x:v>10</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="C32" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D32" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E32" s="19" t="s">
-        <x:v>278</x:v>
+        <x:v>704</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A33" s="9" t="s">
-        <x:v>10</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B33" s="9" t="s">
-        <x:v>28</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="C33" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D33" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E33" s="19" t="s">
-        <x:v>272</x:v>
+        <x:v>698</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A34" s="9" t="s">
-        <x:v>28</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B34" s="9" t="s">
-        <x:v>60</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="C34" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D34" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E34" s="5" t="s">
-        <x:v>263</x:v>
+        <x:v>675</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A35" s="9" t="s">
-        <x:v>60</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B35" s="9" t="s">
-        <x:v>47</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="C35" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D35" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E35" s="19" t="s">
-        <x:v>193</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A36" s="9" t="s">
-        <x:v>47</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B36" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="E36" s="19" t="s">
-        <x:v>184</x:v>
+        <x:v>447</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B37" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="C37" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D37" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E37" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="F37" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="G37" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>371</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A38" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B38" s="5" t="s">
-        <x:v>117</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C38" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D38" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E38" s="5" t="s">
-        <x:v>177</x:v>
+        <x:v>640</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A39" s="5" t="s">
-        <x:v>117</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B39" s="5" t="s">
-        <x:v>114</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="C39" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D39" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E39" s="5" t="s">
-        <x:v>175</x:v>
+        <x:v>639</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A40" s="5" t="s">
-        <x:v>114</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B40" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="C40" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D40" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E40" s="19" t="s">
-        <x:v>173</x:v>
+        <x:v>630</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A41" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B41" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="C41" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D41" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E41" s="5" t="s">
-        <x:v>187</x:v>
+        <x:v>449</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A42" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B42" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="C42" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D42" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E42" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>518</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A43" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B43" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="C43" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D43" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E43" s="5" t="s">
-        <x:v>239</x:v>
+        <x:v>654</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A44" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B44" s="5" t="s">
-        <x:v>128</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="C44" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D44" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E44" s="5" t="s">
-        <x:v>257</x:v>
+        <x:v>670</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A45" s="5" t="s">
-        <x:v>128</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="B45" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="C45" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D45" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E45" s="19" t="s">
-        <x:v>169</x:v>
+        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A46" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B46" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="C46" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D46" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E46" s="5" t="s">
-        <x:v>220</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A47" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B47" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="C47" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D47" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E47" s="5" t="s">
-        <x:v>256</x:v>
+        <x:v>668</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A48" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B48" s="5" t="s">
-        <x:v>136</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="C48" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D48" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E48" s="5" t="s">
-        <x:v>201</x:v>
+        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A49" s="5" t="s">
-        <x:v>136</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B49" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="C49" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D49" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E49" s="5" t="s">
-        <x:v>206</x:v>
+        <x:v>459</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A50" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B50" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C50" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D50" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E50" s="5" t="s">
-        <x:v>253</x:v>
+        <x:v>662</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A51" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B51" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="C51" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D51" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E51" s="19" t="s">
-        <x:v>234</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F51" s="5" t="s">
-        <x:v>115</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="G51" s="5" t="s">
-        <x:v>153</x:v>
+        <x:v>374</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A52" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B52" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="C52" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D52" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E52" s="19" t="s">
-        <x:v>277</x:v>
+        <x:v>705</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A53" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B53" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="C53" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D53" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E53" s="19" t="s">
-        <x:v>202</x:v>
+        <x:v>462</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A54" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B54" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D54" s="8"/>
       <x:c r="E54" s="21" t="s">
-        <x:v>199</x:v>
+        <x:v>456</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A55" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B55" s="5" t="s">
-        <x:v>101</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="E55" s="20" t="s">
-        <x:v>217</x:v>
+        <x:v>636</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A56" s="5" t="s">
-        <x:v>101</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B56" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="C56" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D56" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E56" s="19" t="s">
-        <x:v>148</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A57" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B57" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="C57" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D57" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E57" s="19" t="s">
-        <x:v>228</x:v>
+        <x:v>476</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A58" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B58" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D58" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E58" s="5" t="s">
-        <x:v>260</x:v>
+        <x:v>665</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A59" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B59" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="C59" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D59" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E59" s="19" t="s">
-        <x:v>165</x:v>
+        <x:v>411</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A60" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="B60" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="C60" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D60" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E60" s="19" t="s">
-        <x:v>174</x:v>
+        <x:v>633</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A61" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B61" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="C61" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D61" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E61" s="19" t="s">
-        <x:v>262</x:v>
+        <x:v>674</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A62" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B62" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C62" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D62" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E62" s="19" t="s">
-        <x:v>196</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A63" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B63" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="C63" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D63" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E63" s="19" t="s">
-        <x:v>255</x:v>
+        <x:v>667</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A64" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B64" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="C64" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D64" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E64" s="5" t="s">
-        <x:v>282</x:v>
+        <x:v>715</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A65" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B65" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="C65" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D65" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E65" s="19" t="s">
-        <x:v>170</x:v>
+        <x:v>634</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A66" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B66" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="C66" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D66" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E66" s="5" t="s">
-        <x:v>231</x:v>
+        <x:v>480</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A67" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B67" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="C67" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D67" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E67" s="5" t="s">
-        <x:v>273</x:v>
+        <x:v>702</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A68" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B68" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="C68" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D68" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E68" s="19" t="s">
-        <x:v>223</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A69" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="B69" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="C69" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D69" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E69" s="19" t="s">
-        <x:v>235</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A70" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="B70" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="C70" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D70" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E70" s="19" t="s">
-        <x:v>204</x:v>
+        <x:v>458</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A71" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B71" s="5" t="s">
-        <x:v>78</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="C71" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D71" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E71" s="19" t="s">
-        <x:v>250</x:v>
+        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A72" s="5" t="s">
-        <x:v>78</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B72" s="5" t="s">
-        <x:v>95</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="C72" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D72" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E72" s="19" t="s">
-        <x:v>226</x:v>
+        <x:v>468</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A73" s="5" t="s">
-        <x:v>95</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="B73" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C73" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D73" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E73" s="19" t="s">
-        <x:v>167</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A74" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B74" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C74" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D74" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E74" s="19" t="s">
-        <x:v>181</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="F74" s="5" t="s">
-        <x:v>115</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="G74" s="5" t="s">
-        <x:v>141</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A75" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B75" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="C75" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D75" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E75" s="19" t="s">
-        <x:v>280</x:v>
+        <x:v>711</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A76" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B76" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="C76" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D76" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E76" s="5" t="s">
-        <x:v>197</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A77" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B77" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="C77" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D77" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E77" s="19" t="s">
-        <x:v>182</x:v>
+        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A78" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B78" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="C78" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D78" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E78" s="5" t="s">
-        <x:v>237</x:v>
+        <x:v>649</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A79" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B79" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C79" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D79" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E79" s="19" t="s">
-        <x:v>240</x:v>
+        <x:v>659</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A80" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B80" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C80" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D80" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E80" s="5" t="s">
-        <x:v>254</x:v>
+        <x:v>671</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A81" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B81" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C81" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D81" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E81" s="19" t="s">
-        <x:v>221</x:v>
+        <x:v>478</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A82" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B82" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="C82" s="8" t="s">
-        <x:v>158</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D82" s="8" t="s">
-        <x:v>261</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="E82" s="19" t="s">
-        <x:v>209</x:v>
+        <x:v>645</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A83" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B83" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="C83" s="8" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D83" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E83" s="19" t="s">
-        <x:v>176</x:v>
+        <x:v>638</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A84" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B84" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="C84" s="8" t="s">
-        <x:v>147</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="D84" s="8" t="s">
-        <x:v>251</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="E84" s="19" t="s">
-        <x:v>212</x:v>
+        <x:v>641</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A85" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B85" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C85" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D85" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E85" s="19" t="s">
-        <x:v>164</x:v>
+        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A86" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B86" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="C86" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D86" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E86" s="19" t="s">
-        <x:v>208</x:v>
+        <x:v>647</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A87" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B87" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="C87" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D87" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E87" s="19" t="s">
-        <x:v>99</x:v>
+        <x:v>582</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A88" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B88" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="C88" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D88" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E88" s="5" t="s">
-        <x:v>219</x:v>
+        <x:v>469</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A89" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B89" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="C89" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D89" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E89" s="5" t="s">
-        <x:v>207</x:v>
+        <x:v>646</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A90" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B90" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="C90" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D90" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E90" s="19" t="s">
-        <x:v>171</x:v>
+        <x:v>632</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A91" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B91" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="C91" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D91" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E91" s="5" t="s">
-        <x:v>192</x:v>
+        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A92" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B92" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="C92" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D92" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E92" s="19" t="s">
-        <x:v>172</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A93" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B93" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="C93" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D93" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E93" s="5" t="s">
-        <x:v>265</x:v>
+        <x:v>676</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A94" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B94" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="C94" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D94" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E94" s="5" t="s">
-        <x:v>200</x:v>
+        <x:v>464</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A95" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B95" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="E95" s="19" t="s">
-        <x:v>269</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="F95" s="5" t="s">
-        <x:v>141</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A96" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B96" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="E96" s="19" t="s">
-        <x:v>229</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A97" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B97" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="E97" s="5" t="s">
-        <x:v>178</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A98" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B98" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="E98" s="5" t="s">
-        <x:v>180</x:v>
+        <x:v>427</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A99" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B99" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="E99" s="5" t="s">
-        <x:v>198</x:v>
+        <x:v>461</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A100" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B100" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="E100" s="5" t="s">
-        <x:v>236</x:v>
+        <x:v>655</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A101" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B101" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="C101" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D101" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="F101" s="5" t="s">
-        <x:v>115</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="G101" s="5" t="s">
-        <x:v>159</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A102" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B102" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="C102" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D102" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E102" s="5" t="s">
-        <x:v>227</x:v>
+        <x:v>482</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A103" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B103" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="C103" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D103" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E103" s="19" t="s">
-        <x:v>168</x:v>
+        <x:v>415</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A104" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B104" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="C104" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D104" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E104" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A105" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B105" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="C105" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D105" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E105" s="19" t="s">
-        <x:v>232</x:v>
+        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A106" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B106" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="C106" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D106" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E106" s="5" t="s">
-        <x:v>244</x:v>
+        <x:v>657</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A107" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B107" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="C107" s="5" t="s">
-        <x:v>158</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D107" s="8" t="s">
-        <x:v>261</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="E107" s="19" t="s">
-        <x:v>241</x:v>
+        <x:v>660</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A108" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B108" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="C108" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D108" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E108" s="19" t="s">
-        <x:v>166</x:v>
+        <x:v>409</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A109" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B109" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="C109" s="5" t="s">
-        <x:v>158</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D109" s="8" t="s">
-        <x:v>261</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="E109" s="19" t="s">
-        <x:v>224</x:v>
+        <x:v>477</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A110" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B110" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="C110" s="5" t="s">
-        <x:v>158</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D110" s="8" t="s">
-        <x:v>261</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="E110" s="5" t="s">
-        <x:v>245</x:v>
+        <x:v>658</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A111" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B111" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C111" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D111" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E111" s="19" t="s">
-        <x:v>188</x:v>
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A112" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B112" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="C112" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D112" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E112" s="19" t="s">
-        <x:v>162</x:v>
+        <x:v>413</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A113" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B113" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="C113" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D113" s="8" t="s">
-        <x:v>266</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E113" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>587</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A114" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B114" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="C114" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="D114" s="8" t="s">
-        <x:v>251</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="E114" s="5" t="s">
-        <x:v>274</x:v>
+        <x:v>699</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A115" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B115" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C115" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="D115" s="8" t="s">
-        <x:v>251</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="E115" s="5" t="s">
-        <x:v>194</x:v>
+        <x:v>441</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A116" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B116" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C116" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D116" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E116" s="19" t="s">
-        <x:v>191</x:v>
+        <x:v>437</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A117" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B117" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="C117" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D117" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E117" s="5" t="s">
-        <x:v>279</x:v>
+        <x:v>713</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A118" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B118" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="C118" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D118" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E118" s="19" t="s">
-        <x:v>214</x:v>
+        <x:v>643</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A119" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B119" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C119" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D119" s="8" t="s">
-        <x:v>252</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E119" s="19" t="s">
-        <x:v>189</x:v>
+        <x:v>438</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A120" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B120" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="E120" s="19" t="s">
-        <x:v>259</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="F120" s="5" t="s">
-        <x:v>108</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A121" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B121" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="E121" s="19" t="s">
-        <x:v>210</x:v>
+        <x:v>648</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A122" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B122" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="E122" s="5" t="s">
-        <x:v>216</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A123" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B123" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="E123" s="5" t="s">
-        <x:v>211</x:v>
+        <x:v>644</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A124" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B124" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="E124" s="5" t="s">
-        <x:v>186</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A125" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B125" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="E125" s="5" t="s">
-        <x:v>218</x:v>
+        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A126" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B126" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="E126" s="5" t="s">
-        <x:v>275</x:v>
+        <x:v>700</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A127" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B127" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="E127" s="5" t="s">
-        <x:v>258</x:v>
+        <x:v>672</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A128" s="5" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="B128" s="5" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="E128" s="5" t="s">
+        <x:v>664</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A129" s="23" t="s">
+        <x:v>682</x:v>
+      </x:c>
+      <x:c r="B129" s="23" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C129" s="23"/>
+      <x:c r="D129" s="23"/>
+      <x:c r="E129" s="24" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="F129" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G129" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A130" s="23" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B130" s="23" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C130" s="23"/>
+      <x:c r="D130" s="23"/>
+      <x:c r="E130" s="24" t="s">
+        <x:v>635</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A131" s="23" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B131" s="23" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C131" s="23"/>
+      <x:c r="D131" s="23"/>
+      <x:c r="E131" s="24" t="s">
+        <x:v>455</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A132" s="23" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B132" s="23" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C132" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D132" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E132" s="24" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A133" s="23" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B133" s="23" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C133" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D133" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E133" s="23" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A134" s="23" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B134" s="23" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C134" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D134" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E134" s="23" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A135" s="23" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B135" s="23" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C135" s="23"/>
+      <x:c r="D135" s="23"/>
+      <x:c r="E135" s="24" t="s">
+        <x:v>450</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A136" s="23" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B136" s="23">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C136" s="23"/>
+      <x:c r="D136" s="23"/>
+      <x:c r="E136" s="24" t="s">
+        <x:v>692</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A137" s="23" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B137" s="23" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="C137" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D137" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E137" s="24" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="F137" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G137" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A138" s="23" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="B138" s="23" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="C138" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D138" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E138" s="23" t="s">
+        <x:v>366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A139" s="23" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B139" s="23" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="C139" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D139" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E139" s="23" t="s">
+        <x:v>718</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A140" s="23" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B140" s="23">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C140" s="23"/>
+      <x:c r="D140" s="23"/>
+      <x:c r="E140" s="24" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A141" s="23" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B141" s="23" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C141" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D141" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E141" s="24" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="F141" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G141" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A142" s="23" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B142" s="23" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C142" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D142" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E142" s="24" t="s">
+        <x:v>637</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A143" s="23" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B143" s="23" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C143" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D143" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E143" s="24" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F143" s="5" t="s">
+        <x:v>359</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A144" s="23" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B144" s="23" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C144" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D144" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E144" s="23" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A145" s="23" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B145" s="23" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C145" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D145" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E145" s="24" t="s">
+        <x:v>710</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A146" s="23" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B146" s="23">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C146" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D146" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E146" s="23" t="s">
+        <x:v>442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A147" s="25" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B147" s="25" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C147" s="25"/>
+      <x:c r="D147" s="25"/>
+      <x:c r="E147" s="26" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="F147" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G147" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A148" s="25" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B148" s="25" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C148" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D148" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E148" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A149" s="25" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B149" s="25" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C149" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D149" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E149" s="26" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A150" s="25" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B150" s="25" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C150" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D150" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E150" s="26" t="s">
+        <x:v>402</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A151" s="25" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B151" s="25" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C151" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D151" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E151" s="25" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A152" s="25" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B152" s="25" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C152" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D152" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E152" s="25" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A153" s="25" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B153" s="25" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C153" s="25"/>
+      <x:c r="D153" s="25"/>
+      <x:c r="E153" s="26" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A154" s="25" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B154" s="25" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C154" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D154" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E154" s="26" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A155" s="25" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B155" s="25" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C155" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D155" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E155" s="25" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A156" s="25" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B156" s="25">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C156" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D156" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E156" s="25" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A157" s="25" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B157" s="25" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C157" s="25"/>
+      <x:c r="D157" s="25"/>
+      <x:c r="E157" s="26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F157" s="5" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="G157" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A158" s="25" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B158" s="25" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C158" s="25"/>
+      <x:c r="D158" s="25"/>
+      <x:c r="E158" s="25" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A159" s="25" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B159" s="25" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C159" s="25"/>
+      <x:c r="D159" s="25"/>
+      <x:c r="E159" s="25" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A160" s="25" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B160" s="25" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C160" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D160" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E160" s="26" t="s">
+        <x:v>693</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A161" s="25" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B161" s="25" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C161" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D161" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E161" s="25" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A162" s="25" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B162" s="25" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C162" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D162" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E162" s="26" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A163" s="25" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B163" s="25" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C163" s="23" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D163" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="E163" s="25" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A164" s="25" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B164" s="25" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C164" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D164" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E164" s="26" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A165" s="25" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B165" s="25" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C165" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D165" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E165" s="28" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A166" s="25" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B166" s="25" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C166" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D166" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E166" s="26" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A167" s="25" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B167" s="25">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C167" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D167" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E167" s="26" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A168" s="25" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B168" s="25" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C168" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D168" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E168" s="26" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="F168" s="5" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="G168" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A169" s="25" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B169" s="25" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C169" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D169" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E169" s="25" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A170" s="25" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B170" s="25" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C170" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D170" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E170" s="26" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A171" s="25" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B171" s="25" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="C171" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D171" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E171" s="26" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A172" s="25" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B172" s="25" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="C172" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D172" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E172" s="25" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A173" s="25" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B173" s="25" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C173" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D173" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E173" s="26" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A174" s="25" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B174" s="25" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C174" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D174" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E174" s="25" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F174" s="5" t="s">
+        <x:v>328</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A175" s="25" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B175" s="25" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="C175" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D175" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E175" s="25" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A176" s="25" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B176" s="25" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="C176" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D176" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E176" s="27" t="s">
+        <x:v>707</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A177" s="25" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B177" s="25" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="C177" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D177" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E177" s="25" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A178" s="25" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B178" s="25" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C178" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D178" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E178" s="25" t="s">
+        <x:v>694</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A179" s="25" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B179" s="25">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C179" s="25" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D179" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E179" s="25" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A180" s="29" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B180" s="29" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C180" s="29"/>
+      <x:c r="D180" s="29"/>
+      <x:c r="E180" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F180" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G180" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A181" s="29" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B181" s="29" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C181" s="29"/>
+      <x:c r="D181" s="29"/>
+      <x:c r="E181" s="30" t="s">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A182" s="29" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B182" s="29" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C182" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D182" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E182" s="30" t="s">
+        <x:v>706</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A183" s="29" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B183" s="29" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C183" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D183" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E183" s="29" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A184" s="29" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B184" s="29" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C184" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D184" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E184" s="30" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A185" s="29" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B185" s="29" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C185" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D185" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E185" s="30" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A186" s="29" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B186" s="29" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C186" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D186" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E186" s="30" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A187" s="29" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B187" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C187" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D187" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E187" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A188" s="29" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B188" s="29" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C188" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D188" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E188" s="29" t="s">
+        <x:v>247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A189" s="29" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B189" s="29" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C189" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D189" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E189" s="29" t="s">
+        <x:v>270</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A190" s="29" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B190" s="29" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C190" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D190" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E190" s="29" t="s">
+        <x:v>383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A191" s="29" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B191" s="29" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C191" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D191" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E191" s="29" t="s">
+        <x:v>419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A192" s="29" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B192" s="29" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="C192" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D192" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E192" s="29" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A193" s="29" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B193" s="29">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C193" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D193" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E193" s="30" t="s">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A194" s="29" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B194" s="29" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C194" s="29"/>
+      <x:c r="D194" s="29"/>
+      <x:c r="E194" s="29" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="F194" s="5" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="G194" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A195" s="29" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B195" s="29" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C195" s="29" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D195" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E195" s="30" t="s">
+        <x:v>431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A196" s="29" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B196" s="29" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C196" s="29" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D196" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E196" s="29" t="s">
+        <x:v>430</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A197" s="29" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B197" s="29" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C197" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D197" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E197" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A198" s="29" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B198" s="29" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C198" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D198" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E198" s="29" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A199" s="29" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B199" s="29" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C199" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D199" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E199" s="29" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A200" s="29" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B200" s="29" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C200" s="29" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D200" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E200" s="30" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A201" s="29" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B201" s="29" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C201" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D201" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E201" s="30" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A202" s="29" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B202" s="29" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="C202" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D202" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E202" s="29" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A203" s="29" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B203" s="29">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C203" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D203" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E203" s="29" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A204" s="29" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B204" s="29" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="C204" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D204" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E204" s="30" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="F204" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G204" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A205" s="29" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B205" s="29" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="C205" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D205" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E205" s="29" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A206" s="29" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B206" s="29" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="C206" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D206" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E206" s="30" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A207" s="29" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B207" s="29" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="C207" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D207" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E207" s="29" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A208" s="29" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B208" s="29" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="C208" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D208" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E208" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A209" s="29" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="B209" s="29" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="C209" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D209" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E209" s="29" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A210" s="29" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B210" s="29" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="C210" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D210" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E210" s="29" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="F210" s="5" t="s">
+        <x:v>418</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A211" s="29" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B211" s="29" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="C211" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D211" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E211" s="29" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A212" s="29" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="B212" s="29" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="C212" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D212" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E212" s="30" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A213" s="29" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B213" s="29" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="C213" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D213" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E213" s="29" t="s">
+        <x:v>384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A214" s="29" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B214" s="29" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="C214" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D214" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E214" s="30" t="s">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A215" s="29" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B215" s="29">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C215" s="29" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D215" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E215" s="29" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A216" s="31" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B216" s="31" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="C216" s="31"/>
+      <x:c r="D216" s="31"/>
+      <x:c r="E216" s="31" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F216" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G216" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A217" s="31" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B217" s="31" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="C217" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D217" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E217" s="32" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A218" s="31" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B218" s="31" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="C218" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D218" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E218" s="31" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A219" s="31" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B219" s="31" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="C219" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D219" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E219" s="31" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A220" s="31" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B220" s="31" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="C220" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D220" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E220" s="32" t="s">
+        <x:v>292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A221" s="31" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B221" s="31" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="C221" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D221" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E221" s="32" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A222" s="31" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="B222" s="31" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="C222" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D222" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E222" s="32" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A223" s="31" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B223" s="31" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C223" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D223" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E223" s="32" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A224" s="31" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B224" s="31">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C224" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D224" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E224" s="31" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A225" s="31" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B225" s="31" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="C225" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D225" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E225" s="31" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F225" s="5" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="G225" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A226" s="31" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B226" s="31" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="C226" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D226" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E226" s="32" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B128" s="5" t="s">
+    </x:row>
+    <x:row r="227" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A227" s="31" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B227" s="31" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="C227" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D227" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E227" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A228" s="31" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B228" s="31" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="C228" s="8" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D228" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E228" s="32" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A229" s="31" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B229" s="31" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="C229" s="31" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D229" s="8" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="E229" s="31" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="E128" s="5" t="s">
+    </x:row>
+    <x:row r="230" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A230" s="31" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B230" s="31" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="C230" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D230" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E230" s="32" t="s">
+        <x:v>627</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A231" s="31" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B231" s="31" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="C231" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D231" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E231" s="31" t="s">
+        <x:v>210</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A232" s="31" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B232" s="31" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="C232" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D232" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E232" s="32" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A233" s="31" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B233" s="31" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C233" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D233" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E233" s="32" t="s">
+        <x:v>209</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A234" s="31" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B234" s="31">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C234" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D234" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E234" s="31" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A235" s="31" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B235" s="31" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C235" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D235" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E235" s="32" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F235" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G235" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A236" s="31" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B236" s="31" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="C236" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D236" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E236" s="32" t="s">
+        <x:v>454</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A237" s="31" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B237" s="31" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="C237" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D237" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E237" s="32" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A238" s="31" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B238" s="31" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="C238" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D238" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E238" s="31" t="s">
+        <x:v>265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A239" s="31" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B239" s="31" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="C239" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D239" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E239" s="32" t="s">
+        <x:v>628</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A240" s="31" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B240" s="31" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="C240" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D240" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E240" s="31" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A241" s="31" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B241" s="31" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="C241" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D241" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E241" s="32" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A242" s="31" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B242" s="31" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C242" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D242" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E242" s="32" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F242" s="5" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A243" s="31" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B243" s="31" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="C243" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D243" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E243" s="31" t="s">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A244" s="31" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B244" s="31" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C244" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D244" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E244" s="32" t="s">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A245" s="31" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B245" s="31">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C245" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D245" s="8" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="E245" s="31" t="s">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A246" s="33" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B246" s="33" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="E246" s="19" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="F246" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G246" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A247" s="33" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="B247" s="33" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="C247" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D247" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E247" s="5" t="s">
+        <x:v>629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A248" s="33" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="B248" s="33" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="C248" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D248" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E248" s="19" t="s">
+        <x:v>295</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A249" s="33" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="B249" s="33" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="C249" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D249" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E249" s="5" t="s">
+        <x:v>294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A250" s="33" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="B250" s="33" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="C250" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D250" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E250" s="19" t="s">
+        <x:v>257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A251" s="33" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="B251" s="33" t="s">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="C251" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D251" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E251" s="19" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A252" s="33" t="s">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="B252" s="33" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="C252" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D252" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E252" s="19" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A253" s="33" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="B253" s="33" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="C253" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D253" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E253" s="19" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A254" s="33" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="B254" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C254" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D254" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E254" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A255" s="33" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B255" s="33" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C255" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D255" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E255" s="5" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F255" s="5" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="G255" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A256" s="33" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B256" s="33" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C256" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D256" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E256" s="5" t="s">
+        <x:v>329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A257" s="33" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B257" s="33" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="E257" s="5" t="s">
+        <x:v>291</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A258" s="33" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B258" s="33" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="C258" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D258" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E258" s="19" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A259" s="33" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B259" s="33" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C259" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D259" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E259" s="5" t="s">
+        <x:v>709</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A260" s="33" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B260" s="33" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="C260" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D260" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E260" s="5" t="s">
+        <x:v>423</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A261" s="33" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B261" s="33" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="C261" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D261" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E261" s="19" t="s">
+        <x:v>416</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A262" s="33" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B262" s="33" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="C262" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D262" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E262" s="19" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A263" s="33" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B263" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C263" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D263" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E263" s="5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A264" s="33" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B264" s="33" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C264" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D264" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E264" s="19" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F264" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G264" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A265" s="33" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B265" s="33" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C265" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D265" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E265" s="19" t="s">
+        <x:v>708</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A266" s="33" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B266" s="33" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C266" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D266" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E266" s="19" t="s">
+        <x:v>717</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A267" s="33" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B267" s="33" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C267" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D267" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E267" s="5" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A268" s="33" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B268" s="33" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C268" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D268" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E268" s="19" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A269" s="33" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B269" s="33" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C269" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D269" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E269" s="19" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A270" s="33" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B270" s="33" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C270" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D270" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E270" s="19" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F270" s="5" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A271" s="33" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B271" s="33" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="C271" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D271" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E271" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A272" s="33" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B272" s="33" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C272" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D272" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E272" s="19" t="s">
+        <x:v>716</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A273" s="33" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B273" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C273" s="5" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D273" s="8" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="E273" s="5" t="s">
+        <x:v>483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A274" s="34" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B274" s="34" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="C274" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D274" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E274" s="35" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F274" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G274" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A275" s="34" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B275" s="34" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="C275" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D275" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E275" s="35" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A276" s="34" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B276" s="34" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="C276" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D276" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E276" s="35" t="s">
+        <x:v>289</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A277" s="34" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B277" s="34" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="C277" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D277" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E277" s="35" t="s">
+        <x:v>288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A278" s="34" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B278" s="34" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="C278" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D278" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E278" s="35" t="s">
+        <x:v>406</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A279" s="34" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B279" s="34" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="C279" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D279" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E279" s="34" t="s">
+        <x:v>426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A280" s="34" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B280" s="34" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="C280" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D280" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E280" s="35" t="s">
+        <x:v>405</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A281" s="34" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="B281" s="34" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="C281" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D281" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E281" s="34" t="s">
+        <x:v>243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A282" s="34" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B282" s="34" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="C282" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D282" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E282" s="35" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A283" s="34" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B283" s="34">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C283" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D283" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E283" s="34" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A284" s="34" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B284" s="34" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C284" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D284" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E284" s="35" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F284" s="5" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="G284" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A285" s="34" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B285" s="34" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C285" s="8" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D285" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E285" s="35" t="s">
+        <x:v>340</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A286" s="34" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B286" s="34" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C286" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D286" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E286" s="35" t="s">
+        <x:v>339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A287" s="34" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B287" s="34" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C287" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D287" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E287" s="34" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A288" s="34" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B288" s="34" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C288" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D288" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E288" s="34" t="s">
+        <x:v>258</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A289" s="34" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B289" s="34" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C289" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D289" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E289" s="34" t="s">
+        <x:v>691</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A290" s="34" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B290" s="34" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C290" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D290" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E290" s="34" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A291" s="34" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B291" s="34" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C291" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D291" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E291" s="35" t="s">
+        <x:v>358</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A292" s="34" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B292" s="34" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C292" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D292" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E292" s="35" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A293" s="34" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B293" s="34" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C293" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D293" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E293" s="34" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A294" s="34" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B294" s="34">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C294" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D294" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E294" s="34" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A295" s="34" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B295" s="34" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="C295" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D295" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E295" s="35" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F295" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G295" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A296" s="34" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B296" s="34" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C296" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D296" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E296" s="35" t="s">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A297" s="34" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B297" s="34" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="C297" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D297" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E297" s="35" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A298" s="34" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B298" s="34" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C298" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D298" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E298" s="34" t="s">
+        <x:v>261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A299" s="34" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B299" s="34" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C299" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D299" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E299" s="35" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F299" s="5" t="s">
+        <x:v>690</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A300" s="34" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B300" s="34" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="C300" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D300" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E300" s="34" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A301" s="34" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B301" s="34" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C301" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D301" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E301" s="35" t="s">
+        <x:v>338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A302" s="34" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B302" s="34" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="C302" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D302" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E302" s="35" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A303" s="34" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B303" s="34" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C303" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D303" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E303" s="34" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A304" s="34" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B304" s="34">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C304" s="5" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D304" s="8" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E304" s="34" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A305" s="33" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B305" s="33" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="C305" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D305" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E305" s="19" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="F305" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G305" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A306" s="33" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B306" s="33" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="C306" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D306" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E306" s="19" t="s">
+        <x:v>311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A307" s="33" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B307" s="33" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E307" s="26" t="s">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A308" s="33" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B308" s="33" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="C308" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D308" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E308" s="19" t="s">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A309" s="33" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B309" s="33" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="C309" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D309" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E309" s="19" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A310" s="33" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B310" s="33" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="C310" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D310" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E310" s="19" t="s">
         <x:v>267</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="15.75" customHeight="1"/>
-    <x:row r="130" ht="15.75" customHeight="1"/>
-    <x:row r="131" ht="15.75" customHeight="1"/>
-    <x:row r="132" ht="15.75" customHeight="1"/>
-    <x:row r="133" ht="15.75" customHeight="1"/>
-    <x:row r="134" ht="15.75" customHeight="1"/>
-    <x:row r="135" ht="15.75" customHeight="1"/>
-    <x:row r="136" ht="15.75" customHeight="1"/>
-    <x:row r="137" ht="15.75" customHeight="1"/>
-    <x:row r="138" ht="15.75" customHeight="1"/>
-    <x:row r="139" ht="15.75" customHeight="1"/>
-    <x:row r="140" ht="15.75" customHeight="1"/>
-    <x:row r="141" ht="15.75" customHeight="1"/>
-    <x:row r="142" ht="15.75" customHeight="1"/>
-    <x:row r="143" ht="15.75" customHeight="1"/>
-    <x:row r="144" ht="15.75" customHeight="1"/>
-    <x:row r="145" ht="15.75" customHeight="1"/>
-    <x:row r="146" ht="15.75" customHeight="1"/>
-    <x:row r="147" ht="15.75" customHeight="1"/>
-    <x:row r="148" ht="15.75" customHeight="1"/>
-    <x:row r="149" ht="15.75" customHeight="1"/>
-    <x:row r="150" ht="15.75" customHeight="1"/>
-    <x:row r="151" ht="15.75" customHeight="1"/>
-    <x:row r="152" ht="15.75" customHeight="1"/>
-    <x:row r="153" ht="15.75" customHeight="1"/>
-    <x:row r="154" ht="15.75" customHeight="1"/>
-    <x:row r="155" ht="15.75" customHeight="1"/>
-    <x:row r="156" ht="15.75" customHeight="1"/>
-    <x:row r="157" ht="15.75" customHeight="1"/>
-    <x:row r="158" ht="15.75" customHeight="1"/>
-    <x:row r="159" ht="15.75" customHeight="1"/>
-    <x:row r="160" ht="15.75" customHeight="1"/>
-    <x:row r="161" ht="15.75" customHeight="1"/>
-    <x:row r="162" ht="15.75" customHeight="1"/>
-    <x:row r="163" ht="15.75" customHeight="1"/>
-    <x:row r="164" ht="15.75" customHeight="1"/>
-    <x:row r="165" ht="15.75" customHeight="1"/>
-    <x:row r="166" ht="15.75" customHeight="1"/>
-    <x:row r="167" ht="15.75" customHeight="1"/>
-    <x:row r="168" ht="15.75" customHeight="1"/>
-    <x:row r="169" ht="15.75" customHeight="1"/>
-    <x:row r="170" ht="15.75" customHeight="1"/>
-    <x:row r="171" ht="15.75" customHeight="1"/>
-    <x:row r="172" ht="15.75" customHeight="1"/>
-    <x:row r="173" ht="15.75" customHeight="1"/>
-    <x:row r="174" ht="15.75" customHeight="1"/>
-    <x:row r="175" ht="15.75" customHeight="1"/>
-    <x:row r="176" ht="15.75" customHeight="1"/>
-    <x:row r="177" ht="15.75" customHeight="1"/>
-    <x:row r="178" ht="15.75" customHeight="1"/>
-    <x:row r="179" ht="15.75" customHeight="1"/>
-    <x:row r="180" ht="15.75" customHeight="1"/>
-    <x:row r="181" ht="15.75" customHeight="1"/>
-    <x:row r="182" ht="15.75" customHeight="1"/>
-    <x:row r="183" ht="15.75" customHeight="1"/>
-    <x:row r="184" ht="15.75" customHeight="1"/>
-    <x:row r="185" ht="15.75" customHeight="1"/>
-    <x:row r="186" ht="15.75" customHeight="1"/>
-    <x:row r="187" ht="15.75" customHeight="1"/>
-    <x:row r="188" ht="15.75" customHeight="1"/>
-    <x:row r="189" ht="15.75" customHeight="1"/>
-    <x:row r="190" ht="15.75" customHeight="1"/>
-    <x:row r="191" ht="15.75" customHeight="1"/>
-    <x:row r="192" ht="15.75" customHeight="1"/>
-    <x:row r="193" ht="15.75" customHeight="1"/>
-    <x:row r="194" ht="15.75" customHeight="1"/>
-    <x:row r="195" ht="15.75" customHeight="1"/>
-    <x:row r="196" ht="15.75" customHeight="1"/>
-    <x:row r="197" ht="15.75" customHeight="1"/>
-    <x:row r="198" ht="15.75" customHeight="1"/>
-    <x:row r="199" ht="15.75" customHeight="1"/>
-    <x:row r="200" ht="15.75" customHeight="1"/>
-    <x:row r="201" ht="15.75" customHeight="1"/>
-    <x:row r="202" ht="15.75" customHeight="1"/>
-    <x:row r="203" ht="15.75" customHeight="1"/>
-    <x:row r="204" ht="15.75" customHeight="1"/>
-    <x:row r="205" ht="15.75" customHeight="1"/>
-    <x:row r="206" ht="15.75" customHeight="1"/>
-    <x:row r="207" ht="15.75" customHeight="1"/>
-    <x:row r="208" ht="15.75" customHeight="1"/>
-    <x:row r="209" ht="15.75" customHeight="1"/>
-    <x:row r="210" ht="15.75" customHeight="1"/>
-    <x:row r="211" ht="15.75" customHeight="1"/>
-    <x:row r="212" ht="15.75" customHeight="1"/>
-    <x:row r="213" ht="15.75" customHeight="1"/>
-    <x:row r="214" ht="15.75" customHeight="1"/>
-    <x:row r="215" ht="15.75" customHeight="1"/>
-    <x:row r="216" ht="15.75" customHeight="1"/>
-    <x:row r="217" ht="15.75" customHeight="1"/>
-    <x:row r="218" ht="15.75" customHeight="1"/>
-    <x:row r="219" ht="15.75" customHeight="1"/>
-    <x:row r="220" ht="15.75" customHeight="1"/>
-    <x:row r="221" ht="15.75" customHeight="1"/>
-    <x:row r="222" ht="15.75" customHeight="1"/>
-    <x:row r="223" ht="15.75" customHeight="1"/>
-    <x:row r="224" ht="15.75" customHeight="1"/>
-    <x:row r="225" ht="15.75" customHeight="1"/>
-    <x:row r="226" ht="15.75" customHeight="1"/>
-    <x:row r="227" ht="15.75" customHeight="1"/>
-    <x:row r="228" ht="15.75" customHeight="1"/>
-    <x:row r="229" ht="15.75" customHeight="1"/>
-    <x:row r="230" ht="15.75" customHeight="1"/>
-    <x:row r="231" ht="15.75" customHeight="1"/>
-    <x:row r="232" ht="15.75" customHeight="1"/>
-    <x:row r="233" ht="15.75" customHeight="1"/>
-    <x:row r="234" ht="15.75" customHeight="1"/>
-    <x:row r="235" ht="15.75" customHeight="1"/>
-    <x:row r="236" ht="15.75" customHeight="1"/>
-    <x:row r="237" ht="15.75" customHeight="1"/>
-    <x:row r="238" ht="15.75" customHeight="1"/>
-    <x:row r="239" ht="15.75" customHeight="1"/>
-    <x:row r="240" ht="15.75" customHeight="1"/>
-    <x:row r="241" ht="15.75" customHeight="1"/>
-    <x:row r="242" ht="15.75" customHeight="1"/>
-    <x:row r="243" ht="15.75" customHeight="1"/>
-    <x:row r="244" ht="15.75" customHeight="1"/>
-    <x:row r="245" ht="15.75" customHeight="1"/>
-    <x:row r="246" ht="15.75" customHeight="1"/>
-    <x:row r="247" ht="15.75" customHeight="1"/>
-    <x:row r="248" ht="15.75" customHeight="1"/>
-    <x:row r="249" ht="15.75" customHeight="1"/>
-    <x:row r="250" ht="15.75" customHeight="1"/>
-    <x:row r="251" ht="15.75" customHeight="1"/>
-    <x:row r="252" ht="15.75" customHeight="1"/>
-    <x:row r="253" ht="15.75" customHeight="1"/>
-    <x:row r="254" ht="15.75" customHeight="1"/>
-    <x:row r="255" ht="15.75" customHeight="1"/>
-    <x:row r="256" ht="15.75" customHeight="1"/>
-    <x:row r="257" ht="15.75" customHeight="1"/>
-    <x:row r="258" ht="15.75" customHeight="1"/>
-    <x:row r="259" ht="15.75" customHeight="1"/>
-    <x:row r="260" ht="15.75" customHeight="1"/>
-    <x:row r="261" ht="15.75" customHeight="1"/>
-    <x:row r="262" ht="15.75" customHeight="1"/>
-    <x:row r="263" ht="15.75" customHeight="1"/>
-    <x:row r="264" ht="15.75" customHeight="1"/>
-    <x:row r="265" ht="15.75" customHeight="1"/>
-    <x:row r="266" ht="15.75" customHeight="1"/>
-    <x:row r="267" ht="15.75" customHeight="1"/>
-    <x:row r="268" ht="15.75" customHeight="1"/>
-    <x:row r="269" ht="15.75" customHeight="1"/>
-    <x:row r="270" ht="15.75" customHeight="1"/>
-    <x:row r="271" ht="15.75" customHeight="1"/>
-    <x:row r="272" ht="15.75" customHeight="1"/>
-    <x:row r="273" ht="15.75" customHeight="1"/>
-    <x:row r="274" ht="15.75" customHeight="1"/>
-    <x:row r="275" ht="15.75" customHeight="1"/>
-    <x:row r="276" ht="15.75" customHeight="1"/>
-    <x:row r="277" ht="15.75" customHeight="1"/>
-    <x:row r="278" ht="15.75" customHeight="1"/>
-    <x:row r="279" ht="15.75" customHeight="1"/>
-    <x:row r="280" ht="15.75" customHeight="1"/>
-    <x:row r="281" ht="15.75" customHeight="1"/>
-    <x:row r="282" ht="15.75" customHeight="1"/>
-    <x:row r="283" ht="15.75" customHeight="1"/>
-    <x:row r="284" ht="15.75" customHeight="1"/>
-    <x:row r="285" ht="15.75" customHeight="1"/>
-    <x:row r="286" ht="15.75" customHeight="1"/>
-    <x:row r="287" ht="15.75" customHeight="1"/>
-    <x:row r="288" ht="15.75" customHeight="1"/>
-    <x:row r="289" ht="15.75" customHeight="1"/>
-    <x:row r="290" ht="15.75" customHeight="1"/>
-    <x:row r="291" ht="15.75" customHeight="1"/>
-    <x:row r="292" ht="15.75" customHeight="1"/>
-    <x:row r="293" ht="15.75" customHeight="1"/>
-    <x:row r="294" ht="15.75" customHeight="1"/>
-    <x:row r="295" ht="15.75" customHeight="1"/>
-    <x:row r="296" ht="15.75" customHeight="1"/>
-    <x:row r="297" ht="15.75" customHeight="1"/>
-    <x:row r="298" ht="15.75" customHeight="1"/>
-    <x:row r="299" ht="15.75" customHeight="1"/>
-    <x:row r="300" ht="15.75" customHeight="1"/>
-    <x:row r="301" ht="15.75" customHeight="1"/>
-    <x:row r="302" ht="15.75" customHeight="1"/>
-    <x:row r="303" ht="15.75" customHeight="1"/>
-    <x:row r="304" ht="15.75" customHeight="1"/>
-    <x:row r="305" ht="15.75" customHeight="1"/>
-    <x:row r="306" ht="15.75" customHeight="1"/>
-    <x:row r="307" ht="15.75" customHeight="1"/>
-    <x:row r="308" ht="15.75" customHeight="1"/>
-    <x:row r="309" ht="15.75" customHeight="1"/>
-    <x:row r="310" ht="15.75" customHeight="1"/>
-    <x:row r="311" ht="15.75" customHeight="1"/>
-    <x:row r="312" ht="15.75" customHeight="1"/>
-    <x:row r="313" ht="15.75" customHeight="1"/>
-    <x:row r="314" ht="15.75" customHeight="1"/>
-    <x:row r="315" ht="15.75" customHeight="1"/>
-    <x:row r="316" ht="15.75" customHeight="1"/>
-    <x:row r="317" ht="15.75" customHeight="1"/>
-    <x:row r="318" ht="15.75" customHeight="1"/>
-    <x:row r="319" ht="15.75" customHeight="1"/>
-    <x:row r="320" ht="15.75" customHeight="1"/>
-    <x:row r="321" ht="15.75" customHeight="1"/>
-    <x:row r="322" ht="15.75" customHeight="1"/>
-    <x:row r="323" ht="15.75" customHeight="1"/>
-    <x:row r="324" ht="15.75" customHeight="1"/>
-    <x:row r="325" ht="15.75" customHeight="1"/>
-    <x:row r="326" ht="15.75" customHeight="1"/>
-    <x:row r="327" ht="15.75" customHeight="1"/>
-    <x:row r="328" ht="15.75" customHeight="1"/>
-    <x:row r="329" ht="15.75" customHeight="1"/>
-    <x:row r="330" ht="15.75" customHeight="1"/>
-    <x:row r="331" ht="15.75" customHeight="1"/>
-    <x:row r="332" ht="15.75" customHeight="1"/>
-    <x:row r="333" ht="15.75" customHeight="1"/>
-    <x:row r="334" ht="15.75" customHeight="1"/>
-    <x:row r="335" ht="15.75" customHeight="1"/>
-    <x:row r="336" ht="15.75" customHeight="1"/>
-    <x:row r="337" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A311" s="33" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B311" s="33" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="C311" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D311" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E311" s="19" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A312" s="33" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B312" s="33" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="C312" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D312" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E312" s="19" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A313" s="33" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="B313" s="33" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="C313" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D313" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E313" s="19" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A314" s="33" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B314" s="33" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C314" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D314" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E314" s="5" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A315" s="33" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B315" s="33" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C315" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D315" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E315" s="19" t="s">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A316" s="33" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B316" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C316" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D316" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E316" s="5" t="s">
+        <x:v>424</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A317" s="33" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B317" s="33" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C317" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D317" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E317" s="19" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F317" s="5" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="G317" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A318" s="33" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="B318" s="33" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C318" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D318" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E318" s="5" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A319" s="33" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B319" s="33" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C319" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D319" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E319" s="19" t="s">
+        <x:v>433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A320" s="33" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B320" s="33" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C320" s="5" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D320" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E320" s="19" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A321" s="33" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B321" s="33" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C321" s="5" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D321" s="8" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E321" s="19" t="s">
+        <x:v>624</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A322" s="33" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B322" s="33" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C322" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D322" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E322" s="19" t="s">
+        <x:v>432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A323" s="33" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B323" s="33" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C323" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D323" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E323" s="19" t="s">
+        <x:v>625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A324" s="33" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B324" s="33" t="s">
+        <x:v>719</x:v>
+      </x:c>
+      <x:c r="C324" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D324" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E324" s="19" t="s">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A325" s="33" t="s">
+        <x:v>719</x:v>
+      </x:c>
+      <x:c r="B325" s="33" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="C325" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D325" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E325" s="19" t="s">
+        <x:v>275</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A326" s="33" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B326" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C326" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D326" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E326" s="5" t="s">
+        <x:v>276</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A327" s="33" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="B327" s="33" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="C327" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D327" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E327" s="19" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F327" s="5" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G327" s="5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A328" s="33" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B328" s="33" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="C328" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D328" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E328" s="5" t="s">
+        <x:v>330</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A329" s="33" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B329" s="33" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C329" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D329" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E329" s="19" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A330" s="33" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B330" s="33" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C330" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D330" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E330" s="19" t="s">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A331" s="33" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B331" s="33" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C331" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D331" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E331" s="19" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A332" s="33" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B332" s="33" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C332" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D332" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E332" s="19" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A333" s="33" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B333" s="33" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C333" s="8" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="D333" s="8" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="E333" s="19" t="s">
+        <x:v>338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A334" s="33" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B334" s="33" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C334" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D334" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E334" s="19" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F334" s="5" t="s">
+        <x:v>365</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A335" s="33" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B335" s="33" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C335" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D335" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E335" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A336" s="33" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B336" s="33" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C336" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D336" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E336" s="19" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A337" s="33" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B337" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C337" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D337" s="8" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E337" s="5" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
     <x:row r="338" ht="15.75" customHeight="1"/>
     <x:row r="339" ht="15.75" customHeight="1"/>
     <x:row r="340" ht="15.75" customHeight="1"/>
@@ -4845,6 +9641,10 @@
     <x:row r="998" ht="15.75" customHeight="1"/>
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
+    <x:row r="1001" ht="15.75" customHeight="1"/>
+    <x:row r="1002" ht="15.75" customHeight="1"/>
+    <x:row r="1003" ht="15.75" customHeight="1"/>
+    <x:row r="1004" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
